--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="1701">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6217,12 +6217,242 @@
     <t>貼上剛剛複製的兌換碼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>溯回青空</t>
+  </si>
+  <si>
+    <t>蒼之啟示錄</t>
+  </si>
+  <si>
+    <t>第六絕區</t>
+  </si>
+  <si>
+    <t>MO.KO</t>
+  </si>
+  <si>
+    <t>幻世三國：一騎當千</t>
+  </si>
+  <si>
+    <t>經典日系x末日魔王x卡牌RPG《溯回青空》
+這是你與生俱來的使命——統率不老不死的少年少女騎士團，化身「魔王」對抗眾神
+在眾神與人類爭奪星球霸權的亂世中，人類在第八度瀕臨滅絕後開啟了「第九軌道人類史」。
+此刻，眾神再次啟動「軌道修正計畫」，企圖將人類存在徹底抹除於歷史長河。
+而你，將率領前八大軌道的騎士團，對抗眾神，奪回青空。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《蒼之啟示錄》以架空大陸魔王蘇醒為背景，玩家扮演「神選者」，透過收集聖器、挑戰副本來阻止魔族入侵，融合了PVE/PVP雙線戰鬥與開放世界探索機制。遊戲採用二次元畫風與日韓幻想美術風格，建構涵蓋九大區域的里斯特大陸。核心玩法包含自動掛網戰鬥、自由交易系統和英靈變身戰鬥，設有三大職業轉職體系及天啟之書成長指引。社交模塊整合了聖團協作、伴侶締結與跨服溫泉等互動玩法，結合馴龍作戰、釣魚種花等休閒內容，形成獨特的「佛系冒險」特色。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未來世界因名為「米洛斯」的能源核心失控陷入危機，倖存者退守至最後的防線 —— 第六絕區。
+作為指揮官，你將帶領小隊探索被異變的其它絕區：自動化戰鬥解放雙手，離線也能積累資源；自由搭配未來槍械、戰術裝備與變異戰寵，組建專屬戰鬥流派。在廢墟中搜尋強化物資，抵禦變異生物侵襲，逐步揭開「米洛斯」爆發的真相。
+末世已至，點擊開啟你的「放置割草 + 策略生存」之旅！　</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我們非常高興你能來體驗《mo.co》。我們的團隊致力於打造一款融合輕度RPG元素的多人動作遊戲，希望能讓它簡單好上手、社交互動豐富，且充滿活力。
+從想體驗碎片化MMO或ARPG遊戲的資深玩家，到從未感受過這類遊戲樂趣的新玩家，我們希望打造一款能讓每個人都可以沉浸其中的遊戲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃魂再啟，三國新紀元，邀你共赴熱血激戰！
+在《幻世三國：一騎當千》的世界裡，歷史與幻想交織，經典英雄與全新設定碰撞出令人熱血沸騰的冒險！這是一款融合了動作連招、策略養成與社交互動的三國ARPG手遊。
+時空的縫隙撕裂了三國大地，神秘力量令群雄異化，昔日的英雄化身全新戰神，東漢末年的烽煙中夾雜著神明的低語與科技的嘶鳴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100石 稱號秘密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEIKAIHAGAMEDECHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXRMIZUGI2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100石 稱號blade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうさんにちきねんび</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入下方連結兌換</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rxr.happyelements.co.jp/campaign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AK79513 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約禮包 + 2025抽卡機會</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS34567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏日補給虛寶空投</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲後點左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主角畫面中按"兌換碼"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兌換完成後到信箱領取禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小兵立大功</t>
+  </si>
+  <si>
+    <t>像素全明星</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《小兵立大功》率領召喚師、英雄和小兵擊潰敵軍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>打造專屬軍團</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>充滿打擊感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>展開史詩級戰爭。
+從召喚師、英雄、小兵升級中做出選擇，在如同殭屍般移動的敵人圍毆中存活下來！體驗充滿緊張刺激的類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rogue RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>！
+體驗直觀操作及充滿打擊感的休閒系動作手遊！</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>像素全明星陣容，熱門經典人物大亂鬥
+遊戲採用經典的點數風格，帶給玩家濃厚的懷舊感。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>每個角色、場景和技能效果都呈現出極具創意和魅力的點數藝術，讓你在回憶經典的同時，享受全新的遊戲體驗。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6323,6 +6553,19 @@
       <name val="Inherit"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6356,7 +6599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -6412,11 +6655,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6472,9 +6725,17 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -6776,7 +7037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW656"/>
+  <dimension ref="A1:AW654"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
@@ -15298,7 +15559,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C156" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C163" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -16434,26 +16695,262 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="19.899999999999999" customHeight="1"/>
-    <row r="158" spans="1:31" ht="19.899999999999999" customHeight="1"/>
-    <row r="159" spans="1:31" ht="19.899999999999999" customHeight="1"/>
-    <row r="160" spans="1:31" ht="19.899999999999999" customHeight="1"/>
-    <row r="161" ht="19.899999999999999" customHeight="1"/>
-    <row r="162" ht="19.899999999999999" customHeight="1"/>
-    <row r="163" ht="19.899999999999999" customHeight="1"/>
-    <row r="164" ht="19.899999999999999" customHeight="1"/>
-    <row r="165" ht="19.899999999999999" customHeight="1"/>
-    <row r="166" ht="19.899999999999999" customHeight="1"/>
-    <row r="167" ht="19.899999999999999" customHeight="1"/>
-    <row r="168" ht="19.899999999999999" customHeight="1"/>
-    <row r="169" ht="19.899999999999999" customHeight="1"/>
-    <row r="170" ht="19.899999999999999" customHeight="1"/>
-    <row r="171" ht="19.899999999999999" customHeight="1"/>
-    <row r="172" ht="19.899999999999999" customHeight="1"/>
-    <row r="173" ht="19.899999999999999" customHeight="1"/>
-    <row r="174" ht="19.899999999999999" customHeight="1"/>
-    <row r="175" ht="19.899999999999999" customHeight="1"/>
-    <row r="176" ht="19.899999999999999" customHeight="1"/>
+    <row r="157" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A157" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C157" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
+      </c>
+      <c r="D157" s="23" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F157" s="24" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="O157" s="2" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="158" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A158" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C158" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
+      </c>
+      <c r="D158" s="23" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="159" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A159" s="12" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C159" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
+      </c>
+      <c r="D159" s="23" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="160" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A160" s="12" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C160" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/MO.KO-禮包碼.jpg</v>
+      </c>
+      <c r="D160" s="23" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L160" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A161" s="12" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C161" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
+      </c>
+      <c r="D161" s="23" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A162" s="12" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C162" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
+      </c>
+      <c r="D162" s="25" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A163" s="12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C163" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
+      </c>
+      <c r="D163" s="25" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="165" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="166" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="167" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="168" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="169" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="170" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="171" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="172" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="173" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="174" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="175" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="176" spans="1:13" ht="19.899999999999999" customHeight="1"/>
     <row r="177" ht="19.899999999999999" customHeight="1"/>
     <row r="178" ht="19.899999999999999" customHeight="1"/>
     <row r="179" ht="19.899999999999999" customHeight="1"/>
@@ -16932,11 +17429,12 @@
     <row r="652" ht="19.899999999999999" customHeight="1"/>
     <row r="653" ht="19.899999999999999" customHeight="1"/>
     <row r="654" ht="19.899999999999999" customHeight="1"/>
-    <row r="655" ht="19.899999999999999" customHeight="1"/>
-    <row r="656" ht="19.899999999999999" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F157" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -6225,9 +6225,6 @@
   </si>
   <si>
     <t>第六絕區</t>
-  </si>
-  <si>
-    <t>MO.KO</t>
   </si>
   <si>
     <t>幻世三國：一騎當千</t>
@@ -6445,6 +6442,10 @@
       </rPr>
       <t>每個角色、場景和技能效果都呈現出極具創意和魅力的點數藝術，讓你在回憶經典的同時，享受全新的遊戲體驗。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MO.CO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16704,31 +16705,31 @@
         <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="E157" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F157" s="24" t="s">
         <v>1687</v>
       </c>
-      <c r="F157" s="24" t="s">
-        <v>1688</v>
-      </c>
       <c r="J157" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="M157" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="K157" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="L157" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="M157" s="2" t="s">
+      <c r="N157" s="2" t="s">
         <v>1684</v>
       </c>
-      <c r="N157" s="2" t="s">
+      <c r="O157" s="2" t="s">
         <v>1685</v>
-      </c>
-      <c r="O157" s="2" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="158" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
@@ -16740,28 +16741,28 @@
         <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
       </c>
       <c r="D158" s="23" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="159" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
@@ -16773,109 +16774,109 @@
         <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
       </c>
       <c r="D159" s="23" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>1693</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="G159" s="2" t="s">
         <v>1694</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="H159" s="2" t="s">
         <v>1695</v>
       </c>
-      <c r="H159" s="2" t="s">
-        <v>1696</v>
-      </c>
       <c r="J159" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K159" s="2" t="s">
         <v>1689</v>
       </c>
-      <c r="K159" s="2" t="s">
+      <c r="L159" s="2" t="s">
         <v>1690</v>
       </c>
-      <c r="L159" s="2" t="s">
+      <c r="M159" s="2" t="s">
         <v>1691</v>
-      </c>
-      <c r="M159" s="2" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="160" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A160" s="12" t="s">
-        <v>1673</v>
+        <v>1700</v>
       </c>
       <c r="C160" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>giftcodesbanner/MO.KO-禮包碼.jpg</v>
+        <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A161" s="12" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C161" s="2" t="str">
         <f t="shared" si="3"/>
         <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
       </c>
       <c r="D161" s="23" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>1679</v>
       </c>
-      <c r="E161" s="2" t="s">
-        <v>1680</v>
-      </c>
       <c r="F161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A162" s="12" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C162" s="2" t="str">
         <f t="shared" si="3"/>
         <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>1478</v>
@@ -16904,14 +16905,14 @@
     </row>
     <row r="163" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A163" s="12" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="C163" s="2" t="str">
         <f t="shared" si="3"/>
         <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>1478</v>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="1701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="1716">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6448,12 +6448,74 @@
     <t>MO.CO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>浣熊傳說</t>
+  </si>
+  <si>
+    <t>勇者格鬥城</t>
+  </si>
+  <si>
+    <t>即時高智商對戰！獨創五行制衡戰術！
+過百種浣熊英雄！每張都是藝術品！
+全球PVP競技場！用策略證明誰是浣熊之王！
+無門檻終極狂歡！首發限定SSR免費領！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《勇者格鬥城》橫版動作手遊震撼來襲！六大職業任選，暢爽連招對決BOSS。挑戰深淵副本贏稀有裝備，PVP競技場展現操作實力。無論是冒險獨行俠還是競技達人，都能找到專屬戰鬥樂趣！即刻加入，體驗極致打擊快感，爭奪最強勇者稱號！
+【六大獨特職業】
+任你選擇，專屬技能與戰鬥風格帶來截然不同的體驗！挑戰多層次副本，從普通地下城到深淵Boss，海量關卡，驚喜不斷！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip999</t>
+  </si>
+  <si>
+    <t>點擊主界面坐上頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上即可兌換成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">vip888 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄經驗*50000+金幣*50000+鑽石*200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*100000+一元大鈔*3+鑽石*400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*70000+一元大鈔*2+鑽石*300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*50000+一元大鈔*1+鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6567,6 +6629,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFE2E5E9"/>
+      <name val="Segoe UI Historic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6670,7 +6738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6733,6 +6801,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -15560,7 +15629,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C163" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C165" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -16834,7 +16903,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="161" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A161" s="12" t="s">
         <v>1673</v>
       </c>
@@ -16867,7 +16936,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="162" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A162" s="12" t="s">
         <v>1696</v>
       </c>
@@ -16903,7 +16972,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="163" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A163" s="12" t="s">
         <v>1697</v>
       </c>
@@ -16939,19 +17008,98 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="165" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="166" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="167" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="168" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="169" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="170" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="171" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="172" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="173" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="174" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="175" spans="1:13" ht="19.899999999999999" customHeight="1"/>
-    <row r="176" spans="1:13" ht="19.899999999999999" customHeight="1"/>
+    <row r="164" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A164" s="12" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C164" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/浣熊傳說-禮包碼.jpg</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="J164" s="26" t="s">
+        <v>1705</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="N164" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="O164" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="P164" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="Q164" s="2" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A165" s="12" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C165" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/勇者格鬥城-禮包碼.jpg</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="167" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="168" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="169" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="170" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="171" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="172" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="173" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="174" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="175" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="176" spans="1:17" ht="19.899999999999999" customHeight="1"/>
     <row r="177" ht="19.899999999999999" customHeight="1"/>
     <row r="178" ht="19.899999999999999" customHeight="1"/>
     <row r="179" ht="19.899999999999999" customHeight="1"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="1716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="1740">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6508,6 +6508,103 @@
   </si>
   <si>
     <t>金幣*50000+一元大鈔*1+鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星耀球會</t>
+  </si>
+  <si>
+    <t>背上小小背包出發世界旅行的白熊, 龐寶。偶然遇見的寶箱怪低著聲說「從你身上感受到勇士的氣息。」
+一直沉睡的魔像“領路者”醒了過來,龐寶則和36位夥伴一起向著新大陸前進。而那個地方有著可怕的魔王“藍波”在等著。
+“現在, 是時候由背著背包的命運勇士 - 龐寶照亮前方的路了。”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cutieggg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bnsc2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soccerclub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點擊左上方隊徽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在禮品碼後點擊「輸入」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈窗中輸入禮包碼即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameplayhk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龐寶：背包英雄們</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《星耀球會》一款由球隊名、隊徽、主場風格任你設計的手遊，玩家將同時化身事會主席、球探、經理、甚至教練。你的球會，由你話事!
+遊戲以「球會」為核心，玩家唔止係揀陣式咁簡單。由起訓練設施、規劃財政、球員買賣、隊伍發展，到球場設計都由你話事。你係球會掌舵人，完全掌控整個球會並自己心目中的理想！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>東方幻想ECLIPSE</t>
+  </si>
+  <si>
+    <t>被遺忘之人匯聚的樂園——幻想鄉。 人類與妖怪在這片寧靜之地共存，歲月靜好，彷彿永恆不變…… 然而，突如其來的「它們」，打破了這份安寧。 前所未見的異質存在，如暗潮般悄然蔓延，將整個幻想鄉捲入前所未有的混亂。 生活在這片土地上的「她們」，懷抱著各自的信念與使命，踏上了行動的旅途。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weLvkwt4JkEf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★4 想起卡「褪去自我風格」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲首頁，點選右上角「選單」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇右側的「序號碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入序號後，即可領取到對應獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a3aayerPNUHk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈願券*10+藥膳茶*3+復活仙果*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*300+體力包*10+士氣包*10+醫療包*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*2M+金幣*200+士氣包*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*1M+初級球探*200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初級球探*200+士氣包*30+醫療包*30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15629,7 +15726,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C165" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C168" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -17089,9 +17186,120 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="167" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="168" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="166" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A166" s="18" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C166" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/龐寶：背包英雄們-禮包碼.jpg</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A167" s="12" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C167" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/星耀球會-禮包碼.jpg</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="O167" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="P167" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="Q167" s="2" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="A168" s="11" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C168" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/東方幻想ECLIPSE-禮包碼.jpg</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>1735</v>
+      </c>
+    </row>
     <row r="169" spans="1:17" ht="19.899999999999999" customHeight="1"/>
     <row r="170" spans="1:17" ht="19.899999999999999" customHeight="1"/>
     <row r="171" spans="1:17" ht="19.899999999999999" customHeight="1"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="1740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="1790">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6560,51 +6560,251 @@
     <t>東方幻想ECLIPSE</t>
   </si>
   <si>
+    <t>weLvkwt4JkEf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★4 想起卡「褪去自我風格」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲首頁，點選右上角「選單」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇右側的「序號碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入序號後，即可領取到對應獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a3aayerPNUHk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈願券*10+藥膳茶*3+復活仙果*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*300+體力包*10+士氣包*10+醫療包*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*2M+金幣*200+士氣包*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*1M+初級球探*200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初級球探*200+士氣包*30+醫療包*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世紀帝國M</t>
+  </si>
+  <si>
+    <t>歐啦!守得豬</t>
+  </si>
+  <si>
+    <t>點選左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設定後按禮包碼兌換</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製好的禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETW723</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*500+5分鐘建築加速*15+5分鐘研發加速*15+5分鐘訓練加速*15+1萬安全資源箱*25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右邊三條線選單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設置進去點禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的禮包碼按確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ724</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18櫻花幕府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOK924</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DUALOS7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>被遺忘之人匯聚的樂園——幻想鄉。 人類與妖怪在這片寧靜之地共存，歲月靜好，彷彿永恆不變…… 然而，突如其來的「它們」，打破了這份安寧。 前所未見的異質存在，如暗潮般悄然蔓延，將整個幻想鄉捲入前所未有的混亂。 生活在這片土地上的「她們」，懷抱著各自的信念與使命，踏上了行動的旅途。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>weLvkwt4JkEf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>★4 想起卡「褪去自我風格」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入遊戲首頁，點選右上角「選單」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>選擇右側的「序號碼」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入序號後，即可領取到對應獎勵。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a3aayerPNUHk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>祈願券*10+藥膳茶*3+復活仙果*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*300+體力包*10+士氣包*10+醫療包*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資金*2M+金幣*200+士氣包*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資金*1M+初級球探*200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初級球探*200+士氣包*30+醫療包*30</t>
+    <t>戰姬的魅力，從不只在戰場！每位乙女皆擁有隱藏立繪與進階服裝，隨著升星、親密互動、羈絆突破逐步解鎖---從威武戰甲到柔情私服，從冷豔武將到嬌羞美人。這場亂世，不只是爭霸，更是攻略每一顆芳心。
+《18櫻花幕府》與盟友並肩奪城，成為一國之主！
+加入家族，參與大型跨服城戰。運籌帷幄，調度戰姬，佔領據點、掠奪資源，證明你才是真正的幕府霸主。兄弟齊心，其利斷金，稱霸戰國等你來挑戰！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*10+金扭蛋幣*10+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+體力*20+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+初級鎧甲圖紙+初級王冠圖紙+初級聖杯圖紙*4+初級面具圖紙*3+初級聖劍圖紙*1+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWAWAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEM888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWHAGENG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWKUANGBAOXIAOJIAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWNL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWHUALUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWCHIGUIBOBO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWGUIGOU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWWAYNE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOVEAOEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEMGL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYJULY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEMTWEMULATOR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳說現世招募券*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*N+隨機資源加速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進去之後畫面中間偏右下禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>織田信秀姬魂*100+3級經驗書*10+判金*500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判金*888+神樂鈴*10+銅錢*88888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《世紀帝國M》引入玩家熟悉的八大文明(中式、羅馬式、法蘭克式、拜占庭式、埃及式、不列顛式、日式及韓式)、傭兵系統，以及經典的資源採集和分配機制，玩家需要合理安排村民進行採礦、捕魚、打獵、採樹莓…等，收集、累積、分配資源用於發展帝國；此外，《世紀帝國》經典的音樂音效、宏偉逼真的攻城器械也將在遊戲中出現，玩家不僅能使用到豐富的策略，更能被喚起有關《世紀帝國》的美好回憶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>誰說英雄一定要帥？《歐啦！守得豬》的英雄角色可謂是「跨次元」的明星大集合！我們汲取了大量流行元素，巧妙地將其與各種動物形象融合，打造出個性十足、醜萌兼具的天團戰隊。每一位英雄都身懷絕技，每一次召喚都可能帶來意外的驚喜與強大的戰力。各種趣味屬性、羈絆配搭，讓策略變得既豐富又有趣，誰說塔防一定嚴肅？來點萌萌鬼畜，笑著守住你的家園！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15726,7 +15926,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C168" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C172" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -17000,7 +17200,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="161" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A161" s="12" t="s">
         <v>1673</v>
       </c>
@@ -17033,7 +17233,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="162" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A162" s="12" t="s">
         <v>1696</v>
       </c>
@@ -17069,7 +17269,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="163" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A163" s="12" t="s">
         <v>1697</v>
       </c>
@@ -17105,7 +17305,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="164" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A164" s="12" t="s">
         <v>1701</v>
       </c>
@@ -17150,7 +17350,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="165" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A165" s="12" t="s">
         <v>1702</v>
       </c>
@@ -17186,7 +17386,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="166" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A166" s="18" t="s">
         <v>1725</v>
       </c>
@@ -17222,7 +17422,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="167" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A167" s="12" t="s">
         <v>1716</v>
       </c>
@@ -17246,28 +17446,28 @@
         <v>1718</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>1719</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="N167" s="2" t="s">
         <v>1720</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="P167" s="2" t="s">
         <v>1724</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="168" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A168" s="11" t="s">
         <v>1727</v>
       </c>
@@ -17276,38 +17476,232 @@
         <v>giftcodesbanner/東方幻想ECLIPSE-禮包碼.jpg</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J168" s="2" t="s">
         <v>1728</v>
       </c>
-      <c r="E168" s="2" t="s">
-        <v>1731</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>1732</v>
-      </c>
-      <c r="G168" s="2" t="s">
+      <c r="K168" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="L168" s="2" t="s">
         <v>1733</v>
       </c>
-      <c r="J168" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>1730</v>
-      </c>
-      <c r="L168" s="2" t="s">
+      <c r="M168" s="2" t="s">
         <v>1734</v>
       </c>
-      <c r="M168" s="2" t="s">
-        <v>1735</v>
-      </c>
     </row>
-    <row r="169" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="170" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="171" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="172" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="173" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="174" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="175" spans="1:17" ht="19.899999999999999" customHeight="1"/>
-    <row r="176" spans="1:17" ht="19.899999999999999" customHeight="1"/>
+    <row r="169" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A169" s="12" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C169" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/世紀帝國M-禮包碼.jpg</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="N169" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="O169" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="Q169" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="R169" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="S169" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="T169" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="U169" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="V169" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="W169" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="X169" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="Y169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="Z169" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AA169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AB169" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AC169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AD169" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="AE169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AF169" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="AG169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AH169" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="AI169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AJ169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AK169" s="2" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="170" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A170" s="12" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C170" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/歐啦!守得豬-禮包碼.jpg</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="O170" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="Q170" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="R170" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="S170" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="T170" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="U170" s="2" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="171" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A171" s="18" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C171" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/18櫻花幕府-禮包碼.jpg</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="172" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
+      <c r="A172" s="12"/>
+    </row>
+    <row r="173" spans="1:37" ht="19.899999999999999" customHeight="1"/>
+    <row r="174" spans="1:37" ht="19.899999999999999" customHeight="1"/>
+    <row r="175" spans="1:37" ht="19.899999999999999" customHeight="1"/>
+    <row r="176" spans="1:37" ht="19.899999999999999" customHeight="1"/>
     <row r="177" ht="19.899999999999999" customHeight="1"/>
     <row r="178" ht="19.899999999999999" customHeight="1"/>
     <row r="179" ht="19.899999999999999" customHeight="1"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="1790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="1812">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6807,12 +6807,92 @@
     <t>誰說英雄一定要帥？《歐啦！守得豬》的英雄角色可謂是「跨次元」的明星大集合！我們汲取了大量流行元素，巧妙地將其與各種動物形象融合，打造出個性十足、醜萌兼具的天團戰隊。每一位英雄都身懷絕技，每一次召喚都可能帶來意外的驚喜與強大的戰力。各種趣味屬性、羈絆配搭，讓策略變得既豐富又有趣，誰說塔防一定嚴肅？來點萌萌鬼畜，笑著守住你的家園！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>大武道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中央貼上兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按兌換就可以囉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giKuBa</t>
+  </si>
+  <si>
+    <t>穿書先鋒補給</t>
+  </si>
+  <si>
+    <t>FTFiRo</t>
+  </si>
+  <si>
+    <t>先行修練補給包</t>
+  </si>
+  <si>
+    <t>QCKhLg</t>
+  </si>
+  <si>
+    <t>yABTEh</t>
+  </si>
+  <si>
+    <t>nHTgib</t>
+  </si>
+  <si>
+    <t>GmzUMo</t>
+  </si>
+  <si>
+    <t>waWrHF</t>
+  </si>
+  <si>
+    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
+遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6Z3QVNZNC9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V768FCD2MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YZEFPZUYP3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QWDZBKJZ8E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+潛能點掛機券*5+探寶令*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+功法殘頁*10+技能點掛機券*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+探寶令*5+淬體精華掛機券*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功法殘頁*10+探寶令*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6932,6 +7012,20 @@
       <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000080"/>
+      <name val="Inherit"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -7035,7 +7129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7099,6 +7193,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -17696,7 +17802,91 @@
       </c>
     </row>
     <row r="172" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A172" s="12"/>
+      <c r="A172" s="18" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C172" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>giftcodesbanner/大武道-禮包碼.jpg</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="J172" s="27" t="s">
+        <v>1794</v>
+      </c>
+      <c r="K172" s="28" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L172" s="29" t="s">
+        <v>1796</v>
+      </c>
+      <c r="M172" s="30" t="s">
+        <v>1797</v>
+      </c>
+      <c r="N172" s="27" t="s">
+        <v>1798</v>
+      </c>
+      <c r="O172" s="28" t="s">
+        <v>1795</v>
+      </c>
+      <c r="P172" s="29" t="s">
+        <v>1799</v>
+      </c>
+      <c r="Q172" s="30" t="s">
+        <v>1797</v>
+      </c>
+      <c r="R172" s="27" t="s">
+        <v>1800</v>
+      </c>
+      <c r="S172" s="28" t="s">
+        <v>1795</v>
+      </c>
+      <c r="T172" s="29" t="s">
+        <v>1801</v>
+      </c>
+      <c r="U172" s="30" t="s">
+        <v>1797</v>
+      </c>
+      <c r="V172" s="27" t="s">
+        <v>1802</v>
+      </c>
+      <c r="W172" s="28" t="s">
+        <v>1795</v>
+      </c>
+      <c r="X172" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="Y172" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="Z172" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AA172" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AB172" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AC172" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AD172" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AE172" s="2" t="s">
+        <v>1811</v>
+      </c>
     </row>
     <row r="173" spans="1:37" ht="19.899999999999999" customHeight="1"/>
     <row r="174" spans="1:37" ht="19.899999999999999" customHeight="1"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="1812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="1813">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -5634,6 +5634,1085 @@
   </si>
   <si>
     <t>RO仙境傳說：曙光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美男惡徒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《美男惡徒－暗夜中綻放的邪惡之戀》 「CROWN」是由維多利亞女王欽命成立的秘密組織。所有的成員都是擁有「童話詛咒」的男子，而這些詛咒賦予他們特殊的力量。他們以「以惡制惡」的方式，執行暗殺等任務，維護國家的穩定。
+　　原為郵差的妳，因意外得知 CROWN 的秘密而被迫成為「童話師」，負責記錄成員們的詛咒故事。在一個月內除了要與所有成員一起同住外，還需要記錄所有成員的故事，期間不得與任何人墜入愛河，否則將面臨死亡的命運。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突破5,000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轉蛋券 ×3、雞尾酒套餐（體力+100）×1、經典編織低髻髮型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突破10,000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轉蛋券 ×3、鑽石 ×200、玫瑰模樣的維多利亞風黑色洋裝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突破30,000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轉蛋券 ×4、鑽石 ×300、雞尾酒套餐（體力+100）×2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突破50,000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保證★4角色的【標準角色卡轉蛋券】×1！、鑽石x1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三國冰河時代</t>
+  </si>
+  <si>
+    <t>暗黑崛起</t>
+  </si>
+  <si>
+    <t>轉生魔劍士養成：策略放置RPG</t>
+  </si>
+  <si>
+    <t>輕鬆系三國冰雪模擬經營遊戲《三國冰河時代》今日再度公開全新重點與核心玩法特色，進一步展現「不肝也能玩」的輕鬆體驗，準備這個夏季來一場” 冰的” 三國演習。兩位人氣武將「孫尚香」與「張飛」也同步現身，將以全新造型與技能設計加入各位主公的隊伍。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【純正暗黑體驗，探索祕境之戰】戰法職業流派與豐富的職業內容同步釋出！與來自深海的邪惡勢力對抗，守護結界殘存的能量，成為統禦賽季最強的英雄！
+【暢快連擊無限割草，享受廝殺的快感】雙搖桿操作，無體力限制想戰就戰，面對不斷襲擊的敵人，使用各式各樣的技能爽快連擊、無限割草，Hack and Slash，簡單操作隨時暢玩，Speedrun考驗操作技術，回歸遊戲最純粹的樂趣。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「死亡不是終點復仇才正要開始。」
+魔劍士亞莉亞在與魔王決戰前夕遭到摯友們的背叛而喪命。
+然而她在死亡邊緣重獲新生回到了過去還是新手劍士的時代。
+帶著未來的記憶亞莉亞展開了第二次復仇與成長的旅程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icewar666</t>
+  </si>
+  <si>
+    <t>icewar777</t>
+  </si>
+  <si>
+    <t>icewar888</t>
+  </si>
+  <si>
+    <t>icewar999</t>
+  </si>
+  <si>
+    <t>FBVALUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《極速漂移:3v3》與全球玩家組隊競速、漂移，暢享速度激情。 《極速漂移:3v3》與許多世界頂尖車商合作，讓你能夠駕駛知名品牌的正版豪華車。 炫技般地做出令人驚嘆的漂移，在多樣且逼真的賽道上展開激烈的3v3 對戰，還能與全球玩家組隊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斗羅大陸：獵魂世界</t>
+  </si>
+  <si>
+    <t>指點兵兵</t>
+  </si>
+  <si>
+    <t>《斗羅大陸：獵魂世界》作為首款基於頂尖國漫 IP《斗羅大陸》打造的開放世界 RPG，細膩還原魂獸、魂環、魂骨等核心設定，無論是施展酷炫魂技的燃魂激鬥，還是與夥伴組隊獵殺強大魂獸，都將為玩家帶來最真實的斗羅冒險。
+　　官方今日重磅釋出「斗羅時空」終極代言影片，影片中，終極一班原班人馬傾情演繹，從現實校園跨入斗羅大世界的時空，完美詮釋了遊戲「突破界限、勇敢冒險」的核心精神，點燃所有粉絲玩家的戰鬥熱血！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《指點兵兵》這是一款以三國歷史為背景的塔防類策略遊戲。生於亂世，為了維護世間太平，玩家需要不斷招兵買馬，透過合理的資源配置和戰術安排，建造城池，排兵布陣，抵禦敵人的進攻，最後成為名震一方的主公。
+每局戰鬥共20波敵軍攻勢，透過隨機卡牌強化部隊，打造獨特戰術流派！
+主公將不斷解鎖新型兵種，合適的兵種互相搭配，可獲得獨一無二的聯合技！
+透過招兵買馬，軍師運籌帷幄，武將決勝千里，協助玩家過關斬將！
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>終極斗羅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首款斗羅大世界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獵魂777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃金昊天錘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全民獵魂瓜分百萬現金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斗羅大陸獵魂世界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真斗羅真開放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魂師回歸禮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>變身傳奇</t>
+  </si>
+  <si>
+    <t>Blue eyes：公會大師</t>
+  </si>
+  <si>
+    <t>《變身傳奇》是一款掛機角色扮演遊戲，玩家在遊戲中扮演被神選中的勇者，獲得變身力量，在奇幻世界中冒險，並不斷進化成傳奇英雄。 遊戲主打輕鬆的掛機體驗，即使離線也能持續成長，並提供豐富的社交和pvp元素。  化身為傳說中的英雄，體驗更強大的力量與華麗的戰鬥。 透過冒險與戰鬥成長，在競爭中勝出，奪取無可匹敵的地位！ 放置型動作RPG的真正樂趣無論何時何地都能輕鬆培養角色。 即使你暫時離線，英雄也會持續成長，當你回來時，將展開一場刺激的戰鬥並獲得豐富的獎勵！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>『地球、武林界、符文大地、艾爾弗拉多、魯坎……無數個世界被「高塔」所選中。
+被選中的世界【玩家】，可登上高塔，不斷變強。
+他們為了登上更高的殿堂，創立了【公會】。
+所以說【Blue Eyes】，
+這個如今成為傳說的公會名稱，是所有公會大師的夢想與目標。』</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即將更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEGLOBALOPEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dead Spirit Box (Non-Enhanceable) x1
+Common Element x50
+Common Soul Fragment x200
+Summon Stone Fragment x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入主畫面，點選右上角四個點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入右下設定（齒輪）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊添加優惠券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先點擊CS code右邊的複製</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點添加優惠券貼上Cscode跟禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杖劍傳說：坎斯汀之約</t>
+  </si>
+  <si>
+    <t xml:space="preserve">《杖劍傳說》是一款異世界休閒冒險放置RPG。
+在這裡，你將作為冒險者，自由探索坎斯汀世界的每一個角落。
+在這裡撥開地圖迷霧，尋得掉落在各地的珍稀寶物，體驗輕鬆爽快的
+異世界之旅吧。
+當然，在旅途的過程中，你還會邂逅各式各樣夥伴，與他們並肩作
+戰，共同挑戰神秘的聖獸。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊帳號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入主畫面後點右下角小方塊圖案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金葉子*3+鳶尾*5+暖陽*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>時之沙*300+石塊*100+粗煉石300+歷戰精華1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土雞蛋*3+普通凍乾*5+結緣繩*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJ666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豐饒之葉*100+命運果實*1+體力*25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJ777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨星*200+星之願*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJ888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳說女神牌*2+史詩女神牌*10+稀有女神牌*20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJ999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>糖果小人*2+蜜汁烤肉*3+青草糰子*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSFB888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有女神牌*10+星之願*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSDC888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSLINE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《超級海戰：紀元崛起》是一款以未來海戰為主題的策略軍事遊戲。 故事背景設定在2064年，全球海平面上升後，世界重組為三大海上陣營。 玩家將扮演艦隊指揮官，建設基地、研發武器、打造艦隊，並在三大陣營中爭奪海上霸權。
+總體而言，《超級海戰：紀元崛起》是一款玩法豐富，畫面精美的未來海戰策略遊戲，值得玩家期待。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超級海戰：紀元崛起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VENOM99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPECTRE20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CJHZKF666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入主畫面後點左上角人頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中間偏左"兌換"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入兌換碼/禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰艦建造令*10+鑽石*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5分鐘加速*6+中型鋼材捆*3+大型發電機*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鋼鐵*100K+電力*100K+5分鐘加速*6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰艦建造令*10+鋼材購買券*10+中級艦長訓練手冊*10+鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進擊的惡魔團</t>
+  </si>
+  <si>
+    <t>開遊戲進入主畫面後</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右上角的齒輪設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按下登陸優惠券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛複製好的兌換碼/禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"進擊的惡魔團"
+裡面的惡魔角色頗可愛，月卡黨要打到後面的關卡也沒有很難
+閒著沒事可以點個廣告來看拿獎勵，可以拿到不錯的獎勵，不過我懶得等30秒就很少看。
+遊戲內容就是組自己的惡魔團小隊打關卡升級，畢竟遊戲本體就叫進擊的惡魔團，每一關大概10-15秒很適合拉屎或上班摸魚玩。
+每隻惡魔都有自己的特色和技能，有的很會打、有的很會補，還有一些特別的輔助惡魔，讓你玩起來很有挑戰性，怎麼搭配惡魔組成惡魔團才是關鍵。
+不管是挑戰關卡、PVP對戰，還是限時活動，本身是個非常喜新厭舊的人，進擊的惡魔團目前我是還沒玩膩。
+進擊的惡魔團絕對是一款值得你試試看的免費手遊，一起上班摸魚玩進擊的惡魔團！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hrdbboney</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金角瘦骨</t>
+  </si>
+  <si>
+    <t>hellsquadopen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250紅寶+5000金幣+5成長藥水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thanks0715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>store1st</t>
+  </si>
+  <si>
+    <t>appleon1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10K金幣+5隨機惡魔徽章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200紅寶+10K金幣+5成長藥水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20K金幣+20能量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RO：Crush</t>
+  </si>
+  <si>
+    <t>蝕影：緋之契</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《蝕影：緋之契》平安時代，京都曾是御神者與鬼怪共存的平衡之地。百年後，一場神秘的「月蝕祭典」撕裂了陰陽兩岸的結界，玉藻前殘魂蘇醒，策劃'血月嫁儀'欲染指現世。玩家將化身「末裔御神者」，手持符咒踏入混沌，收服百鬼，揭開「狐嫁女」與「孟婆」的滅世陰謀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Ragnarok Crush》有別於以往 RO 常見的 MMORPG 玩法，本作主打休閒策略，遊戲中保留了 RO 經典的職業元素以及養成玩法，在挑戰關卡的過程中，玩家可以透過移動遊戲中的棋子完成合成，並且召喚出高階夥伴，連續合成還可以獲得額外步數，透過合成以及關卡中升級所獲得的隨機能力，挑戰在一波一波的魔物攻勢中生存下來。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OP888888</t>
+  </si>
+  <si>
+    <t>上市典禮專屬獎勵，包含 SSR 卡、抽卡券</t>
+  </si>
+  <si>
+    <t>預約特典，包含內部福利（如經驗加成、道具）</t>
+  </si>
+  <si>
+    <t>同SVIP666多平台序號，領取獎勵相同</t>
+  </si>
+  <si>
+    <t>預約更高階特典，可獲得額外福利</t>
+  </si>
+  <si>
+    <t>遊戲畫面左上角頭像點進去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在設定裡面找到激活碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上兌換碼按領取就可以囉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRUSH777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20鑽石+200奧丁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中間下方的兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溯回青空</t>
+  </si>
+  <si>
+    <t>蒼之啟示錄</t>
+  </si>
+  <si>
+    <t>第六絕區</t>
+  </si>
+  <si>
+    <t>幻世三國：一騎當千</t>
+  </si>
+  <si>
+    <t>經典日系x末日魔王x卡牌RPG《溯回青空》
+這是你與生俱來的使命——統率不老不死的少年少女騎士團，化身「魔王」對抗眾神
+在眾神與人類爭奪星球霸權的亂世中，人類在第八度瀕臨滅絕後開啟了「第九軌道人類史」。
+此刻，眾神再次啟動「軌道修正計畫」，企圖將人類存在徹底抹除於歷史長河。
+而你，將率領前八大軌道的騎士團，對抗眾神，奪回青空。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《蒼之啟示錄》以架空大陸魔王蘇醒為背景，玩家扮演「神選者」，透過收集聖器、挑戰副本來阻止魔族入侵，融合了PVE/PVP雙線戰鬥與開放世界探索機制。遊戲採用二次元畫風與日韓幻想美術風格，建構涵蓋九大區域的里斯特大陸。核心玩法包含自動掛網戰鬥、自由交易系統和英靈變身戰鬥，設有三大職業轉職體系及天啟之書成長指引。社交模塊整合了聖團協作、伴侶締結與跨服溫泉等互動玩法，結合馴龍作戰、釣魚種花等休閒內容，形成獨特的「佛系冒險」特色。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未來世界因名為「米洛斯」的能源核心失控陷入危機，倖存者退守至最後的防線 —— 第六絕區。
+作為指揮官，你將帶領小隊探索被異變的其它絕區：自動化戰鬥解放雙手，離線也能積累資源；自由搭配未來槍械、戰術裝備與變異戰寵，組建專屬戰鬥流派。在廢墟中搜尋強化物資，抵禦變異生物侵襲，逐步揭開「米洛斯」爆發的真相。
+末世已至，點擊開啟你的「放置割草 + 策略生存」之旅！　</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我們非常高興你能來體驗《mo.co》。我們的團隊致力於打造一款融合輕度RPG元素的多人動作遊戲，希望能讓它簡單好上手、社交互動豐富，且充滿活力。
+從想體驗碎片化MMO或ARPG遊戲的資深玩家，到從未感受過這類遊戲樂趣的新玩家，我們希望打造一款能讓每個人都可以沉浸其中的遊戲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃魂再啟，三國新紀元，邀你共赴熱血激戰！
+在《幻世三國：一騎當千》的世界裡，歷史與幻想交織，經典英雄與全新設定碰撞出令人熱血沸騰的冒險！這是一款融合了動作連招、策略養成與社交互動的三國ARPG手遊。
+時空的縫隙撕裂了三國大地，神秘力量令群雄異化，昔日的英雄化身全新戰神，東漢末年的烽煙中夾雜著神明的低語與科技的嘶鳴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100石 稱號秘密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEIKAIHAGAMEDECHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXRMIZUGI2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100石 稱號blade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうさんにちきねんび</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入下方連結兌換</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rxr.happyelements.co.jp/campaign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AK79513 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約禮包 + 2025抽卡機會</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS34567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏日補給虛寶空投</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲後點左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主角畫面中按"兌換碼"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兌換完成後到信箱領取禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小兵立大功</t>
+  </si>
+  <si>
+    <t>像素全明星</t>
+  </si>
+  <si>
+    <t>MO.CO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浣熊傳說</t>
+  </si>
+  <si>
+    <t>勇者格鬥城</t>
+  </si>
+  <si>
+    <t>即時高智商對戰！獨創五行制衡戰術！
+過百種浣熊英雄！每張都是藝術品！
+全球PVP競技場！用策略證明誰是浣熊之王！
+無門檻終極狂歡！首發限定SSR免費領！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《勇者格鬥城》橫版動作手遊震撼來襲！六大職業任選，暢爽連招對決BOSS。挑戰深淵副本贏稀有裝備，PVP競技場展現操作實力。無論是冒險獨行俠還是競技達人，都能找到專屬戰鬥樂趣！即刻加入，體驗極致打擊快感，爭奪最強勇者稱號！
+【六大獨特職業】
+任你選擇，專屬技能與戰鬥風格帶來截然不同的體驗！挑戰多層次副本，從普通地下城到深淵Boss，海量關卡，驚喜不斷！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip999</t>
+  </si>
+  <si>
+    <t>點擊主界面坐上頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上即可兌換成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">vip888 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄經驗*50000+金幣*50000+鑽石*200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*100000+一元大鈔*3+鑽石*400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*70000+一元大鈔*2+鑽石*300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*50000+一元大鈔*1+鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星耀球會</t>
+  </si>
+  <si>
+    <t>背上小小背包出發世界旅行的白熊, 龐寶。偶然遇見的寶箱怪低著聲說「從你身上感受到勇士的氣息。」
+一直沉睡的魔像“領路者”醒了過來,龐寶則和36位夥伴一起向著新大陸前進。而那個地方有著可怕的魔王“藍波”在等著。
+“現在, 是時候由背著背包的命運勇士 - 龐寶照亮前方的路了。”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cutieggg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bnsc2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soccerclub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點擊左上方隊徽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在禮品碼後點擊「輸入」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈窗中輸入禮包碼即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameplayhk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龐寶：背包英雄們</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《星耀球會》一款由球隊名、隊徽、主場風格任你設計的手遊，玩家將同時化身事會主席、球探、經理、甚至教練。你的球會，由你話事!
+遊戲以「球會」為核心，玩家唔止係揀陣式咁簡單。由起訓練設施、規劃財政、球員買賣、隊伍發展，到球場設計都由你話事。你係球會掌舵人，完全掌控整個球會並自己心目中的理想！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>東方幻想ECLIPSE</t>
+  </si>
+  <si>
+    <t>weLvkwt4JkEf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★4 想起卡「褪去自我風格」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲首頁，點選右上角「選單」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇右側的「序號碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入序號後，即可領取到對應獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a3aayerPNUHk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈願券*10+藥膳茶*3+復活仙果*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*300+體力包*10+士氣包*10+醫療包*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*2M+金幣*200+士氣包*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資金*1M+初級球探*200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初級球探*200+士氣包*30+醫療包*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世紀帝國M</t>
+  </si>
+  <si>
+    <t>歐啦!守得豬</t>
+  </si>
+  <si>
+    <t>點選左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設定後按禮包碼兌換</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製好的禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETW723</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*500+5分鐘建築加速*15+5分鐘研發加速*15+5分鐘訓練加速*15+1萬安全資源箱*25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右邊三條線選單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設置進去點禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的禮包碼按確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ724</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLSDZ999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18櫻花幕府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOK924</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DUALOS7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被遺忘之人匯聚的樂園——幻想鄉。 人類與妖怪在這片寧靜之地共存，歲月靜好，彷彿永恆不變…… 然而，突如其來的「它們」，打破了這份安寧。 前所未見的異質存在，如暗潮般悄然蔓延，將整個幻想鄉捲入前所未有的混亂。 生活在這片土地上的「她們」，懷抱著各自的信念與使命，踏上了行動的旅途。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰姬的魅力，從不只在戰場！每位乙女皆擁有隱藏立繪與進階服裝，隨著升星、親密互動、羈絆突破逐步解鎖---從威武戰甲到柔情私服，從冷豔武將到嬌羞美人。這場亂世，不只是爭霸，更是攻略每一顆芳心。
+《18櫻花幕府》與盟友並肩奪城，成為一國之主！
+加入家族，參與大型跨服城戰。運籌帷幄，調度戰姬，佔領據點、掠奪資源，證明你才是真正的幕府霸主。兄弟齊心，其利斷金，稱霸戰國等你來挑戰！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*10+金扭蛋幣*10+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+體力*20+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+初級鎧甲圖紙+初級王冠圖紙+初級聖杯圖紙*4+初級面具圖紙*3+初級聖劍圖紙*1+金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*88.8K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWAWAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEM888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWHAGENG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWKUANGBAOXIAOJIAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWNL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWHUALUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWCHIGUIBOBO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWGUIGOU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEMOBILETWWAYNE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOVEAOEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEMGL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYJULY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOEMTWEMULATOR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳說現世招募券*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝國幣*N+隨機資源加速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進去之後畫面中間偏右下禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>織田信秀姬魂*100+3級經驗書*10+判金*500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判金*888+神樂鈴*10+銅錢*88888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《世紀帝國M》引入玩家熟悉的八大文明(中式、羅馬式、法蘭克式、拜占庭式、埃及式、不列顛式、日式及韓式)、傭兵系統，以及經典的資源採集和分配機制，玩家需要合理安排村民進行採礦、捕魚、打獵、採樹莓…等，收集、累積、分配資源用於發展帝國；此外，《世紀帝國》經典的音樂音效、宏偉逼真的攻城器械也將在遊戲中出現，玩家不僅能使用到豐富的策略，更能被喚起有關《世紀帝國》的美好回憶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>誰說英雄一定要帥？《歐啦！守得豬》的英雄角色可謂是「跨次元」的明星大集合！我們汲取了大量流行元素，巧妙地將其與各種動物形象融合，打造出個性十足、醜萌兼具的天團戰隊。每一位英雄都身懷絕技，每一次召喚都可能帶來意外的驚喜與強大的戰力。各種趣味屬性、羈絆配搭，讓策略變得既豐富又有趣，誰說塔防一定嚴肅？來點萌萌鬼畜，笑著守住你的家園！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大武道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中央貼上兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按兌換就可以囉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giKuBa</t>
+  </si>
+  <si>
+    <t>穿書先鋒補給</t>
+  </si>
+  <si>
+    <t>FTFiRo</t>
+  </si>
+  <si>
+    <t>先行修練補給包</t>
+  </si>
+  <si>
+    <t>QCKhLg</t>
+  </si>
+  <si>
+    <t>yABTEh</t>
+  </si>
+  <si>
+    <t>nHTgib</t>
+  </si>
+  <si>
+    <t>GmzUMo</t>
+  </si>
+  <si>
+    <t>waWrHF</t>
+  </si>
+  <si>
+    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
+遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6Z3QVNZNC9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V768FCD2MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YZEFPZUYP3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QWDZBKJZ8E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+潛能點掛機券*5+探寶令*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+功法殘頁*10+技能點掛機券*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精力*30+探寶令*5+淬體精華掛機券*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功法殘頁*10+探寶令*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canonical_url</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5663,6 +6742,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>極速漂移：3V3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《小兵立大功》率領召喚師、英雄和小兵擊潰敵軍 打造專屬軍團 充滿打擊感 展開史詩級戰爭。
+從召喚師、英雄、小兵升級中做出選擇，在如同殭屍般移動的敵人圍毆中存活下來！體驗充滿緊張刺激的類Rogue RPG！
+體驗直觀操作及充滿打擊感的休閒系動作手遊！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>像素全明星陣容，熱門經典人物大亂鬥
+遊戲採用經典的點數風格，帶給玩家濃厚的懷舊感。 每個角色、場景和技能效果都呈現出極具創意和魅力的點數藝術，讓你在回憶經典的同時，享受全新的遊戲體驗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">MICHAN </t>
     </r>
@@ -5678,1221 +6772,12 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>美男惡徒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《美男惡徒－暗夜中綻放的邪惡之戀》 「CROWN」是由維多利亞女王欽命成立的秘密組織。所有的成員都是擁有「童話詛咒」的男子，而這些詛咒賦予他們特殊的力量。他們以「以惡制惡」的方式，執行暗殺等任務，維護國家的穩定。
-　　原為郵差的妳，因意外得知 CROWN 的秘密而被迫成為「童話師」，負責記錄成員們的詛咒故事。在一個月內除了要與所有成員一起同住外，還需要記錄所有成員的故事，期間不得與任何人墜入愛河，否則將面臨死亡的命運。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>突破5,000人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>轉蛋券 ×3、雞尾酒套餐（體力+100）×1、經典編織低髻髮型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>突破10,000人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>轉蛋券 ×3、鑽石 ×200、玫瑰模樣的維多利亞風黑色洋裝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>突破30,000人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>轉蛋券 ×4、鑽石 ×300、雞尾酒套餐（體力+100）×2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>突破50,000人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保證★4角色的【標準角色卡轉蛋券】×1！、鑽石x1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三國冰河時代</t>
-  </si>
-  <si>
-    <t>暗黑崛起</t>
-  </si>
-  <si>
-    <t>轉生魔劍士養成：策略放置RPG</t>
-  </si>
-  <si>
-    <t>輕鬆系三國冰雪模擬經營遊戲《三國冰河時代》今日再度公開全新重點與核心玩法特色，進一步展現「不肝也能玩」的輕鬆體驗，準備這個夏季來一場” 冰的” 三國演習。兩位人氣武將「孫尚香」與「張飛」也同步現身，將以全新造型與技能設計加入各位主公的隊伍。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【純正暗黑體驗，探索祕境之戰】戰法職業流派與豐富的職業內容同步釋出！與來自深海的邪惡勢力對抗，守護結界殘存的能量，成為統禦賽季最強的英雄！
-【暢快連擊無限割草，享受廝殺的快感】雙搖桿操作，無體力限制想戰就戰，面對不斷襲擊的敵人，使用各式各樣的技能爽快連擊、無限割草，Hack and Slash，簡單操作隨時暢玩，Speedrun考驗操作技術，回歸遊戲最純粹的樂趣。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>「死亡不是終點復仇才正要開始。」
-魔劍士亞莉亞在與魔王決戰前夕遭到摯友們的背叛而喪命。
-然而她在死亡邊緣重獲新生回到了過去還是新手劍士的時代。
-帶著未來的記憶亞莉亞展開了第二次復仇與成長的旅程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ice666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ice777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ice888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ice999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icewar666</t>
-  </si>
-  <si>
-    <t>icewar777</t>
-  </si>
-  <si>
-    <t>icewar888</t>
-  </si>
-  <si>
-    <t>icewar999</t>
-  </si>
-  <si>
-    <t>FBVALUE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>極速漂移：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3V3</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《極速漂移:3v3》與全球玩家組隊競速、漂移，暢享速度激情。 《極速漂移:3v3》與許多世界頂尖車商合作，讓你能夠駕駛知名品牌的正版豪華車。 炫技般地做出令人驚嘆的漂移，在多樣且逼真的賽道上展開激烈的3v3 對戰，還能與全球玩家組隊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斗羅大陸：獵魂世界</t>
-  </si>
-  <si>
-    <t>指點兵兵</t>
-  </si>
-  <si>
-    <t>《斗羅大陸：獵魂世界》作為首款基於頂尖國漫 IP《斗羅大陸》打造的開放世界 RPG，細膩還原魂獸、魂環、魂骨等核心設定，無論是施展酷炫魂技的燃魂激鬥，還是與夥伴組隊獵殺強大魂獸，都將為玩家帶來最真實的斗羅冒險。
-　　官方今日重磅釋出「斗羅時空」終極代言影片，影片中，終極一班原班人馬傾情演繹，從現實校園跨入斗羅大世界的時空，完美詮釋了遊戲「突破界限、勇敢冒險」的核心精神，點燃所有粉絲玩家的戰鬥熱血！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">《指點兵兵》這是一款以三國歷史為背景的塔防類策略遊戲。生於亂世，為了維護世間太平，玩家需要不斷招兵買馬，透過合理的資源配置和戰術安排，建造城池，排兵布陣，抵禦敵人的進攻，最後成為名震一方的主公。
-每局戰鬥共20波敵軍攻勢，透過隨機卡牌強化部隊，打造獨特戰術流派！
-主公將不斷解鎖新型兵種，合適的兵種互相搭配，可獲得獨一無二的聯合技！
-透過招兵買馬，軍師運籌帷幄，武將決勝千里，協助玩家過關斬將！
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP555</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>終極斗羅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>首款斗羅大世界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>獵魂777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃金昊天錘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全民獵魂瓜分百萬現金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斗羅大陸獵魂世界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>真斗羅真開放</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魂師回歸禮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MMO666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MMO777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MMO888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>變身傳奇</t>
-  </si>
-  <si>
-    <t>Blue eyes：公會大師</t>
-  </si>
-  <si>
-    <t>《變身傳奇》是一款掛機角色扮演遊戲，玩家在遊戲中扮演被神選中的勇者，獲得變身力量，在奇幻世界中冒險，並不斷進化成傳奇英雄。 遊戲主打輕鬆的掛機體驗，即使離線也能持續成長，並提供豐富的社交和pvp元素。  化身為傳說中的英雄，體驗更強大的力量與華麗的戰鬥。 透過冒險與戰鬥成長，在競爭中勝出，奪取無可匹敵的地位！ 放置型動作RPG的真正樂趣無論何時何地都能輕鬆培養角色。 即使你暫時離線，英雄也會持續成長，當你回來時，將展開一場刺激的戰鬥並獲得豐富的獎勵！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>『地球、武林界、符文大地、艾爾弗拉多、魯坎……無數個世界被「高塔」所選中。
-被選中的世界【玩家】，可登上高塔，不斷變強。
-他們為了登上更高的殿堂，創立了【公會】。
-所以說【Blue Eyes】，
-這個如今成為傳說的公會名稱，是所有公會大師的夢想與目標。』</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即將更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BEGLOBALOPEN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dead Spirit Box (Non-Enhanceable) x1
-Common Element x50
-Common Soul Fragment x200
-Summon Stone Fragment x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入主畫面，點選右上角四個點</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入右下設定（齒輪）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊添加優惠券</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先點擊CS code右邊的複製</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點添加優惠券貼上Cscode跟禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杖劍傳說：坎斯汀之約</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《杖劍傳說》是一款異世界休閒冒險放置RPG。
-在這裡，你將作為冒險者，自由探索坎斯汀世界的每一個角落。
-在這裡撥開地圖迷霧，尋得掉落在各地的珍稀寶物，體驗輕鬆爽快的
-異世界之旅吧。
-當然，在旅途的過程中，你還會邂逅各式各樣夥伴，與他們並肩作
-戰，共同挑戰神秘的聖獸。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊帳號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入主畫面後點右下角小方塊圖案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SS666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SS777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金葉子*3+鳶尾*5+暖陽*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>時之沙*300+石塊*100+粗煉石300+歷戰精華1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SS999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>土雞蛋*3+普通凍乾*5+結緣繩*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJ666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>豐饒之葉*100+命運果實*1+體力*25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJ777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>晨星*200+星之願*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJ888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傳說女神牌*2+史詩女神牌*10+稀有女神牌*20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJ999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>糖果小人*2+蜜汁烤肉*3+青草糰子*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SSFB888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>稀有女神牌*10+星之願*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SSDC888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SSLINE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">《超級海戰：紀元崛起》是一款以未來海戰為主題的策略軍事遊戲。 故事背景設定在2064年，全球海平面上升後，世界重組為三大海上陣營。 玩家將扮演艦隊指揮官，建設基地、研發武器、打造艦隊，並在三大陣營中爭奪海上霸權。
-總體而言，《超級海戰：紀元崛起》是一款玩法豐富，畫面精美的未來海戰策略遊戲，值得玩家期待。 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超級海戰：紀元崛起</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VENOM99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SPECTRE20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CJHZKF666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入主畫面後點左上角人頭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>畫面中間偏左"兌換"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入兌換碼/禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>戰艦建造令*10+鑽石*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5分鐘加速*6+中型鋼材捆*3+大型發電機*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鋼鐵*100K+電力*100K+5分鐘加速*6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>戰艦建造令*10+鋼材購買券*10+中級艦長訓練手冊*10+鑽石*100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進擊的惡魔團</t>
-  </si>
-  <si>
-    <t>開遊戲進入主畫面後</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>右上角的齒輪設定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按下登陸優惠券</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上剛複製好的兌換碼/禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"進擊的惡魔團"
-裡面的惡魔角色頗可愛，月卡黨要打到後面的關卡也沒有很難
-閒著沒事可以點個廣告來看拿獎勵，可以拿到不錯的獎勵，不過我懶得等30秒就很少看。
-遊戲內容就是組自己的惡魔團小隊打關卡升級，畢竟遊戲本體就叫進擊的惡魔團，每一關大概10-15秒很適合拉屎或上班摸魚玩。
-每隻惡魔都有自己的特色和技能，有的很會打、有的很會補，還有一些特別的輔助惡魔，讓你玩起來很有挑戰性，怎麼搭配惡魔組成惡魔團才是關鍵。
-不管是挑戰關卡、PVP對戰，還是限時活動，本身是個非常喜新厭舊的人，進擊的惡魔團目前我是還沒玩膩。
-進擊的惡魔團絕對是一款值得你試試看的免費手遊，一起上班摸魚玩進擊的惡魔團！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hrdbboney</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金角瘦骨</t>
-  </si>
-  <si>
-    <t>hellsquadopen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250紅寶+5000金幣+5成長藥水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thanks0715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>store1st</t>
-  </si>
-  <si>
-    <t>appleon1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10K金幣+5隨機惡魔徽章</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200紅寶+10K金幣+5成長藥水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20K金幣+20能量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RO：Crush</t>
-  </si>
-  <si>
-    <t>蝕影：緋之契</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《蝕影：緋之契》平安時代，京都曾是御神者與鬼怪共存的平衡之地。百年後，一場神秘的「月蝕祭典」撕裂了陰陽兩岸的結界，玉藻前殘魂蘇醒，策劃'血月嫁儀'欲染指現世。玩家將化身「末裔御神者」，手持符咒踏入混沌，收服百鬼，揭開「狐嫁女」與「孟婆」的滅世陰謀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《Ragnarok Crush》有別於以往 RO 常見的 MMORPG 玩法，本作主打休閒策略，遊戲中保留了 RO 經典的職業元素以及養成玩法，在挑戰關卡的過程中，玩家可以透過移動遊戲中的棋子完成合成，並且召喚出高階夥伴，連續合成還可以獲得額外步數，透過合成以及關卡中升級所獲得的隨機能力，挑戰在一波一波的魔物攻勢中生存下來。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OP888888</t>
-  </si>
-  <si>
-    <t>上市典禮專屬獎勵，包含 SSR 卡、抽卡券</t>
-  </si>
-  <si>
-    <t>預約特典，包含內部福利（如經驗加成、道具）</t>
-  </si>
-  <si>
-    <t>同SVIP666多平台序號，領取獎勵相同</t>
-  </si>
-  <si>
-    <t>預約更高階特典，可獲得額外福利</t>
-  </si>
-  <si>
-    <t>遊戲畫面左上角頭像點進去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在設定裡面找到激活碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上兌換碼按領取就可以囉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CRUSH777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20鑽石+200奧丁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>畫面中間下方的兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上剛剛複製的兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>溯回青空</t>
-  </si>
-  <si>
-    <t>蒼之啟示錄</t>
-  </si>
-  <si>
-    <t>第六絕區</t>
-  </si>
-  <si>
-    <t>幻世三國：一騎當千</t>
-  </si>
-  <si>
-    <t>經典日系x末日魔王x卡牌RPG《溯回青空》
-這是你與生俱來的使命——統率不老不死的少年少女騎士團，化身「魔王」對抗眾神
-在眾神與人類爭奪星球霸權的亂世中，人類在第八度瀕臨滅絕後開啟了「第九軌道人類史」。
-此刻，眾神再次啟動「軌道修正計畫」，企圖將人類存在徹底抹除於歷史長河。
-而你，將率領前八大軌道的騎士團，對抗眾神，奪回青空。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《蒼之啟示錄》以架空大陸魔王蘇醒為背景，玩家扮演「神選者」，透過收集聖器、挑戰副本來阻止魔族入侵，融合了PVE/PVP雙線戰鬥與開放世界探索機制。遊戲採用二次元畫風與日韓幻想美術風格，建構涵蓋九大區域的里斯特大陸。核心玩法包含自動掛網戰鬥、自由交易系統和英靈變身戰鬥，設有三大職業轉職體系及天啟之書成長指引。社交模塊整合了聖團協作、伴侶締結與跨服溫泉等互動玩法，結合馴龍作戰、釣魚種花等休閒內容，形成獨特的「佛系冒險」特色。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未來世界因名為「米洛斯」的能源核心失控陷入危機，倖存者退守至最後的防線 —— 第六絕區。
-作為指揮官，你將帶領小隊探索被異變的其它絕區：自動化戰鬥解放雙手，離線也能積累資源；自由搭配未來槍械、戰術裝備與變異戰寵，組建專屬戰鬥流派。在廢墟中搜尋強化物資，抵禦變異生物侵襲，逐步揭開「米洛斯」爆發的真相。
-末世已至，點擊開啟你的「放置割草 + 策略生存」之旅！　</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我們非常高興你能來體驗《mo.co》。我們的團隊致力於打造一款融合輕度RPG元素的多人動作遊戲，希望能讓它簡單好上手、社交互動豐富，且充滿活力。
-從想體驗碎片化MMO或ARPG遊戲的資深玩家，到從未感受過這類遊戲樂趣的新玩家，我們希望打造一款能讓每個人都可以沉浸其中的遊戲。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃魂再啟，三國新紀元，邀你共赴熱血激戰！
-在《幻世三國：一騎當千》的世界裡，歷史與幻想交織，經典英雄與全新設定碰撞出令人熱血沸騰的冒險！這是一款融合了動作連招、策略養成與社交互動的三國ARPG手遊。
-時空的縫隙撕裂了三國大地，神秘力量令群雄異化，昔日的英雄化身全新戰神，東漢末年的烽煙中夾雜著神明的低語與科技的嘶鳴。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100石 稱號秘密</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEIKAIHAGAMEDECHECK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RXRMIZUGI2024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100石 稱號blade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>じゅうさんにちきねんび</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>130石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入下方連結兌換</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rxr.happyelements.co.jp/campaign</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">AK79513 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>預約禮包 + 2025抽卡機會</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AS34567</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏日補給虛寶空投</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入遊戲後點左上角頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主角畫面中按"兌換碼"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上剛剛複製的兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兌換完成後到信箱領取禮包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小兵立大功</t>
-  </si>
-  <si>
-    <t>像素全明星</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>《小兵立大功》率領召喚師、英雄和小兵擊潰敵軍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>打造專屬軍團</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>充滿打擊感</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>展開史詩級戰爭。
-從召喚師、英雄、小兵升級中做出選擇，在如同殭屍般移動的敵人圍毆中存活下來！體驗充滿緊張刺激的類</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Rogue RPG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>！
-體驗直觀操作及充滿打擊感的休閒系動作手遊！</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>像素全明星陣容，熱門經典人物大亂鬥
-遊戲採用經典的點數風格，帶給玩家濃厚的懷舊感。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>每個角色、場景和技能效果都呈現出極具創意和魅力的點數藝術，讓你在回憶經典的同時，享受全新的遊戲體驗。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MO.CO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浣熊傳說</t>
-  </si>
-  <si>
-    <t>勇者格鬥城</t>
-  </si>
-  <si>
-    <t>即時高智商對戰！獨創五行制衡戰術！
-過百種浣熊英雄！每張都是藝術品！
-全球PVP競技場！用策略證明誰是浣熊之王！
-無門檻終極狂歡！首發限定SSR免費領！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《勇者格鬥城》橫版動作手遊震撼來襲！六大職業任選，暢爽連招對決BOSS。挑戰深淵副本贏稀有裝備，PVP競技場展現操作實力。無論是冒險獨行俠還是競技達人，都能找到專屬戰鬥樂趣！即刻加入，體驗極致打擊快感，爭奪最強勇者稱號！
-【六大獨特職業】
-任你選擇，專屬技能與戰鬥風格帶來截然不同的體驗！挑戰多層次副本，從普通地下城到深淵Boss，海量關卡，驚喜不斷！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vip999</t>
-  </si>
-  <si>
-    <t>點擊主界面坐上頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上即可兌換成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">vip888 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vip777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vip666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄經驗*50000+金幣*50000+鑽石*200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*100000+一元大鈔*3+鑽石*400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*70000+一元大鈔*2+鑽石*300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*50000+一元大鈔*1+鑽石*100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星耀球會</t>
-  </si>
-  <si>
-    <t>背上小小背包出發世界旅行的白熊, 龐寶。偶然遇見的寶箱怪低著聲說「從你身上感受到勇士的氣息。」
-一直沉睡的魔像“領路者”醒了過來,龐寶則和36位夥伴一起向著新大陸前進。而那個地方有著可怕的魔王“藍波”在等著。
-“現在, 是時候由背著背包的命運勇士 - 龐寶照亮前方的路了。”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cutieggg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bnsc2025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>soccerclub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲內點擊左上方隊徽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在禮品碼後點擊「輸入」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彈窗中輸入禮包碼即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gameplayhk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龐寶：背包英雄們</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《星耀球會》一款由球隊名、隊徽、主場風格任你設計的手遊，玩家將同時化身事會主席、球探、經理、甚至教練。你的球會，由你話事!
-遊戲以「球會」為核心，玩家唔止係揀陣式咁簡單。由起訓練設施、規劃財政、球員買賣、隊伍發展，到球場設計都由你話事。你係球會掌舵人，完全掌控整個球會並自己心目中的理想！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>東方幻想ECLIPSE</t>
-  </si>
-  <si>
-    <t>weLvkwt4JkEf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>★4 想起卡「褪去自我風格」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入遊戲首頁，點選右上角「選單」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>選擇右側的「序號碼」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入序號後，即可領取到對應獎勵。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a3aayerPNUHk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>祈願券*10+藥膳茶*3+復活仙果*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*300+體力包*10+士氣包*10+醫療包*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資金*2M+金幣*200+士氣包*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資金*1M+初級球探*200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初級球探*200+士氣包*30+醫療包*30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>世紀帝國M</t>
-  </si>
-  <si>
-    <t>歐啦!守得豬</t>
-  </si>
-  <si>
-    <t>點選左上角頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入設定後按禮包碼兌換</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上剛剛複製好的禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETW723</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帝國幣*500+5分鐘建築加速*15+5分鐘研發加速*15+5分鐘訓練加速*15+1萬安全資源箱*25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>畫面右邊三條線選單</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>設置進去點禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上剛剛複製的禮包碼按確認</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OLSDZ724</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OLSDZ888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OLSDZ999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18櫻花幕府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOOK924</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DUALOS7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被遺忘之人匯聚的樂園——幻想鄉。 人類與妖怪在這片寧靜之地共存，歲月靜好，彷彿永恆不變…… 然而，突如其來的「它們」，打破了這份安寧。 前所未見的異質存在，如暗潮般悄然蔓延，將整個幻想鄉捲入前所未有的混亂。 生活在這片土地上的「她們」，懷抱著各自的信念與使命，踏上了行動的旅途。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>戰姬的魅力，從不只在戰場！每位乙女皆擁有隱藏立繪與進階服裝，隨著升星、親密互動、羈絆突破逐步解鎖---從威武戰甲到柔情私服，從冷豔武將到嬌羞美人。這場亂世，不只是爭霸，更是攻略每一顆芳心。
-《18櫻花幕府》與盟友並肩奪城，成為一國之主！
-加入家族，參與大型跨服城戰。運籌帷幄，調度戰姬，佔領據點、掠奪資源，證明你才是真正的幕府霸主。兄弟齊心，其利斷金，稱霸戰國等你來挑戰！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>體力*10+金扭蛋幣*10+金幣*88.8K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*100+體力*20+金幣*88.8K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*100+初級鎧甲圖紙+初級王冠圖紙+初級聖杯圖紙*4+初級面具圖紙*3+初級聖劍圖紙*1+金幣*88.8K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*88.8K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>體力*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWAWAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOEM888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWHAGENG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWKUANGBAOXIAOJIAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWNL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWHUALUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWCHIGUIBOBO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWGUIGOU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGEMOBILETWWAYNE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOVEAOEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOEMGL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HAPPYJULY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOEMTWEMULATOR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傳說現世招募券*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 帝國幣*200、5分鐘建造/研發*5、1萬安全資源寶箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帝國幣*N+隨機資源加速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲主畫面左上角頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進去之後畫面中間偏右下禮包碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>織田信秀姬魂*100+3級經驗書*10+判金*500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判金*888+神樂鈴*10+銅錢*88888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《世紀帝國M》引入玩家熟悉的八大文明(中式、羅馬式、法蘭克式、拜占庭式、埃及式、不列顛式、日式及韓式)、傭兵系統，以及經典的資源採集和分配機制，玩家需要合理安排村民進行採礦、捕魚、打獵、採樹莓…等，收集、累積、分配資源用於發展帝國；此外，《世紀帝國》經典的音樂音效、宏偉逼真的攻城器械也將在遊戲中出現，玩家不僅能使用到豐富的策略，更能被喚起有關《世紀帝國》的美好回憶。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>誰說英雄一定要帥？《歐啦！守得豬》的英雄角色可謂是「跨次元」的明星大集合！我們汲取了大量流行元素，巧妙地將其與各種動物形象融合，打造出個性十足、醜萌兼具的天團戰隊。每一位英雄都身懷絕技，每一次召喚都可能帶來意外的驚喜與強大的戰力。各種趣味屬性、羈絆配搭，讓策略變得既豐富又有趣，誰說塔防一定嚴肅？來點萌萌鬼畜，笑著守住你的家園！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大武道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲主畫面左上角頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>畫面中央貼上兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按兌換就可以囉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>giKuBa</t>
-  </si>
-  <si>
-    <t>穿書先鋒補給</t>
-  </si>
-  <si>
-    <t>FTFiRo</t>
-  </si>
-  <si>
-    <t>先行修練補給包</t>
-  </si>
-  <si>
-    <t>QCKhLg</t>
-  </si>
-  <si>
-    <t>yABTEh</t>
-  </si>
-  <si>
-    <t>nHTgib</t>
-  </si>
-  <si>
-    <t>GmzUMo</t>
-  </si>
-  <si>
-    <t>waWrHF</t>
-  </si>
-  <si>
-    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
-遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6Z3QVNZNC9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>V768FCD2MD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YZEFPZUYP3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QWDZBKJZ8E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精力*30+潛能點掛機券*5+探寶令*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精力*30+功法殘頁*10+技能點掛機券*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精力*30+探寶令*5+淬體精華掛機券*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功法殘頁*10+探寶令*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6935,65 +6820,6 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFF1F1F1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF9900"/>
-      <name val="Inherit"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF9900"/>
-      <name val="Inherit"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF993300"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Inherit"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -7002,61 +6828,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <u/>
       <sz val="14"/>
-      <color rgb="FFE2E5E9"/>
-      <name val="Segoe UI Historic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000080"/>
-      <name val="Inherit"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Inherit"/>
-      <family val="2"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE5CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A1A1A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFCFC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -7127,9 +6912,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7154,55 +6939,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -7510,18 +7264,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW654"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5"/>
+  <dimension ref="A1:AX654"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
     <col min="2" max="3" width="37.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="79.140625" style="2" customWidth="1"/>
     <col min="5" max="9" width="18.28515625" style="2" customWidth="1"/>
     <col min="10" max="34" width="12.140625" style="2" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="2"/>
+    <col min="35" max="49" width="9" style="2"/>
+    <col min="50" max="50" width="16.5703125" style="2" customWidth="1"/>
+    <col min="51" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7669,8 +7425,11 @@
       <c r="AW1" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="AX1" s="2" t="s">
+        <v>1807</v>
+      </c>
     </row>
-    <row r="2" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="2" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>107</v>
       </c>
@@ -7804,8 +7563,12 @@
       <c r="AU2" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX2" s="2" t="str">
+        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A2</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=巔峰極速</v>
+      </c>
     </row>
-    <row r="3" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="3" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>108</v>
       </c>
@@ -7849,8 +7612,12 @@
       <c r="Q3" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="AX3" s="2" t="str">
+        <f t="shared" ref="AX3:AX66" si="1">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A3</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=原神</v>
+      </c>
     </row>
-    <row r="4" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="4" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
@@ -7891,8 +7658,12 @@
       <c r="Q4" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=極速快感</v>
+      </c>
     </row>
-    <row r="5" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="5" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>110</v>
       </c>
@@ -7990,8 +7761,12 @@
       <c r="AI5" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=俠客傳說：小小英雄</v>
+      </c>
     </row>
-    <row r="6" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="6" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>111</v>
       </c>
@@ -8017,8 +7792,12 @@
       <c r="K6" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="AX6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=逆水寒</v>
+      </c>
     </row>
-    <row r="7" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="7" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>112</v>
       </c>
@@ -8080,8 +7859,12 @@
       <c r="W7" s="2" t="s">
         <v>222</v>
       </c>
+      <c r="AX7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：一定要可愛</v>
+      </c>
     </row>
-    <row r="8" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="8" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>113</v>
       </c>
@@ -8137,8 +7920,12 @@
       <c r="U8" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO新世代</v>
+      </c>
     </row>
-    <row r="9" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="9" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>114</v>
       </c>
@@ -8230,8 +8017,12 @@
       <c r="AG9" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=上古：龍神覺醒</v>
+      </c>
     </row>
-    <row r="10" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="10" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>115</v>
       </c>
@@ -8299,8 +8090,12 @@
       <c r="Y10" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小艦艦超勇</v>
+      </c>
     </row>
-    <row r="11" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="11" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>116</v>
       </c>
@@ -8338,8 +8133,12 @@
       <c r="O11" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=天使軍團</v>
+      </c>
     </row>
-    <row r="12" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="12" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>117</v>
       </c>
@@ -8371,8 +8170,12 @@
       <c r="M12" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=天堂W</v>
+      </c>
     </row>
-    <row r="13" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="13" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>118</v>
       </c>
@@ -8440,8 +8243,12 @@
       <c r="Y13" s="2" t="s">
         <v>261</v>
       </c>
+      <c r="AX13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=少女前線2：追放</v>
+      </c>
     </row>
-    <row r="14" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="14" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>119</v>
       </c>
@@ -8533,8 +8340,12 @@
       <c r="AG14" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=幻獸傳說Ｍ</v>
+      </c>
     </row>
-    <row r="15" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="15" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>120</v>
       </c>
@@ -8584,8 +8395,12 @@
       <c r="S15" s="2" t="s">
         <v>280</v>
       </c>
+      <c r="AX15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=未定事件簿</v>
+      </c>
     </row>
-    <row r="16" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="16" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>121</v>
       </c>
@@ -8611,8 +8426,12 @@
       <c r="K16" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="AX16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=永恆靈魂</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="17" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>122</v>
       </c>
@@ -8674,8 +8493,12 @@
       <c r="W17" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=守住呀主公</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>123</v>
       </c>
@@ -8719,8 +8542,12 @@
       <c r="Q18" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=吟遊戰記</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="19" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>124</v>
       </c>
@@ -8788,8 +8615,12 @@
       <c r="Y19" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=我獨自升級：ARISE</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="20" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>125</v>
       </c>
@@ -8875,8 +8706,12 @@
       <c r="AE20" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=命運聖契：少女的羈絆</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="21" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>126</v>
       </c>
@@ -8926,8 +8761,12 @@
       <c r="S21" s="2" t="s">
         <v>422</v>
       </c>
+      <c r="AX21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=放置軍團</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="22" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>127</v>
       </c>
@@ -8953,8 +8792,12 @@
       <c r="K22" s="2" t="s">
         <v>424</v>
       </c>
+      <c r="AX22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=明日方舟</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="23" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>128</v>
       </c>
@@ -9034,8 +8877,12 @@
       <c r="AC23" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=屍鬼三國</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="24" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -9091,8 +8938,12 @@
       <c r="U24" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="AX24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星鏈計畫：未來少女</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="25" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>130</v>
       </c>
@@ -9166,8 +9017,12 @@
       <c r="AA25" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄之王</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="26" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>131</v>
       </c>
@@ -9196,8 +9051,12 @@
       <c r="M26" s="2" t="s">
         <v>458</v>
       </c>
+      <c r="AX26" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄聯盟</v>
+      </c>
     </row>
-    <row r="27" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="27" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>132</v>
       </c>
@@ -9217,8 +9076,12 @@
       <c r="G27" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="AX27" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=恐龍突變</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="28" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>133</v>
       </c>
@@ -9250,8 +9113,12 @@
       <c r="M28" s="2" t="s">
         <v>462</v>
       </c>
+      <c r="AX28" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=神域</v>
+      </c>
     </row>
-    <row r="29" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="29" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>134</v>
       </c>
@@ -9277,8 +9144,12 @@
       <c r="K29" s="2" t="s">
         <v>464</v>
       </c>
+      <c r="AX29" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=崩壞：星穹鐵道</v>
+      </c>
     </row>
-    <row r="30" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="30" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>135</v>
       </c>
@@ -9346,8 +9217,12 @@
       <c r="Y30" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX30" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=救世者之樹：新世界</v>
+      </c>
     </row>
-    <row r="31" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="31" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>136</v>
       </c>
@@ -9385,8 +9260,12 @@
       <c r="O31" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX31" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=球球英雄</v>
+      </c>
     </row>
-    <row r="32" spans="1:31" ht="19.899999999999999" customHeight="1">
+    <row r="32" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>137</v>
       </c>
@@ -9412,8 +9291,12 @@
       <c r="K32" s="2" t="s">
         <v>480</v>
       </c>
+      <c r="AX32" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=第七史詩</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="33" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>138</v>
       </c>
@@ -9499,8 +9382,12 @@
       <c r="AE33" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX33" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=創世紀戰M：阿修羅計畫</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="34" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>139</v>
       </c>
@@ -9592,8 +9479,12 @@
       <c r="AG34" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX34" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=最強宗師</v>
+      </c>
     </row>
-    <row r="35" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="35" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>140</v>
       </c>
@@ -9637,8 +9528,12 @@
       <c r="Q35" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX35" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=無期迷途</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="36" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>141</v>
       </c>
@@ -9700,8 +9595,12 @@
       <c r="W36" s="2" t="s">
         <v>520</v>
       </c>
+      <c r="AX36" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=絕區零</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="37" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>142</v>
       </c>
@@ -9733,8 +9632,12 @@
       <c r="M37" s="2" t="s">
         <v>524</v>
       </c>
+      <c r="AX37" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=傳說對決</v>
+      </c>
     </row>
-    <row r="38" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="38" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>336</v>
       </c>
@@ -9778,8 +9681,12 @@
       <c r="Q38" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX38" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=楓之谷M</v>
+      </c>
     </row>
-    <row r="39" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="39" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>143</v>
       </c>
@@ -9823,8 +9730,12 @@
       <c r="Q39" s="2" t="s">
         <v>538</v>
       </c>
+      <c r="AX39" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=鳴潮</v>
+      </c>
     </row>
-    <row r="40" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="40" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>144</v>
       </c>
@@ -9874,8 +9785,12 @@
       <c r="S40" s="2" t="s">
         <v>548</v>
       </c>
+      <c r="AX40" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=劍與遠征：啟程</v>
+      </c>
     </row>
-    <row r="41" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="41" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>145</v>
       </c>
@@ -9937,8 +9852,12 @@
       <c r="W41" s="2" t="s">
         <v>561</v>
       </c>
+      <c r="AX41" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=熱血大作戰</v>
+      </c>
     </row>
-    <row r="42" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="42" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>146</v>
       </c>
@@ -10036,8 +9955,12 @@
       <c r="AI42" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX42" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=骷髏傳說：戰神崛起</v>
+      </c>
     </row>
-    <row r="43" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="43" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>147</v>
       </c>
@@ -10135,8 +10058,12 @@
       <c r="AI43" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX43" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=黎明：血色魔女</v>
+      </c>
     </row>
-    <row r="44" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="44" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>148</v>
       </c>
@@ -10210,8 +10137,12 @@
       <c r="AA44" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX44" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=黎明啟示錄</v>
+      </c>
     </row>
-    <row r="45" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="45" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>149</v>
       </c>
@@ -10309,8 +10240,12 @@
       <c r="AI45" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX45" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=龍魂旅人</v>
+      </c>
     </row>
-    <row r="46" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="46" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>150</v>
       </c>
@@ -10426,8 +10361,12 @@
       <c r="AO46" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX46" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=戀與深空</v>
+      </c>
     </row>
-    <row r="47" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="47" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>151</v>
       </c>
@@ -10477,8 +10416,12 @@
       <c r="S47" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX47" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=靈魂衝擊：無限放置</v>
+      </c>
     </row>
-    <row r="48" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="48" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>152</v>
       </c>
@@ -10558,8 +10501,12 @@
       <c r="AC48" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX48" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=楓葉島</v>
+      </c>
     </row>
-    <row r="49" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="49" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>153</v>
       </c>
@@ -10603,8 +10550,12 @@
       <c r="Q49" s="2" t="s">
         <v>635</v>
       </c>
+      <c r="AX49" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=無名江湖</v>
+      </c>
     </row>
-    <row r="50" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="50" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>154</v>
       </c>
@@ -10672,8 +10623,12 @@
       <c r="Y50" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX50" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=萬妖領域</v>
+      </c>
     </row>
-    <row r="51" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="51" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>155</v>
       </c>
@@ -10717,8 +10672,12 @@
       <c r="Q51" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX51" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=一姬當千TD</v>
+      </c>
     </row>
-    <row r="52" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="52" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>156</v>
       </c>
@@ -10750,8 +10709,12 @@
       <c r="M52" s="2" t="s">
         <v>647</v>
       </c>
+      <c r="AX52" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=劍客行</v>
+      </c>
     </row>
-    <row r="53" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="53" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>157</v>
       </c>
@@ -10795,8 +10758,12 @@
       <c r="Q53" s="2" t="s">
         <v>656</v>
       </c>
+      <c r="AX53" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=時之樹少女</v>
+      </c>
     </row>
-    <row r="54" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="54" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>158</v>
       </c>
@@ -10924,8 +10891,12 @@
       <c r="AS54" s="4" t="s">
         <v>671</v>
       </c>
+      <c r="AX54" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=錨點降臨Re：Code</v>
+      </c>
     </row>
-    <row r="55" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="55" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>159</v>
       </c>
@@ -11041,8 +11012,12 @@
       <c r="AO55" s="4" t="s">
         <v>704</v>
       </c>
+      <c r="AX55" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=神契氣靈師</v>
+      </c>
     </row>
-    <row r="56" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="56" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>160</v>
       </c>
@@ -11118,8 +11093,12 @@
       <c r="AC56" s="4" t="s">
         <v>713</v>
       </c>
+      <c r="AX56" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=不休旅途：繪卷世界</v>
+      </c>
     </row>
-    <row r="57" spans="1:49" ht="34.5" customHeight="1">
+    <row r="57" spans="1:50" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>161</v>
       </c>
@@ -11211,8 +11190,12 @@
       <c r="AG57" s="9" t="s">
         <v>729</v>
       </c>
+      <c r="AX57" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=別破防鴨</v>
+      </c>
     </row>
-    <row r="58" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="58" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>162</v>
       </c>
@@ -11250,8 +11233,12 @@
       <c r="O58" s="9" t="s">
         <v>736</v>
       </c>
+      <c r="AX58" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=超派救星幫幫忙</v>
+      </c>
     </row>
-    <row r="59" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="59" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>163</v>
       </c>
@@ -11325,8 +11312,12 @@
       <c r="AA59" s="2" t="s">
         <v>758</v>
       </c>
+      <c r="AX59" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=時光大爆炸</v>
+      </c>
     </row>
-    <row r="60" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="60" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>164</v>
       </c>
@@ -11424,8 +11415,12 @@
       <c r="AI60" s="4" t="s">
         <v>755</v>
       </c>
+      <c r="AX60" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=深淵：不滅者</v>
+      </c>
     </row>
-    <row r="61" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="61" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>52</v>
       </c>
@@ -11451,8 +11446,12 @@
       <c r="K61" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX61" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Last War</v>
+      </c>
     </row>
-    <row r="62" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="62" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>165</v>
       </c>
@@ -11562,8 +11561,12 @@
       <c r="AM62" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX62" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=勇士不要停</v>
+      </c>
     </row>
-    <row r="63" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="63" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>166</v>
       </c>
@@ -11703,8 +11706,12 @@
       <c r="AW63" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX63" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=元氣火柴人</v>
+      </c>
     </row>
-    <row r="64" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="64" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>167</v>
       </c>
@@ -11736,8 +11743,12 @@
       <c r="M64" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX64" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=深淵之影</v>
+      </c>
     </row>
-    <row r="65" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="65" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>168</v>
       </c>
@@ -11793,8 +11804,12 @@
       <c r="U65" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX65" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=玩星派對</v>
+      </c>
     </row>
-    <row r="66" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="66" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>169</v>
       </c>
@@ -11850,13 +11865,17 @@
       <c r="U66" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX66" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=進化吧!我的人生</v>
+      </c>
     </row>
-    <row r="67" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="67" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B67" s="2" t="str">
-        <f t="shared" ref="B67:B125" si="1">"giftcodesbanner/" &amp; A67 &amp; "-bar.jpg"</f>
+        <f t="shared" ref="B67:B125" si="2">"giftcodesbanner/" &amp; A67 &amp; "-bar.jpg"</f>
         <v>giftcodesbanner/星之夢幻島-bar.jpg</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -11913,13 +11932,17 @@
       <c r="W67" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX67" s="2" t="str">
+        <f t="shared" ref="AX67:AX130" si="3">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A67</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星之夢幻島</v>
+      </c>
     </row>
-    <row r="68" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="68" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B68" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/小冰冰傳奇：回到最初-bar.jpg</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -11988,13 +12011,17 @@
       <c r="AA68" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX68" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小冰冰傳奇：回到最初</v>
+      </c>
     </row>
-    <row r="69" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="69" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>172</v>
       </c>
       <c r="B69" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/江湖風雲傳-bar.jpg</v>
       </c>
       <c r="D69" s="2" t="s">
@@ -12027,13 +12054,17 @@
       <c r="O69" s="2" t="s">
         <v>831</v>
       </c>
+      <c r="AX69" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=江湖風雲傳</v>
+      </c>
     </row>
-    <row r="70" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="70" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>173</v>
       </c>
       <c r="B70" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/星願之冠：狼少女物語-bar.jpg</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -12066,13 +12097,17 @@
       <c r="O70" s="2" t="s">
         <v>837</v>
       </c>
+      <c r="AX70" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星願之冠：狼少女物語</v>
+      </c>
     </row>
-    <row r="71" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="71" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>174</v>
       </c>
       <c r="B71" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/香蕉缺個芭樂-bar.jpg</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -12195,13 +12230,17 @@
       <c r="AS71" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX71" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=香蕉缺個芭樂</v>
+      </c>
     </row>
-    <row r="72" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="72" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>175</v>
       </c>
       <c r="B72" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/精靈塔塔開-bar.jpg</v>
       </c>
       <c r="D72" s="2" t="s">
@@ -12222,13 +12261,17 @@
       <c r="K72" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX72" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=精靈塔塔開</v>
+      </c>
     </row>
-    <row r="73" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="73" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B73" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/終末之歌-bar.jpg</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -12261,13 +12304,17 @@
       <c r="O73" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX73" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=終末之歌</v>
+      </c>
     </row>
-    <row r="74" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="74" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>177</v>
       </c>
       <c r="B74" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/森靈奇境-bar.jpg</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -12348,13 +12395,17 @@
       <c r="AE74" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX74" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=森靈奇境</v>
+      </c>
     </row>
-    <row r="75" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="75" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B75" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/鬥破蒼穹：蕭門篇-bar.jpg</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -12435,13 +12486,17 @@
       <c r="AE75" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX75" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=鬥破蒼穹：蕭門篇</v>
+      </c>
     </row>
-    <row r="76" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="76" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>179</v>
       </c>
       <c r="B76" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/無畏的狼煙-bar.jpg</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -12474,13 +12529,17 @@
       <c r="O76" s="2" t="s">
         <v>899</v>
       </c>
+      <c r="AX76" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=無畏的狼煙</v>
+      </c>
     </row>
-    <row r="77" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="77" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>180</v>
       </c>
       <c r="B77" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/代號：無頭-bar.jpg</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -12543,13 +12602,17 @@
       <c r="Y77" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX77" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=代號：無頭</v>
+      </c>
     </row>
-    <row r="78" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="78" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>181</v>
       </c>
       <c r="B78" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/牛頭人GO-bar.jpg</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -12612,13 +12675,17 @@
       <c r="Y78" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX78" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=牛頭人GO</v>
+      </c>
     </row>
-    <row r="79" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="79" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B79" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/派對吧三國-bar.jpg</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -12693,13 +12760,17 @@
       <c r="AC79" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX79" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=派對吧三國</v>
+      </c>
     </row>
-    <row r="80" spans="1:45" ht="19.899999999999999" customHeight="1">
+    <row r="80" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>183</v>
       </c>
       <c r="B80" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/酒酒大俠-bar.jpg</v>
       </c>
       <c r="D80" s="2" t="s">
@@ -12756,13 +12827,17 @@
       <c r="W80" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX80" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=酒酒大俠</v>
+      </c>
     </row>
-    <row r="81" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="81" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>184</v>
       </c>
       <c r="B81" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/鼠衛家園-bar.jpg</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -12807,13 +12882,17 @@
       <c r="S81" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX81" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=鼠衛家園</v>
+      </c>
     </row>
-    <row r="82" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="82" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>185</v>
       </c>
       <c r="B82" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/未頌者之歌：異世界冒險奇譚-bar.jpg</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -12867,13 +12946,17 @@
       <c r="W82" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX82" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=未頌者之歌：異世界冒險奇譚</v>
+      </c>
     </row>
-    <row r="83" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="83" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B83" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/熱練戰士-bar.jpg</v>
       </c>
       <c r="D83" s="2" t="s">
@@ -12924,13 +13007,17 @@
       <c r="U83" s="2" t="s">
         <v>957</v>
       </c>
+      <c r="AX83" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=熱練戰士</v>
+      </c>
     </row>
-    <row r="84" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="84" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>187</v>
       </c>
       <c r="B84" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/聯盟戰棋-bar.jpg</v>
       </c>
       <c r="D84" s="2" t="s">
@@ -12966,13 +13053,17 @@
       <c r="W84" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX84" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=聯盟戰棋</v>
+      </c>
     </row>
-    <row r="85" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="85" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>188</v>
       </c>
       <c r="B85" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/劍客物語-bar.jpg</v>
       </c>
       <c r="D85" s="2" t="s">
@@ -13041,13 +13132,17 @@
       <c r="AA85" s="2" t="s">
         <v>976</v>
       </c>
+      <c r="AX85" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=劍客物語</v>
+      </c>
     </row>
-    <row r="86" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="86" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>189</v>
       </c>
       <c r="B86" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/人在塔在-bar.jpg</v>
       </c>
       <c r="D86" s="2" t="s">
@@ -13074,13 +13169,17 @@
       <c r="M86" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX86" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=人在塔在</v>
+      </c>
     </row>
-    <row r="87" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="87" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>190</v>
       </c>
       <c r="B87" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/龍語霜城-bar.jpg</v>
       </c>
       <c r="D87" s="2" t="s">
@@ -13173,13 +13272,17 @@
       <c r="AI87" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX87" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=龍語霜城</v>
+      </c>
     </row>
-    <row r="88" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="88" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>191</v>
       </c>
       <c r="B88" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/洛伊的移動要塞-bar.jpg</v>
       </c>
       <c r="D88" s="2" t="s">
@@ -13242,13 +13345,17 @@
       <c r="Y88" s="2" t="s">
         <v>1006</v>
       </c>
+      <c r="AX88" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=洛伊的移動要塞</v>
+      </c>
     </row>
-    <row r="89" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="89" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>192</v>
       </c>
       <c r="B89" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/喵喵王國-bar.jpg</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -13269,13 +13376,17 @@
       <c r="K89" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX89" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=喵喵王國</v>
+      </c>
     </row>
-    <row r="90" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="90" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>193</v>
       </c>
       <c r="B90" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/東京謎影者-bar.jpg</v>
       </c>
       <c r="D90" s="2" t="s">
@@ -13311,13 +13422,17 @@
       <c r="W90" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX90" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=東京謎影者</v>
+      </c>
     </row>
-    <row r="91" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="91" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>194</v>
       </c>
       <c r="B91" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/戰極死遊-bar.jpg</v>
       </c>
       <c r="D91" s="2" t="s">
@@ -13350,13 +13465,17 @@
       <c r="O91" s="2" t="s">
         <v>1009</v>
       </c>
+      <c r="AX91" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=戰極死遊</v>
+      </c>
     </row>
-    <row r="92" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="92" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>195</v>
       </c>
       <c r="B92" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/進擊的蝸牛-bar.jpg</v>
       </c>
       <c r="D92" s="2" t="s">
@@ -13467,13 +13586,17 @@
       <c r="AO92" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX92" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=進擊的蝸牛</v>
+      </c>
     </row>
-    <row r="93" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="93" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>196</v>
       </c>
       <c r="B93" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/純白大作戰-bar.jpg</v>
       </c>
       <c r="D93" s="2" t="s">
@@ -13527,13 +13650,17 @@
       <c r="W93" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX93" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=純白大作戰</v>
+      </c>
     </row>
-    <row r="94" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="94" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>197</v>
       </c>
       <c r="B94" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/黑星勇者-bar.jpg</v>
       </c>
       <c r="D94" s="2" t="s">
@@ -13560,13 +13687,17 @@
       <c r="M94" s="2" t="s">
         <v>1040</v>
       </c>
+      <c r="AX94" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=黑星勇者</v>
+      </c>
     </row>
-    <row r="95" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="95" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>198</v>
       </c>
       <c r="B95" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/龍之谷：經典再現-bar.jpg</v>
       </c>
       <c r="D95" s="2" t="s">
@@ -13617,13 +13748,17 @@
       <c r="W95" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX95" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=龍之谷：經典再現</v>
+      </c>
     </row>
-    <row r="96" spans="1:41" ht="19.899999999999999" customHeight="1">
+    <row r="96" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>199</v>
       </c>
       <c r="B96" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/楓之谷Artale-bar.jpg</v>
       </c>
       <c r="D96" s="2" t="s">
@@ -13659,13 +13794,17 @@
       <c r="W96" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX96" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=楓之谷Artale</v>
+      </c>
     </row>
-    <row r="97" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="97" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>200</v>
       </c>
       <c r="B97" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/出發吧麥芬-bar.jpg</v>
       </c>
       <c r="D97" s="2" t="s">
@@ -13686,13 +13825,17 @@
       <c r="K97" s="2" t="s">
         <v>1048</v>
       </c>
+      <c r="AX97" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=出發吧麥芬</v>
+      </c>
     </row>
-    <row r="98" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="98" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>201</v>
       </c>
       <c r="B98" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/RO仙境傳說：守護永恆的愛 Classic-bar.jpg</v>
       </c>
       <c r="D98" s="2" t="s">
@@ -13821,13 +13964,17 @@
       <c r="AU98" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX98" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：守護永恆的愛 Classic</v>
+      </c>
     </row>
-    <row r="99" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="99" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>202</v>
       </c>
       <c r="B99" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/魔力寶貝：復興-bar.jpg</v>
       </c>
       <c r="D99" s="2" t="s">
@@ -13890,13 +14037,17 @@
       <c r="Y99" s="2" t="s">
         <v>1082</v>
       </c>
+      <c r="AX99" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魔力寶貝：復興</v>
+      </c>
     </row>
-    <row r="100" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="100" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>203</v>
       </c>
       <c r="B100" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/東京喰種Awakening-bar.jpg</v>
       </c>
       <c r="D100" s="2" t="s">
@@ -13989,13 +14140,17 @@
       <c r="AI100" s="2" t="s">
         <v>1108</v>
       </c>
+      <c r="AX100" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=東京喰種Awakening</v>
+      </c>
     </row>
-    <row r="101" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="101" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>204</v>
       </c>
       <c r="B101" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/晶核-bar.jpg</v>
       </c>
       <c r="D101" s="2" t="s">
@@ -14076,13 +14231,17 @@
       <c r="AE101" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX101" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=晶核</v>
+      </c>
     </row>
-    <row r="102" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="102" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>205</v>
       </c>
       <c r="B102" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/無盡夢迴-bar.jpg</v>
       </c>
       <c r="D102" s="2" t="s">
@@ -14133,13 +14292,17 @@
       <c r="U102" s="2" t="s">
         <v>1131</v>
       </c>
+      <c r="AX102" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=無盡夢迴</v>
+      </c>
     </row>
-    <row r="103" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="103" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>206</v>
       </c>
       <c r="B103" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/RO仙境傳說：放推冒險團-bar.jpg</v>
       </c>
       <c r="D103" s="2" t="s">
@@ -14202,13 +14365,17 @@
       <c r="Y103" s="2" t="s">
         <v>1147</v>
       </c>
+      <c r="AX103" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：放推冒險團</v>
+      </c>
     </row>
-    <row r="104" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="104" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B104" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/英雄刷刷刷-bar.jpg</v>
       </c>
       <c r="D104" s="2" t="s">
@@ -14304,13 +14471,17 @@
       <c r="AV104" s="2" t="s">
         <v>1167</v>
       </c>
+      <c r="AX104" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄刷刷刷</v>
+      </c>
     </row>
-    <row r="105" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="105" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>208</v>
       </c>
       <c r="B105" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/萬靈物語-bar.jpg</v>
       </c>
       <c r="D105" s="2" t="s">
@@ -14406,13 +14577,17 @@
       <c r="AV105" s="2" t="s">
         <v>1185</v>
       </c>
+      <c r="AX105" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=萬靈物語</v>
+      </c>
     </row>
-    <row r="106" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="106" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>209</v>
       </c>
       <c r="B106" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/斗羅大陸：逆轉時空-bar.jpg</v>
       </c>
       <c r="D106" s="2" t="s">
@@ -14481,13 +14656,17 @@
       <c r="AD106" s="2" t="s">
         <v>1195</v>
       </c>
+      <c r="AX106" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=斗羅大陸：逆轉時空</v>
+      </c>
     </row>
-    <row r="107" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="107" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>210</v>
       </c>
       <c r="B107" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/魔靈召喚：保衛戰-bar.jpg</v>
       </c>
       <c r="D107" s="2" t="s">
@@ -14502,13 +14681,17 @@
       <c r="G107" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="AX107" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魔靈召喚：保衛戰</v>
+      </c>
     </row>
-    <row r="108" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="108" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>211</v>
       </c>
       <c r="B108" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/潘多蘭島-bar.jpg</v>
       </c>
       <c r="D108" s="2" t="s">
@@ -14529,17 +14712,21 @@
       <c r="K108" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX108" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=潘多蘭島</v>
+      </c>
     </row>
-    <row r="109" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="109" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>212</v>
       </c>
       <c r="B109" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/電鋸果汁大亂鬥-bar.jpg</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1540</v>
+        <v>1808</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>20</v>
@@ -14556,13 +14743,17 @@
       <c r="K109" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX109" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=電鋸果汁大亂鬥</v>
+      </c>
     </row>
-    <row r="110" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="110" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>213</v>
       </c>
       <c r="B110" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/風色幻想NeXus-bar.jpg</v>
       </c>
       <c r="D110" s="2" t="s">
@@ -14595,13 +14786,17 @@
       <c r="O110" s="2" t="s">
         <v>1203</v>
       </c>
+      <c r="AX110" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=風色幻想NeXus</v>
+      </c>
     </row>
-    <row r="111" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="111" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>214</v>
       </c>
       <c r="B111" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/星河訣愛-bar.jpg</v>
       </c>
       <c r="D111" s="2" t="s">
@@ -14664,13 +14859,17 @@
       <c r="Y111" s="2" t="s">
         <v>1219</v>
       </c>
+      <c r="AX111" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星河訣愛</v>
+      </c>
     </row>
-    <row r="112" spans="1:48" ht="19.899999999999999" customHeight="1">
+    <row r="112" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>1221</v>
       </c>
       <c r="B112" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/kingshot-bar.jpg</v>
       </c>
       <c r="D112" s="2" t="s">
@@ -14715,13 +14914,17 @@
       <c r="S112" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX112" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=kingshot</v>
+      </c>
     </row>
-    <row r="113" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="113" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>1222</v>
       </c>
       <c r="B113" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/胡鬧地牢-bar.jpg</v>
       </c>
       <c r="D113" s="2" t="s">
@@ -14808,13 +15011,17 @@
       <c r="AG113" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX113" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=胡鬧地牢</v>
+      </c>
     </row>
-    <row r="114" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="114" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>1223</v>
       </c>
       <c r="B114" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/小小軍團-重生-bar.jpg</v>
       </c>
       <c r="D114" s="2" t="s">
@@ -14907,13 +15114,17 @@
       <c r="AI114" s="2" t="s">
         <v>1256</v>
       </c>
+      <c r="AX114" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小小軍團-重生</v>
+      </c>
     </row>
-    <row r="115" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="115" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>1267</v>
       </c>
       <c r="B115" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/爪爪遠征-bar.jpg</v>
       </c>
       <c r="D115" s="2" t="s">
@@ -14934,13 +15145,17 @@
       <c r="K115" s="2" t="s">
         <v>1290</v>
       </c>
+      <c r="AX115" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=爪爪遠征</v>
+      </c>
     </row>
-    <row r="116" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="116" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>1268</v>
       </c>
       <c r="B116" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/勇士團團轉-bar.jpg</v>
       </c>
       <c r="D116" s="2" t="s">
@@ -14961,13 +15176,17 @@
       <c r="K116" s="2" t="s">
         <v>1290</v>
       </c>
+      <c r="AX116" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=勇士團團轉</v>
+      </c>
     </row>
-    <row r="117" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="117" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>1269</v>
       </c>
       <c r="B117" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/魁 三國志大戰-bar.jpg</v>
       </c>
       <c r="D117" s="2" t="s">
@@ -14994,13 +15213,17 @@
       <c r="M117" s="2" t="s">
         <v>1280</v>
       </c>
+      <c r="AX117" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魁 三國志大戰</v>
+      </c>
     </row>
-    <row r="118" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="118" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>1270</v>
       </c>
       <c r="B118" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/tokyo beast-bar.jpg</v>
       </c>
       <c r="D118" s="2" t="s">
@@ -15021,13 +15244,17 @@
       <c r="K118" s="2" t="s">
         <v>1290</v>
       </c>
+      <c r="AX118" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=tokyo beast</v>
+      </c>
     </row>
-    <row r="119" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="119" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>1271</v>
       </c>
       <c r="B119" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/切換英雄：放置型RPG-bar.jpg</v>
       </c>
       <c r="D119" s="8" t="s">
@@ -15084,13 +15311,17 @@
       <c r="W119" s="9" t="s">
         <v>1288</v>
       </c>
+      <c r="AX119" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=切換英雄：放置型RPG</v>
+      </c>
     </row>
-    <row r="120" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="120" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>1294</v>
       </c>
       <c r="B120" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/小死神傳奇-bar.jpg</v>
       </c>
       <c r="D120" s="2" t="s">
@@ -15111,13 +15342,17 @@
       <c r="K120" s="2" t="s">
         <v>1290</v>
       </c>
+      <c r="AX120" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小死神傳奇</v>
+      </c>
     </row>
-    <row r="121" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="121" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>1295</v>
       </c>
       <c r="B121" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/闇影詩章：凌越世界-bar.jpg</v>
       </c>
       <c r="D121" s="8" t="s">
@@ -15138,13 +15373,17 @@
       <c r="K121" s="2" t="s">
         <v>1290</v>
       </c>
+      <c r="AX121" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=闇影詩章：凌越世界</v>
+      </c>
     </row>
-    <row r="122" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="122" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>1298</v>
       </c>
       <c r="B122" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/雪月風花-bar.jpg</v>
       </c>
       <c r="D122" s="2" t="s">
@@ -15249,13 +15488,17 @@
       <c r="AM122" s="9" t="s">
         <v>1331</v>
       </c>
+      <c r="AX122" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=雪月風花</v>
+      </c>
     </row>
-    <row r="123" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="123" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>1299</v>
       </c>
       <c r="B123" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/文明帝國：同盟時代-bar.jpg</v>
       </c>
       <c r="D123" s="2" t="s">
@@ -15282,13 +15525,17 @@
       <c r="M123" s="3" t="s">
         <v>1335</v>
       </c>
+      <c r="AX123" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=文明帝國：同盟時代</v>
+      </c>
     </row>
-    <row r="124" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="124" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>1300</v>
       </c>
       <c r="B124" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/魔法商店大亨-bar.jpg</v>
       </c>
       <c r="D124" s="2" t="s">
@@ -15345,13 +15592,17 @@
       <c r="W124" s="2" t="s">
         <v>1349</v>
       </c>
+      <c r="AX124" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魔法商店大亨</v>
+      </c>
     </row>
-    <row r="125" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="125" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>1301</v>
       </c>
       <c r="B125" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>giftcodesbanner/新仙劍奇俠傳lite-bar.jpg</v>
       </c>
       <c r="D125" s="2" t="s">
@@ -15486,8 +15737,12 @@
       <c r="AW125" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX125" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=新仙劍奇俠傳lite</v>
+      </c>
     </row>
-    <row r="126" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="126" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>1302</v>
       </c>
@@ -15519,8 +15774,12 @@
       <c r="M126" s="2" t="s">
         <v>1366</v>
       </c>
+      <c r="AX126" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=神州M</v>
+      </c>
     </row>
-    <row r="127" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="127" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>1367</v>
       </c>
@@ -15618,13 +15877,17 @@
       <c r="AI127" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX127" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄傳說：卡卡布三部曲</v>
+      </c>
     </row>
-    <row r="128" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="128" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>1382</v>
       </c>
       <c r="B128" s="2" t="str">
-        <f t="shared" ref="B128:B134" si="2">"giftcodesbanner/" &amp; A128 &amp; "-bar.jpg"</f>
+        <f t="shared" ref="B128:B134" si="4">"giftcodesbanner/" &amp; A128 &amp; "-bar.jpg"</f>
         <v>giftcodesbanner/胡來英雄-bar.jpg</v>
       </c>
       <c r="D128" s="8" t="s">
@@ -15675,13 +15938,17 @@
       <c r="U128" s="2" t="s">
         <v>1397</v>
       </c>
+      <c r="AX128" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=胡來英雄</v>
+      </c>
     </row>
-    <row r="129" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="129" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>1383</v>
       </c>
       <c r="B129" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/一天又一天的RPG-bar.jpg</v>
       </c>
       <c r="D129" s="2" t="s">
@@ -15732,13 +15999,17 @@
       <c r="U129" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX129" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=一天又一天的RPG</v>
+      </c>
     </row>
-    <row r="130" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="130" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>1384</v>
       </c>
       <c r="B130" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/銀與血-bar.jpg</v>
       </c>
       <c r="D130" s="2" t="s">
@@ -15789,13 +16060,17 @@
       <c r="U130" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX130" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=銀與血</v>
+      </c>
     </row>
-    <row r="131" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="131" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>1385</v>
       </c>
       <c r="B131" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/緋石之心-bar.jpg</v>
       </c>
       <c r="D131" s="2" t="s">
@@ -15822,13 +16097,17 @@
       <c r="M131" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX131" s="2" t="str">
+        <f t="shared" ref="AX131:AX172" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=緋石之心</v>
+      </c>
     </row>
-    <row r="132" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="132" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>1416</v>
       </c>
       <c r="B132" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/滔湧少女-bar.jpg</v>
       </c>
       <c r="D132" s="2" t="s">
@@ -15867,13 +16146,17 @@
       <c r="Q132" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX132" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=滔湧少女</v>
+      </c>
     </row>
-    <row r="133" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="133" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>1417</v>
       </c>
       <c r="B133" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/漫威祕法狂潮-bar.jpg</v>
       </c>
       <c r="D133" s="2" t="s">
@@ -15894,13 +16177,17 @@
       <c r="K133" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX133" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=漫威祕法狂潮</v>
+      </c>
     </row>
-    <row r="134" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="134" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>1418</v>
       </c>
       <c r="B134" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/魔教回歸：2D MMORPG-bar.jpg</v>
       </c>
       <c r="D134" s="8" t="s">
@@ -15933,8 +16220,12 @@
       <c r="O134" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX134" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魔教回歸：2D MMORPG</v>
+      </c>
     </row>
-    <row r="135" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="135" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>1436</v>
       </c>
@@ -16026,13 +16317,17 @@
       <c r="AG135" s="9" t="s">
         <v>1457</v>
       </c>
+      <c r="AX135" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=屍戰王朝</v>
+      </c>
     </row>
-    <row r="136" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="136" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C172" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C172" si="6">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -16048,7 +16343,7 @@
         <v>21</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1541</v>
+        <v>1812</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1458</v>
@@ -16071,13 +16366,17 @@
       <c r="Q136" s="2" t="s">
         <v>1464</v>
       </c>
+      <c r="AX136" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=機甲變變變</v>
+      </c>
     </row>
-    <row r="137" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="137" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>1438</v>
       </c>
       <c r="C137" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/狼少女蘭吉-禮包碼.jpg</v>
       </c>
       <c r="D137" s="5" t="s">
@@ -16104,13 +16403,17 @@
       <c r="M137" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX137" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=狼少女蘭吉</v>
+      </c>
     </row>
-    <row r="138" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="138" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="C138" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/RO仙境傳說：曙光-禮包碼.jpg</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -16203,13 +16506,17 @@
       <c r="AI138" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX138" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：曙光</v>
+      </c>
     </row>
-    <row r="139" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="139" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>1437</v>
       </c>
       <c r="C139" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/星曲Ultra-禮包碼.jpg</v>
       </c>
       <c r="D139" s="5" t="s">
@@ -16236,13 +16543,17 @@
       <c r="M139" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX139" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星曲Ultra</v>
+      </c>
     </row>
-    <row r="140" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="140" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>1479</v>
       </c>
       <c r="C140" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/第七天災-禮包碼.jpg</v>
       </c>
       <c r="D140" s="5" t="s">
@@ -16377,13 +16688,17 @@
       <c r="AW140" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX140" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=第七天災</v>
+      </c>
     </row>
-    <row r="141" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="141" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>1480</v>
       </c>
       <c r="C141" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/百萬神界-禮包碼.jpg</v>
       </c>
       <c r="D141" s="5" t="s">
@@ -16452,13 +16767,17 @@
       <c r="AA141" s="4" t="s">
         <v>1538</v>
       </c>
+      <c r="AX141" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=百萬神界</v>
+      </c>
     </row>
-    <row r="142" spans="1:49" ht="19.899999999999999" customHeight="1">
+    <row r="142" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>1481</v>
       </c>
       <c r="C142" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/Dark war-禮包碼.jpg</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -16485,17 +16804,21 @@
       <c r="M142" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX142" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Dark war</v>
+      </c>
     </row>
-    <row r="143" spans="1:49" ht="19.899999999999999" customHeight="1">
-      <c r="A143" s="10" t="s">
-        <v>1542</v>
+    <row r="143" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="11" t="s">
+        <v>1540</v>
       </c>
       <c r="C143" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/美男惡徒-禮包碼.jpg</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>20</v>
@@ -16507,40 +16830,44 @@
         <v>21</v>
       </c>
       <c r="J143" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L143" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="K143" s="2" t="s">
+      <c r="M143" s="2" t="s">
         <v>1545</v>
       </c>
-      <c r="L143" s="2" t="s">
+      <c r="N143" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="M143" s="2" t="s">
+      <c r="O143" s="2" t="s">
         <v>1547</v>
       </c>
-      <c r="N143" s="2" t="s">
+      <c r="P143" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="O143" s="2" t="s">
+      <c r="Q143" s="2" t="s">
         <v>1549</v>
       </c>
-      <c r="P143" s="2" t="s">
+      <c r="AX143" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=美男惡徒</v>
+      </c>
+    </row>
+    <row r="144" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="13" t="s">
         <v>1550</v>
       </c>
-      <c r="Q143" s="2" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="144" spans="1:49" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A144" s="11" t="s">
-        <v>1552</v>
-      </c>
       <c r="C144" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/三國冰河時代-禮包碼.jpg</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>20</v>
@@ -16552,64 +16879,68 @@
         <v>21</v>
       </c>
       <c r="J144" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="N144" s="2" t="s">
         <v>1558</v>
       </c>
-      <c r="K144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="L144" s="2" t="s">
+      <c r="O144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P144" s="2" t="s">
         <v>1559</v>
       </c>
-      <c r="M144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="N144" s="2" t="s">
+      <c r="Q144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="R144" s="13" t="s">
         <v>1560</v>
       </c>
-      <c r="O144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="P144" s="2" t="s">
+      <c r="S144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="T144" s="13" t="s">
         <v>1561</v>
       </c>
-      <c r="Q144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="R144" s="13" t="s">
+      <c r="U144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V144" s="13" t="s">
         <v>1562</v>
       </c>
-      <c r="S144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="T144" s="13" t="s">
+      <c r="W144" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="X144" s="13" t="s">
         <v>1563</v>
       </c>
-      <c r="U144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="V144" s="13" t="s">
-        <v>1564</v>
-      </c>
-      <c r="W144" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="X144" s="13" t="s">
-        <v>1565</v>
-      </c>
       <c r="Y144" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX144" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=三國冰河時代</v>
+      </c>
     </row>
-    <row r="145" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A145" s="12" t="s">
-        <v>1553</v>
+    <row r="145" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="14" t="s">
+        <v>1551</v>
       </c>
       <c r="C145" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/暗黑崛起-禮包碼.jpg</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>20</v>
@@ -16621,22 +16952,26 @@
         <v>21</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX145" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=暗黑崛起</v>
+      </c>
     </row>
-    <row r="146" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A146" s="12" t="s">
-        <v>1554</v>
+    <row r="146" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="14" t="s">
+        <v>1552</v>
       </c>
       <c r="C146" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/轉生魔劍士養成：策略放置RPG-禮包碼.jpg</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>20</v>
@@ -16659,17 +16994,21 @@
       <c r="M146" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX146" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=轉生魔劍士養成：策略放置RPG</v>
+      </c>
     </row>
-    <row r="147" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A147" s="11" t="s">
-        <v>1567</v>
+    <row r="147" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="13" t="s">
+        <v>1809</v>
       </c>
       <c r="C147" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/極速漂移：3V3-禮包碼.jpg</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>20</v>
@@ -16692,17 +17031,21 @@
       <c r="M147" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX147" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=極速漂移：3V3</v>
+      </c>
     </row>
-    <row r="148" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A148" s="12" t="s">
-        <v>1569</v>
+    <row r="148" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="14" t="s">
+        <v>1566</v>
       </c>
       <c r="C148" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/斗羅大陸：獵魂世界-禮包碼.jpg</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>20</v>
@@ -16714,82 +17057,86 @@
         <v>21</v>
       </c>
       <c r="J148" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P148" s="2" t="s">
         <v>1578</v>
       </c>
-      <c r="K148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="L148" s="2" t="s">
+      <c r="Q148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="R148" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="M148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="N148" s="2" t="s">
+      <c r="S148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="T148" s="2" t="s">
         <v>1580</v>
       </c>
-      <c r="O148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="P148" s="2" t="s">
+      <c r="U148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V148" s="2" t="s">
         <v>1581</v>
       </c>
-      <c r="Q148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="R148" s="2" t="s">
+      <c r="W148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="X148" s="2" t="s">
         <v>1582</v>
       </c>
-      <c r="S148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="T148" s="2" t="s">
+      <c r="Y148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="Z148" s="2" t="s">
         <v>1583</v>
       </c>
-      <c r="U148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="V148" s="2" t="s">
+      <c r="AA148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AB148" s="2" t="s">
         <v>1584</v>
       </c>
-      <c r="W148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="X148" s="2" t="s">
+      <c r="AC148" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AD148" s="2" t="s">
         <v>1585</v>
       </c>
-      <c r="Y148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="Z148" s="2" t="s">
-        <v>1586</v>
-      </c>
-      <c r="AA148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AB148" s="2" t="s">
-        <v>1587</v>
-      </c>
-      <c r="AC148" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AD148" s="2" t="s">
-        <v>1588</v>
-      </c>
       <c r="AE148" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX148" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=斗羅大陸：獵魂世界</v>
+      </c>
     </row>
-    <row r="149" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A149" s="12" t="s">
-        <v>1570</v>
+    <row r="149" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="14" t="s">
+        <v>1567</v>
       </c>
       <c r="C149" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/指點兵兵-禮包碼.jpg</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>20</v>
@@ -16801,46 +17148,50 @@
         <v>21</v>
       </c>
       <c r="J149" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="O149" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P149" s="2" t="s">
         <v>1573</v>
       </c>
-      <c r="K149" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="L149" s="2" t="s">
-        <v>1575</v>
-      </c>
-      <c r="M149" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="N149" s="2" t="s">
+      <c r="Q149" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="R149" s="2" t="s">
         <v>1574</v>
       </c>
-      <c r="O149" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="P149" s="2" t="s">
-        <v>1576</v>
-      </c>
-      <c r="Q149" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="R149" s="2" t="s">
-        <v>1577</v>
-      </c>
       <c r="S149" s="2" t="s">
         <v>1243</v>
       </c>
+      <c r="AX149" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=指點兵兵</v>
+      </c>
     </row>
-    <row r="150" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A150" s="12" t="s">
-        <v>1589</v>
+    <row r="150" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="14" t="s">
+        <v>1586</v>
       </c>
       <c r="C150" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/變身傳奇-禮包碼.jpg</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>20</v>
@@ -16852,503 +17203,551 @@
         <v>21</v>
       </c>
       <c r="J150" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="AX150" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=變身傳奇</v>
+      </c>
+    </row>
+    <row r="151" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="14" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C151" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/Blue eyes：公會大師-禮包碼.jpg</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E151" s="4" t="s">
         <v>1593</v>
       </c>
-      <c r="K150" s="2" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M150" s="2" t="s">
-        <v>1593</v>
+      <c r="F151" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="J151" s="15" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K151" s="15" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L151" s="15"/>
+      <c r="M151" s="15"/>
+      <c r="N151" s="15"/>
+      <c r="O151" s="15"/>
+      <c r="P151" s="15"/>
+      <c r="Q151" s="15"/>
+      <c r="R151" s="15"/>
+      <c r="S151" s="15"/>
+      <c r="T151" s="15"/>
+      <c r="U151" s="15"/>
+      <c r="V151" s="15"/>
+      <c r="W151" s="15"/>
+      <c r="X151" s="15"/>
+      <c r="Y151" s="15"/>
+      <c r="Z151" s="15"/>
+      <c r="AA151" s="15"/>
+      <c r="AX151" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Blue eyes：公會大師</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A151" s="12" t="s">
-        <v>1590</v>
-      </c>
-      <c r="C151" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/Blue eyes：公會大師-禮包碼.jpg</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>1597</v>
-      </c>
-      <c r="G151" s="4" t="s">
+    <row r="152" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="13" t="s">
         <v>1598</v>
       </c>
-      <c r="H151" s="2" t="s">
+      <c r="C152" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/杖劍傳說：坎斯汀之約-禮包碼.jpg</v>
+      </c>
+      <c r="D152" s="8" t="s">
         <v>1599</v>
       </c>
-      <c r="I151" s="2" t="s">
+      <c r="E152" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>1600</v>
       </c>
-      <c r="J151" s="14" t="s">
-        <v>1594</v>
-      </c>
-      <c r="K151" s="15" t="s">
-        <v>1595</v>
-      </c>
-      <c r="L151" s="14"/>
-      <c r="M151" s="15"/>
-      <c r="N151" s="14"/>
-      <c r="O151" s="15"/>
-      <c r="P151" s="14"/>
-      <c r="Q151" s="15"/>
-      <c r="R151" s="14"/>
-      <c r="S151" s="15"/>
-      <c r="T151" s="14"/>
-      <c r="U151" s="15"/>
-      <c r="V151" s="14"/>
-      <c r="W151" s="15"/>
-      <c r="X151" s="14"/>
-      <c r="Y151" s="15"/>
-      <c r="Z151" s="14"/>
-      <c r="AA151" s="15"/>
+      <c r="G152" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="O152" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="P152" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="Q152" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="R152" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="S152" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="T152" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="U152" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="V152" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="W152" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="X152" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="Y152" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="Z152" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="AA152" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AB152" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="AC152" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AX152" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=杖劍傳說：坎斯汀之約</v>
+      </c>
     </row>
-    <row r="152" spans="1:31" ht="19.899999999999999" customHeight="1">
-      <c r="A152" s="11" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C152" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/杖劍傳說：坎斯汀之約-禮包碼.jpg</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>1602</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>1603</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>1605</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="L152" s="2" t="s">
-        <v>1608</v>
-      </c>
-      <c r="M152" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="N152" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="O152" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="P152" s="2" t="s">
-        <v>1613</v>
-      </c>
-      <c r="Q152" s="2" t="s">
-        <v>1614</v>
-      </c>
-      <c r="R152" s="2" t="s">
-        <v>1615</v>
-      </c>
-      <c r="S152" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="T152" s="2" t="s">
-        <v>1617</v>
-      </c>
-      <c r="U152" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="V152" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="W152" s="2" t="s">
-        <v>1620</v>
-      </c>
-      <c r="X152" s="2" t="s">
-        <v>1621</v>
-      </c>
-      <c r="Y152" s="2" t="s">
+    <row r="153" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C153" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/超級海戰：紀元崛起-禮包碼.jpg</v>
+      </c>
+      <c r="D153" s="8" t="s">
         <v>1622</v>
       </c>
-      <c r="Z152" s="2" t="s">
-        <v>1623</v>
-      </c>
-      <c r="AA152" s="2" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AB152" s="2" t="s">
+      <c r="E153" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="J153" s="2" t="s">
         <v>1624</v>
       </c>
-      <c r="AC152" s="2" t="s">
-        <v>1622</v>
+      <c r="K153" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="N153" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="O153" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="P153" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="Q153" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="AX153" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=超級海戰：紀元崛起</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="19.899999999999999" customHeight="1">
-      <c r="A153" s="2" t="s">
-        <v>1626</v>
-      </c>
-      <c r="C153" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/超級海戰：紀元崛起-禮包碼.jpg</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>1632</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="J153" s="2" t="s">
-        <v>1627</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>1634</v>
-      </c>
-      <c r="L153" s="2" t="s">
-        <v>1628</v>
-      </c>
-      <c r="M153" s="2" t="s">
+    <row r="154" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="2" t="s">
         <v>1635</v>
       </c>
-      <c r="N153" s="2" t="s">
-        <v>1629</v>
-      </c>
-      <c r="O153" s="2" t="s">
+      <c r="C154" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/進擊的惡魔團-禮包碼.jpg</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>1636</v>
       </c>
-      <c r="P153" s="2" t="s">
-        <v>1630</v>
-      </c>
-      <c r="Q153" s="2" t="s">
+      <c r="F154" s="2" t="s">
         <v>1637</v>
       </c>
+      <c r="G154" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K154" s="13" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="O154" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="P154" s="13" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Q154" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="R154" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="S154" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="AX154" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=進擊的惡魔團</v>
+      </c>
     </row>
-    <row r="154" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A154" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="C154" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/進擊的惡魔團-禮包碼.jpg</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>1643</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>1641</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1642</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>1644</v>
-      </c>
-      <c r="K154" s="16" t="s">
-        <v>1645</v>
-      </c>
-      <c r="L154" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="M154" s="2" t="s">
-        <v>1647</v>
-      </c>
-      <c r="N154" s="2" t="s">
-        <v>1648</v>
-      </c>
-      <c r="O154" s="2" t="s">
+    <row r="155" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="14" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C155" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/蝕影：緋之契-禮包碼.jpg</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>1653</v>
       </c>
-      <c r="P154" s="17" t="s">
-        <v>1649</v>
-      </c>
-      <c r="Q154" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="R154" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="S154" s="2" t="s">
+      <c r="E155" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J155" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K155" s="17" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L155" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="M155" s="17" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N155" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="O155" s="17" t="s">
+        <v>1658</v>
+      </c>
+      <c r="P155" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q155" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AX155" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=蝕影：緋之契</v>
+      </c>
+    </row>
+    <row r="156" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="14" t="s">
         <v>1651</v>
       </c>
+      <c r="C156" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/RO：Crush-禮包碼.jpg</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AX156" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=RO：Crush</v>
+      </c>
     </row>
-    <row r="155" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A155" s="18" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C155" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/蝕影：緋之契-禮包碼.jpg</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="J155" s="19" t="s">
-        <v>1658</v>
-      </c>
-      <c r="K155" s="20" t="s">
-        <v>1659</v>
-      </c>
-      <c r="L155" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="M155" s="22" t="s">
-        <v>1660</v>
-      </c>
-      <c r="N155" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="O155" s="20" t="s">
-        <v>1661</v>
-      </c>
-      <c r="P155" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q155" s="22" t="s">
-        <v>1662</v>
+    <row r="157" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="14" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C157" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="O157" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="AX157" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=溯回青空</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A156" s="12" t="s">
-        <v>1654</v>
-      </c>
-      <c r="C156" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/RO：Crush-禮包碼.jpg</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="F156" s="2" t="s">
+    <row r="158" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="14" t="s">
         <v>1668</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="C158" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AX158" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=蒼之啟示錄</v>
+      </c>
+    </row>
+    <row r="159" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="14" t="s">
         <v>1669</v>
       </c>
-      <c r="J156" s="2" t="s">
-        <v>1666</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>1667</v>
+      <c r="C159" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="AX159" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=第六絕區</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A157" s="12" t="s">
+    <row r="160" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="14" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C160" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AX160" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=MO.CO</v>
+      </c>
+    </row>
+    <row r="161" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="14" t="s">
         <v>1670</v>
       </c>
-      <c r="C157" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
-      </c>
-      <c r="D157" s="23" t="s">
-        <v>1674</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>1686</v>
-      </c>
-      <c r="F157" s="24" t="s">
-        <v>1687</v>
-      </c>
-      <c r="J157" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="L157" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="M157" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="N157" s="2" t="s">
-        <v>1684</v>
-      </c>
-      <c r="O157" s="2" t="s">
-        <v>1685</v>
+      <c r="C161" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AX161" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=幻世三國：一騎當千</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A158" s="12" t="s">
-        <v>1671</v>
-      </c>
-      <c r="C158" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
-      </c>
-      <c r="D158" s="23" t="s">
-        <v>1675</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="J158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="K158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="L158" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="M158" s="2" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="159" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A159" s="12" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C159" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
-      </c>
-      <c r="D159" s="23" t="s">
-        <v>1676</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>1692</v>
-      </c>
-      <c r="F159" s="2" t="s">
+    <row r="162" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="14" t="s">
         <v>1693</v>
       </c>
-      <c r="G159" s="2" t="s">
-        <v>1694</v>
-      </c>
-      <c r="H159" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="J159" s="2" t="s">
-        <v>1688</v>
-      </c>
-      <c r="K159" s="2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="L159" s="2" t="s">
-        <v>1690</v>
-      </c>
-      <c r="M159" s="2" t="s">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="160" spans="1:31" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A160" s="12" t="s">
-        <v>1700</v>
-      </c>
-      <c r="C160" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
-      </c>
-      <c r="D160" s="23" t="s">
-        <v>1677</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="L160" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="M160" s="2" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="161" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A161" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="C161" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
-      </c>
-      <c r="D161" s="23" t="s">
-        <v>1678</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="L161" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="M161" s="2" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="162" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A162" s="12" t="s">
-        <v>1696</v>
-      </c>
       <c r="C162" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
       </c>
-      <c r="D162" s="25" t="s">
-        <v>1698</v>
+      <c r="D162" s="10" t="s">
+        <v>1810</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>1478</v>
@@ -17374,17 +17773,21 @@
       <c r="M162" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX162" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小兵立大功</v>
+      </c>
     </row>
-    <row r="163" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A163" s="12" t="s">
-        <v>1697</v>
+    <row r="163" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="14" t="s">
+        <v>1694</v>
       </c>
       <c r="C163" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
       </c>
-      <c r="D163" s="25" t="s">
-        <v>1699</v>
+      <c r="D163" s="10" t="s">
+        <v>1811</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>1478</v>
@@ -17410,62 +17813,70 @@
       <c r="M163" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX163" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=像素全明星</v>
+      </c>
     </row>
-    <row r="164" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A164" s="12" t="s">
+    <row r="164" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="14" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C164" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/浣熊傳說-禮包碼.jpg</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>1701</v>
       </c>
-      <c r="C164" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/浣熊傳說-禮包碼.jpg</v>
-      </c>
-      <c r="D164" s="8" t="s">
+      <c r="F164" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G164" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="E164" s="2" t="s">
+      <c r="J164" s="13" t="s">
+        <v>1700</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="N164" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="O164" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="P164" s="2" t="s">
         <v>1706</v>
       </c>
-      <c r="F164" s="2" t="s">
-        <v>1707</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>1708</v>
-      </c>
-      <c r="J164" s="26" t="s">
-        <v>1705</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="L164" s="2" t="s">
-        <v>1709</v>
-      </c>
-      <c r="M164" s="2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="N164" s="2" t="s">
+      <c r="Q164" s="2" t="s">
         <v>1710</v>
       </c>
-      <c r="O164" s="2" t="s">
-        <v>1714</v>
-      </c>
-      <c r="P164" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="Q164" s="2" t="s">
-        <v>1715</v>
+      <c r="AX164" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=浣熊傳說</v>
       </c>
     </row>
-    <row r="165" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A165" s="12" t="s">
-        <v>1702</v>
+    <row r="165" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="14" t="s">
+        <v>1697</v>
       </c>
       <c r="C165" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/勇者格鬥城-禮包碼.jpg</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>1478</v>
@@ -17491,17 +17902,21 @@
       <c r="M165" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX165" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=勇者格鬥城</v>
+      </c>
     </row>
-    <row r="166" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A166" s="18" t="s">
-        <v>1725</v>
+    <row r="166" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="14" t="s">
+        <v>1720</v>
       </c>
       <c r="C166" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/龐寶：背包英雄們-禮包碼.jpg</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>1478</v>
@@ -17527,849 +17942,877 @@
       <c r="M166" s="2" t="s">
         <v>1478</v>
       </c>
+      <c r="AX166" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=龐寶：背包英雄們</v>
+      </c>
     </row>
-    <row r="167" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A167" s="12" t="s">
+    <row r="167" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="14" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C167" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/星耀球會-禮包碼.jpg</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>1716</v>
       </c>
-      <c r="C167" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/星耀球會-禮包碼.jpg</v>
-      </c>
-      <c r="D167" s="8" t="s">
+      <c r="F167" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="O167" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="P167" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="Q167" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="AX167" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星耀球會</v>
+      </c>
+    </row>
+    <row r="168" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="13" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C168" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/東方幻想ECLIPSE-禮包碼.jpg</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>1726</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="G167" s="2" t="s">
+      <c r="G168" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="J168" s="2" t="s">
         <v>1723</v>
       </c>
-      <c r="J167" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="K167" s="2" t="s">
+      <c r="K168" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="AX168" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=東方幻想ECLIPSE</v>
+      </c>
+    </row>
+    <row r="169" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="14" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C169" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/世紀帝國M-禮包碼.jpg</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="N169" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="O169" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="Q169" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="R169" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="S169" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="T169" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="U169" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="V169" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="W169" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="X169" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="Y169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="Z169" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AA169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AB169" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AC169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AD169" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="AE169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AF169" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="AG169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AH169" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="AI169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AJ169" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AK169" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="AX169" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=世紀帝國M</v>
+      </c>
+    </row>
+    <row r="170" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="14" t="s">
         <v>1735</v>
       </c>
-      <c r="L167" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="M167" s="2" t="s">
-        <v>1736</v>
-      </c>
-      <c r="N167" s="2" t="s">
-        <v>1720</v>
-      </c>
-      <c r="O167" s="2" t="s">
-        <v>1737</v>
-      </c>
-      <c r="P167" s="2" t="s">
-        <v>1724</v>
-      </c>
-      <c r="Q167" s="2" t="s">
+      <c r="C170" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/歐啦!守得豬-禮包碼.jpg</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="O170" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="Q170" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="R170" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="S170" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="T170" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="U170" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="AX170" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=歐啦!守得豬</v>
+      </c>
+    </row>
+    <row r="171" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="14" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C171" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/18櫻花幕府-禮包碼.jpg</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>1754</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G171" s="2" t="s">
         <v>1738</v>
       </c>
+      <c r="J171" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="AX171" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=18櫻花幕府</v>
+      </c>
     </row>
-    <row r="168" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A168" s="11" t="s">
-        <v>1727</v>
-      </c>
-      <c r="C168" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/東方幻想ECLIPSE-禮包碼.jpg</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>1730</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>1731</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>1732</v>
-      </c>
-      <c r="J168" s="2" t="s">
-        <v>1728</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="L168" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="M168" s="2" t="s">
-        <v>1734</v>
+    <row r="172" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="14" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C172" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/大武道-禮包碼.jpg</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="J172" s="16" t="s">
+        <v>1789</v>
+      </c>
+      <c r="K172" s="17" t="s">
+        <v>1790</v>
+      </c>
+      <c r="L172" s="16" t="s">
+        <v>1791</v>
+      </c>
+      <c r="M172" s="17" t="s">
+        <v>1792</v>
+      </c>
+      <c r="N172" s="16" t="s">
+        <v>1793</v>
+      </c>
+      <c r="O172" s="17" t="s">
+        <v>1790</v>
+      </c>
+      <c r="P172" s="16" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q172" s="17" t="s">
+        <v>1792</v>
+      </c>
+      <c r="R172" s="16" t="s">
+        <v>1795</v>
+      </c>
+      <c r="S172" s="17" t="s">
+        <v>1790</v>
+      </c>
+      <c r="T172" s="16" t="s">
+        <v>1796</v>
+      </c>
+      <c r="U172" s="17" t="s">
+        <v>1792</v>
+      </c>
+      <c r="V172" s="16" t="s">
+        <v>1797</v>
+      </c>
+      <c r="W172" s="17" t="s">
+        <v>1790</v>
+      </c>
+      <c r="X172" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="Y172" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="Z172" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AA172" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AB172" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="AC172" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AD172" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="AE172" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AX172" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=大武道</v>
       </c>
     </row>
-    <row r="169" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A169" s="12" t="s">
-        <v>1739</v>
-      </c>
-      <c r="C169" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/世紀帝國M-禮包碼.jpg</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>1741</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>1744</v>
-      </c>
-      <c r="K169" s="2" t="s">
-        <v>1745</v>
-      </c>
-      <c r="L169" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="M169" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="N169" s="2" t="s">
-        <v>1767</v>
-      </c>
-      <c r="O169" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="P169" s="2" t="s">
-        <v>1768</v>
-      </c>
-      <c r="Q169" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="R169" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="S169" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="T169" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="U169" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="V169" s="2" t="s">
-        <v>1771</v>
-      </c>
-      <c r="W169" s="2" t="s">
-        <v>1782</v>
-      </c>
-      <c r="X169" s="2" t="s">
-        <v>1772</v>
-      </c>
-      <c r="Y169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="Z169" s="2" t="s">
-        <v>1773</v>
-      </c>
-      <c r="AA169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="AB169" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="AC169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="AD169" s="2" t="s">
-        <v>1775</v>
-      </c>
-      <c r="AE169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="AF169" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="AG169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="AH169" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="AI169" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="AJ169" s="2" t="s">
-        <v>1778</v>
-      </c>
-      <c r="AK169" s="2" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="170" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A170" s="12" t="s">
-        <v>1740</v>
-      </c>
-      <c r="C170" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/歐啦!守得豬-禮包碼.jpg</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>1789</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>1746</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>1747</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="J170" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="K170" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L170" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="M170" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="N170" s="2" t="s">
-        <v>1751</v>
-      </c>
-      <c r="O170" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="P170" s="2" t="s">
-        <v>1752</v>
-      </c>
-      <c r="Q170" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="R170" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="S170" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="T170" s="2" t="s">
-        <v>1754</v>
-      </c>
-      <c r="U170" s="2" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="171" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A171" s="18" t="s">
-        <v>1755</v>
-      </c>
-      <c r="C171" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/18櫻花幕府-禮包碼.jpg</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>1759</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>1784</v>
-      </c>
-      <c r="F171" s="2" t="s">
-        <v>1785</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="J171" s="2" t="s">
-        <v>1756</v>
-      </c>
-      <c r="K171" s="2" t="s">
-        <v>1786</v>
-      </c>
-      <c r="L171" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="M171" s="2" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="172" spans="1:37" ht="19.899999999999999" customHeight="1" thickBot="1">
-      <c r="A172" s="18" t="s">
-        <v>1790</v>
-      </c>
-      <c r="C172" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>giftcodesbanner/大武道-禮包碼.jpg</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>1803</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>1791</v>
-      </c>
-      <c r="F172" s="2" t="s">
-        <v>1792</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>1793</v>
-      </c>
-      <c r="J172" s="27" t="s">
-        <v>1794</v>
-      </c>
-      <c r="K172" s="28" t="s">
-        <v>1795</v>
-      </c>
-      <c r="L172" s="29" t="s">
-        <v>1796</v>
-      </c>
-      <c r="M172" s="30" t="s">
-        <v>1797</v>
-      </c>
-      <c r="N172" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="O172" s="28" t="s">
-        <v>1795</v>
-      </c>
-      <c r="P172" s="29" t="s">
-        <v>1799</v>
-      </c>
-      <c r="Q172" s="30" t="s">
-        <v>1797</v>
-      </c>
-      <c r="R172" s="27" t="s">
-        <v>1800</v>
-      </c>
-      <c r="S172" s="28" t="s">
-        <v>1795</v>
-      </c>
-      <c r="T172" s="29" t="s">
-        <v>1801</v>
-      </c>
-      <c r="U172" s="30" t="s">
-        <v>1797</v>
-      </c>
-      <c r="V172" s="27" t="s">
-        <v>1802</v>
-      </c>
-      <c r="W172" s="28" t="s">
-        <v>1795</v>
-      </c>
-      <c r="X172" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="Y172" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="Z172" s="2" t="s">
-        <v>1805</v>
-      </c>
-      <c r="AA172" s="2" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AB172" s="2" t="s">
-        <v>1806</v>
-      </c>
-      <c r="AC172" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AD172" s="2" t="s">
-        <v>1807</v>
-      </c>
-      <c r="AE172" s="2" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="173" spans="1:37" ht="19.899999999999999" customHeight="1"/>
-    <row r="174" spans="1:37" ht="19.899999999999999" customHeight="1"/>
-    <row r="175" spans="1:37" ht="19.899999999999999" customHeight="1"/>
-    <row r="176" spans="1:37" ht="19.899999999999999" customHeight="1"/>
-    <row r="177" ht="19.899999999999999" customHeight="1"/>
-    <row r="178" ht="19.899999999999999" customHeight="1"/>
-    <row r="179" ht="19.899999999999999" customHeight="1"/>
-    <row r="180" ht="19.899999999999999" customHeight="1"/>
-    <row r="181" ht="19.899999999999999" customHeight="1"/>
-    <row r="182" ht="19.899999999999999" customHeight="1"/>
-    <row r="183" ht="19.899999999999999" customHeight="1"/>
-    <row r="184" ht="19.899999999999999" customHeight="1"/>
-    <row r="185" ht="19.899999999999999" customHeight="1"/>
-    <row r="186" ht="19.899999999999999" customHeight="1"/>
-    <row r="187" ht="19.899999999999999" customHeight="1"/>
-    <row r="188" ht="19.899999999999999" customHeight="1"/>
-    <row r="189" ht="19.899999999999999" customHeight="1"/>
-    <row r="190" ht="19.899999999999999" customHeight="1"/>
-    <row r="191" ht="19.899999999999999" customHeight="1"/>
-    <row r="192" ht="19.899999999999999" customHeight="1"/>
-    <row r="193" ht="19.899999999999999" customHeight="1"/>
-    <row r="194" ht="19.899999999999999" customHeight="1"/>
-    <row r="195" ht="19.899999999999999" customHeight="1"/>
-    <row r="196" ht="19.899999999999999" customHeight="1"/>
-    <row r="197" ht="19.899999999999999" customHeight="1"/>
-    <row r="198" ht="19.899999999999999" customHeight="1"/>
-    <row r="199" ht="19.899999999999999" customHeight="1"/>
-    <row r="200" ht="19.899999999999999" customHeight="1"/>
-    <row r="201" ht="19.899999999999999" customHeight="1"/>
-    <row r="202" ht="19.899999999999999" customHeight="1"/>
-    <row r="203" ht="19.899999999999999" customHeight="1"/>
-    <row r="204" ht="19.899999999999999" customHeight="1"/>
-    <row r="205" ht="19.899999999999999" customHeight="1"/>
-    <row r="206" ht="19.899999999999999" customHeight="1"/>
-    <row r="207" ht="19.899999999999999" customHeight="1"/>
-    <row r="208" ht="19.899999999999999" customHeight="1"/>
-    <row r="209" ht="19.899999999999999" customHeight="1"/>
-    <row r="210" ht="19.899999999999999" customHeight="1"/>
-    <row r="211" ht="19.899999999999999" customHeight="1"/>
-    <row r="212" ht="19.899999999999999" customHeight="1"/>
-    <row r="213" ht="19.899999999999999" customHeight="1"/>
-    <row r="214" ht="19.899999999999999" customHeight="1"/>
-    <row r="215" ht="19.899999999999999" customHeight="1"/>
-    <row r="216" ht="19.899999999999999" customHeight="1"/>
-    <row r="217" ht="19.899999999999999" customHeight="1"/>
-    <row r="218" ht="19.899999999999999" customHeight="1"/>
-    <row r="219" ht="19.899999999999999" customHeight="1"/>
-    <row r="220" ht="19.899999999999999" customHeight="1"/>
-    <row r="221" ht="19.899999999999999" customHeight="1"/>
-    <row r="222" ht="19.899999999999999" customHeight="1"/>
-    <row r="223" ht="19.899999999999999" customHeight="1"/>
-    <row r="224" ht="19.899999999999999" customHeight="1"/>
-    <row r="225" ht="19.899999999999999" customHeight="1"/>
-    <row r="226" ht="19.899999999999999" customHeight="1"/>
-    <row r="227" ht="19.899999999999999" customHeight="1"/>
-    <row r="228" ht="19.899999999999999" customHeight="1"/>
-    <row r="229" ht="19.899999999999999" customHeight="1"/>
-    <row r="230" ht="19.899999999999999" customHeight="1"/>
-    <row r="231" ht="19.899999999999999" customHeight="1"/>
-    <row r="232" ht="19.899999999999999" customHeight="1"/>
-    <row r="233" ht="19.899999999999999" customHeight="1"/>
-    <row r="234" ht="19.899999999999999" customHeight="1"/>
-    <row r="235" ht="19.899999999999999" customHeight="1"/>
-    <row r="236" ht="19.899999999999999" customHeight="1"/>
-    <row r="237" ht="19.899999999999999" customHeight="1"/>
-    <row r="238" ht="19.899999999999999" customHeight="1"/>
-    <row r="239" ht="19.899999999999999" customHeight="1"/>
-    <row r="240" ht="19.899999999999999" customHeight="1"/>
-    <row r="241" ht="19.899999999999999" customHeight="1"/>
-    <row r="242" ht="19.899999999999999" customHeight="1"/>
-    <row r="243" ht="19.899999999999999" customHeight="1"/>
-    <row r="244" ht="19.899999999999999" customHeight="1"/>
-    <row r="245" ht="19.899999999999999" customHeight="1"/>
-    <row r="246" ht="19.899999999999999" customHeight="1"/>
-    <row r="247" ht="19.899999999999999" customHeight="1"/>
-    <row r="248" ht="19.899999999999999" customHeight="1"/>
-    <row r="249" ht="19.899999999999999" customHeight="1"/>
-    <row r="250" ht="19.899999999999999" customHeight="1"/>
-    <row r="251" ht="19.899999999999999" customHeight="1"/>
-    <row r="252" ht="19.899999999999999" customHeight="1"/>
-    <row r="253" ht="19.899999999999999" customHeight="1"/>
-    <row r="254" ht="19.899999999999999" customHeight="1"/>
-    <row r="255" ht="19.899999999999999" customHeight="1"/>
-    <row r="256" ht="19.899999999999999" customHeight="1"/>
-    <row r="257" ht="19.899999999999999" customHeight="1"/>
-    <row r="258" ht="19.899999999999999" customHeight="1"/>
-    <row r="259" ht="19.899999999999999" customHeight="1"/>
-    <row r="260" ht="19.899999999999999" customHeight="1"/>
-    <row r="261" ht="19.899999999999999" customHeight="1"/>
-    <row r="262" ht="19.899999999999999" customHeight="1"/>
-    <row r="263" ht="19.899999999999999" customHeight="1"/>
-    <row r="264" ht="19.899999999999999" customHeight="1"/>
-    <row r="265" ht="19.899999999999999" customHeight="1"/>
-    <row r="266" ht="19.899999999999999" customHeight="1"/>
-    <row r="267" ht="19.899999999999999" customHeight="1"/>
-    <row r="268" ht="19.899999999999999" customHeight="1"/>
-    <row r="269" ht="19.899999999999999" customHeight="1"/>
-    <row r="270" ht="19.899999999999999" customHeight="1"/>
-    <row r="271" ht="19.899999999999999" customHeight="1"/>
-    <row r="272" ht="19.899999999999999" customHeight="1"/>
-    <row r="273" ht="19.899999999999999" customHeight="1"/>
-    <row r="274" ht="19.899999999999999" customHeight="1"/>
-    <row r="275" ht="19.899999999999999" customHeight="1"/>
-    <row r="276" ht="19.899999999999999" customHeight="1"/>
-    <row r="277" ht="19.899999999999999" customHeight="1"/>
-    <row r="278" ht="19.899999999999999" customHeight="1"/>
-    <row r="279" ht="19.899999999999999" customHeight="1"/>
-    <row r="280" ht="19.899999999999999" customHeight="1"/>
-    <row r="281" ht="19.899999999999999" customHeight="1"/>
-    <row r="282" ht="19.899999999999999" customHeight="1"/>
-    <row r="283" ht="19.899999999999999" customHeight="1"/>
-    <row r="284" ht="19.899999999999999" customHeight="1"/>
-    <row r="285" ht="19.899999999999999" customHeight="1"/>
-    <row r="286" ht="19.899999999999999" customHeight="1"/>
-    <row r="287" ht="19.899999999999999" customHeight="1"/>
-    <row r="288" ht="19.899999999999999" customHeight="1"/>
-    <row r="289" ht="19.899999999999999" customHeight="1"/>
-    <row r="290" ht="19.899999999999999" customHeight="1"/>
-    <row r="291" ht="19.899999999999999" customHeight="1"/>
-    <row r="292" ht="19.899999999999999" customHeight="1"/>
-    <row r="293" ht="19.899999999999999" customHeight="1"/>
-    <row r="294" ht="19.899999999999999" customHeight="1"/>
-    <row r="295" ht="19.899999999999999" customHeight="1"/>
-    <row r="296" ht="19.899999999999999" customHeight="1"/>
-    <row r="297" ht="19.899999999999999" customHeight="1"/>
-    <row r="298" ht="19.899999999999999" customHeight="1"/>
-    <row r="299" ht="19.899999999999999" customHeight="1"/>
-    <row r="300" ht="19.899999999999999" customHeight="1"/>
-    <row r="301" ht="19.899999999999999" customHeight="1"/>
-    <row r="302" ht="19.899999999999999" customHeight="1"/>
-    <row r="303" ht="19.899999999999999" customHeight="1"/>
-    <row r="304" ht="19.899999999999999" customHeight="1"/>
-    <row r="305" ht="19.899999999999999" customHeight="1"/>
-    <row r="306" ht="19.899999999999999" customHeight="1"/>
-    <row r="307" ht="19.899999999999999" customHeight="1"/>
-    <row r="308" ht="19.899999999999999" customHeight="1"/>
-    <row r="309" ht="19.899999999999999" customHeight="1"/>
-    <row r="310" ht="19.899999999999999" customHeight="1"/>
-    <row r="311" ht="19.899999999999999" customHeight="1"/>
-    <row r="312" ht="19.899999999999999" customHeight="1"/>
-    <row r="313" ht="19.899999999999999" customHeight="1"/>
-    <row r="314" ht="19.899999999999999" customHeight="1"/>
-    <row r="315" ht="19.899999999999999" customHeight="1"/>
-    <row r="316" ht="19.899999999999999" customHeight="1"/>
-    <row r="317" ht="19.899999999999999" customHeight="1"/>
-    <row r="318" ht="19.899999999999999" customHeight="1"/>
-    <row r="319" ht="19.899999999999999" customHeight="1"/>
-    <row r="320" ht="19.899999999999999" customHeight="1"/>
-    <row r="321" ht="19.899999999999999" customHeight="1"/>
-    <row r="322" ht="19.899999999999999" customHeight="1"/>
-    <row r="323" ht="19.899999999999999" customHeight="1"/>
-    <row r="324" ht="19.899999999999999" customHeight="1"/>
-    <row r="325" ht="19.899999999999999" customHeight="1"/>
-    <row r="326" ht="19.899999999999999" customHeight="1"/>
-    <row r="327" ht="19.899999999999999" customHeight="1"/>
-    <row r="328" ht="19.899999999999999" customHeight="1"/>
-    <row r="329" ht="19.899999999999999" customHeight="1"/>
-    <row r="330" ht="19.899999999999999" customHeight="1"/>
-    <row r="331" ht="19.899999999999999" customHeight="1"/>
-    <row r="332" ht="19.899999999999999" customHeight="1"/>
-    <row r="333" ht="19.899999999999999" customHeight="1"/>
-    <row r="334" ht="19.899999999999999" customHeight="1"/>
-    <row r="335" ht="19.899999999999999" customHeight="1"/>
-    <row r="336" ht="19.899999999999999" customHeight="1"/>
-    <row r="337" ht="19.899999999999999" customHeight="1"/>
-    <row r="338" ht="19.899999999999999" customHeight="1"/>
-    <row r="339" ht="19.899999999999999" customHeight="1"/>
-    <row r="340" ht="19.899999999999999" customHeight="1"/>
-    <row r="341" ht="19.899999999999999" customHeight="1"/>
-    <row r="342" ht="19.899999999999999" customHeight="1"/>
-    <row r="343" ht="19.899999999999999" customHeight="1"/>
-    <row r="344" ht="19.899999999999999" customHeight="1"/>
-    <row r="345" ht="19.899999999999999" customHeight="1"/>
-    <row r="346" ht="19.899999999999999" customHeight="1"/>
-    <row r="347" ht="19.899999999999999" customHeight="1"/>
-    <row r="348" ht="19.899999999999999" customHeight="1"/>
-    <row r="349" ht="19.899999999999999" customHeight="1"/>
-    <row r="350" ht="19.899999999999999" customHeight="1"/>
-    <row r="351" ht="19.899999999999999" customHeight="1"/>
-    <row r="352" ht="19.899999999999999" customHeight="1"/>
-    <row r="353" ht="19.899999999999999" customHeight="1"/>
-    <row r="354" ht="19.899999999999999" customHeight="1"/>
-    <row r="355" ht="19.899999999999999" customHeight="1"/>
-    <row r="356" ht="19.899999999999999" customHeight="1"/>
-    <row r="357" ht="19.899999999999999" customHeight="1"/>
-    <row r="358" ht="19.899999999999999" customHeight="1"/>
-    <row r="359" ht="19.899999999999999" customHeight="1"/>
-    <row r="360" ht="19.899999999999999" customHeight="1"/>
-    <row r="361" ht="19.899999999999999" customHeight="1"/>
-    <row r="362" ht="19.899999999999999" customHeight="1"/>
-    <row r="363" ht="19.899999999999999" customHeight="1"/>
-    <row r="364" ht="19.899999999999999" customHeight="1"/>
-    <row r="365" ht="19.899999999999999" customHeight="1"/>
-    <row r="366" ht="19.899999999999999" customHeight="1"/>
-    <row r="367" ht="19.899999999999999" customHeight="1"/>
-    <row r="368" ht="19.899999999999999" customHeight="1"/>
-    <row r="369" ht="19.899999999999999" customHeight="1"/>
-    <row r="370" ht="19.899999999999999" customHeight="1"/>
-    <row r="371" ht="19.899999999999999" customHeight="1"/>
-    <row r="372" ht="19.899999999999999" customHeight="1"/>
-    <row r="373" ht="19.899999999999999" customHeight="1"/>
-    <row r="374" ht="19.899999999999999" customHeight="1"/>
-    <row r="375" ht="19.899999999999999" customHeight="1"/>
-    <row r="376" ht="19.899999999999999" customHeight="1"/>
-    <row r="377" ht="19.899999999999999" customHeight="1"/>
-    <row r="378" ht="19.899999999999999" customHeight="1"/>
-    <row r="379" ht="19.899999999999999" customHeight="1"/>
-    <row r="380" ht="19.899999999999999" customHeight="1"/>
-    <row r="381" ht="19.899999999999999" customHeight="1"/>
-    <row r="382" ht="19.899999999999999" customHeight="1"/>
-    <row r="383" ht="19.899999999999999" customHeight="1"/>
-    <row r="384" ht="19.899999999999999" customHeight="1"/>
-    <row r="385" ht="19.899999999999999" customHeight="1"/>
-    <row r="386" ht="19.899999999999999" customHeight="1"/>
-    <row r="387" ht="19.899999999999999" customHeight="1"/>
-    <row r="388" ht="19.899999999999999" customHeight="1"/>
-    <row r="389" ht="19.899999999999999" customHeight="1"/>
-    <row r="390" ht="19.899999999999999" customHeight="1"/>
-    <row r="391" ht="19.899999999999999" customHeight="1"/>
-    <row r="392" ht="19.899999999999999" customHeight="1"/>
-    <row r="393" ht="19.899999999999999" customHeight="1"/>
-    <row r="394" ht="19.899999999999999" customHeight="1"/>
-    <row r="395" ht="19.899999999999999" customHeight="1"/>
-    <row r="396" ht="19.899999999999999" customHeight="1"/>
-    <row r="397" ht="19.899999999999999" customHeight="1"/>
-    <row r="398" ht="19.899999999999999" customHeight="1"/>
-    <row r="399" ht="19.899999999999999" customHeight="1"/>
-    <row r="400" ht="19.899999999999999" customHeight="1"/>
-    <row r="401" ht="19.899999999999999" customHeight="1"/>
-    <row r="402" ht="19.899999999999999" customHeight="1"/>
-    <row r="403" ht="19.899999999999999" customHeight="1"/>
-    <row r="404" ht="19.899999999999999" customHeight="1"/>
-    <row r="405" ht="19.899999999999999" customHeight="1"/>
-    <row r="406" ht="19.899999999999999" customHeight="1"/>
-    <row r="407" ht="19.899999999999999" customHeight="1"/>
-    <row r="408" ht="19.899999999999999" customHeight="1"/>
-    <row r="409" ht="19.899999999999999" customHeight="1"/>
-    <row r="410" ht="19.899999999999999" customHeight="1"/>
-    <row r="411" ht="19.899999999999999" customHeight="1"/>
-    <row r="412" ht="19.899999999999999" customHeight="1"/>
-    <row r="413" ht="19.899999999999999" customHeight="1"/>
-    <row r="414" ht="19.899999999999999" customHeight="1"/>
-    <row r="415" ht="19.899999999999999" customHeight="1"/>
-    <row r="416" ht="19.899999999999999" customHeight="1"/>
-    <row r="417" ht="19.899999999999999" customHeight="1"/>
-    <row r="418" ht="19.899999999999999" customHeight="1"/>
-    <row r="419" ht="19.899999999999999" customHeight="1"/>
-    <row r="420" ht="19.899999999999999" customHeight="1"/>
-    <row r="421" ht="19.899999999999999" customHeight="1"/>
-    <row r="422" ht="19.899999999999999" customHeight="1"/>
-    <row r="423" ht="19.899999999999999" customHeight="1"/>
-    <row r="424" ht="19.899999999999999" customHeight="1"/>
-    <row r="425" ht="19.899999999999999" customHeight="1"/>
-    <row r="426" ht="19.899999999999999" customHeight="1"/>
-    <row r="427" ht="19.899999999999999" customHeight="1"/>
-    <row r="428" ht="19.899999999999999" customHeight="1"/>
-    <row r="429" ht="19.899999999999999" customHeight="1"/>
-    <row r="430" ht="19.899999999999999" customHeight="1"/>
-    <row r="431" ht="19.899999999999999" customHeight="1"/>
-    <row r="432" ht="19.899999999999999" customHeight="1"/>
-    <row r="433" ht="19.899999999999999" customHeight="1"/>
-    <row r="434" ht="19.899999999999999" customHeight="1"/>
-    <row r="435" ht="19.899999999999999" customHeight="1"/>
-    <row r="436" ht="19.899999999999999" customHeight="1"/>
-    <row r="437" ht="19.899999999999999" customHeight="1"/>
-    <row r="438" ht="19.899999999999999" customHeight="1"/>
-    <row r="439" ht="19.899999999999999" customHeight="1"/>
-    <row r="440" ht="19.899999999999999" customHeight="1"/>
-    <row r="441" ht="19.899999999999999" customHeight="1"/>
-    <row r="442" ht="19.899999999999999" customHeight="1"/>
-    <row r="443" ht="19.899999999999999" customHeight="1"/>
-    <row r="444" ht="19.899999999999999" customHeight="1"/>
-    <row r="445" ht="19.899999999999999" customHeight="1"/>
-    <row r="446" ht="19.899999999999999" customHeight="1"/>
-    <row r="447" ht="19.899999999999999" customHeight="1"/>
-    <row r="448" ht="19.899999999999999" customHeight="1"/>
-    <row r="449" ht="19.899999999999999" customHeight="1"/>
-    <row r="450" ht="19.899999999999999" customHeight="1"/>
-    <row r="451" ht="19.899999999999999" customHeight="1"/>
-    <row r="452" ht="19.899999999999999" customHeight="1"/>
-    <row r="453" ht="19.899999999999999" customHeight="1"/>
-    <row r="454" ht="19.899999999999999" customHeight="1"/>
-    <row r="455" ht="19.899999999999999" customHeight="1"/>
-    <row r="456" ht="19.899999999999999" customHeight="1"/>
-    <row r="457" ht="19.899999999999999" customHeight="1"/>
-    <row r="458" ht="19.899999999999999" customHeight="1"/>
-    <row r="459" ht="19.899999999999999" customHeight="1"/>
-    <row r="460" ht="19.899999999999999" customHeight="1"/>
-    <row r="461" ht="19.899999999999999" customHeight="1"/>
-    <row r="462" ht="19.899999999999999" customHeight="1"/>
-    <row r="463" ht="19.899999999999999" customHeight="1"/>
-    <row r="464" ht="19.899999999999999" customHeight="1"/>
-    <row r="465" ht="19.899999999999999" customHeight="1"/>
-    <row r="466" ht="19.899999999999999" customHeight="1"/>
-    <row r="467" ht="19.899999999999999" customHeight="1"/>
-    <row r="468" ht="19.899999999999999" customHeight="1"/>
-    <row r="469" ht="19.899999999999999" customHeight="1"/>
-    <row r="470" ht="19.899999999999999" customHeight="1"/>
-    <row r="471" ht="19.899999999999999" customHeight="1"/>
-    <row r="472" ht="19.899999999999999" customHeight="1"/>
-    <row r="473" ht="19.899999999999999" customHeight="1"/>
-    <row r="474" ht="19.899999999999999" customHeight="1"/>
-    <row r="475" ht="19.899999999999999" customHeight="1"/>
-    <row r="476" ht="19.899999999999999" customHeight="1"/>
-    <row r="477" ht="19.899999999999999" customHeight="1"/>
-    <row r="478" ht="19.899999999999999" customHeight="1"/>
-    <row r="479" ht="19.899999999999999" customHeight="1"/>
-    <row r="480" ht="19.899999999999999" customHeight="1"/>
-    <row r="481" ht="19.899999999999999" customHeight="1"/>
-    <row r="482" ht="19.899999999999999" customHeight="1"/>
-    <row r="483" ht="19.899999999999999" customHeight="1"/>
-    <row r="484" ht="19.899999999999999" customHeight="1"/>
-    <row r="485" ht="19.899999999999999" customHeight="1"/>
-    <row r="486" ht="19.899999999999999" customHeight="1"/>
-    <row r="487" ht="19.899999999999999" customHeight="1"/>
-    <row r="488" ht="19.899999999999999" customHeight="1"/>
-    <row r="489" ht="19.899999999999999" customHeight="1"/>
-    <row r="490" ht="19.899999999999999" customHeight="1"/>
-    <row r="491" ht="19.899999999999999" customHeight="1"/>
-    <row r="492" ht="19.899999999999999" customHeight="1"/>
-    <row r="493" ht="19.899999999999999" customHeight="1"/>
-    <row r="494" ht="19.899999999999999" customHeight="1"/>
-    <row r="495" ht="19.899999999999999" customHeight="1"/>
-    <row r="496" ht="19.899999999999999" customHeight="1"/>
-    <row r="497" ht="19.899999999999999" customHeight="1"/>
-    <row r="498" ht="19.899999999999999" customHeight="1"/>
-    <row r="499" ht="19.899999999999999" customHeight="1"/>
-    <row r="500" ht="19.899999999999999" customHeight="1"/>
-    <row r="501" ht="19.899999999999999" customHeight="1"/>
-    <row r="502" ht="19.899999999999999" customHeight="1"/>
-    <row r="503" ht="19.899999999999999" customHeight="1"/>
-    <row r="504" ht="19.899999999999999" customHeight="1"/>
-    <row r="505" ht="19.899999999999999" customHeight="1"/>
-    <row r="506" ht="19.899999999999999" customHeight="1"/>
-    <row r="507" ht="19.899999999999999" customHeight="1"/>
-    <row r="508" ht="19.899999999999999" customHeight="1"/>
-    <row r="509" ht="19.899999999999999" customHeight="1"/>
-    <row r="510" ht="19.899999999999999" customHeight="1"/>
-    <row r="511" ht="19.899999999999999" customHeight="1"/>
-    <row r="512" ht="19.899999999999999" customHeight="1"/>
-    <row r="513" ht="19.899999999999999" customHeight="1"/>
-    <row r="514" ht="19.899999999999999" customHeight="1"/>
-    <row r="515" ht="19.899999999999999" customHeight="1"/>
-    <row r="516" ht="19.899999999999999" customHeight="1"/>
-    <row r="517" ht="19.899999999999999" customHeight="1"/>
-    <row r="518" ht="19.899999999999999" customHeight="1"/>
-    <row r="519" ht="19.899999999999999" customHeight="1"/>
-    <row r="520" ht="19.899999999999999" customHeight="1"/>
-    <row r="521" ht="19.899999999999999" customHeight="1"/>
-    <row r="522" ht="19.899999999999999" customHeight="1"/>
-    <row r="523" ht="19.899999999999999" customHeight="1"/>
-    <row r="524" ht="19.899999999999999" customHeight="1"/>
-    <row r="525" ht="19.899999999999999" customHeight="1"/>
-    <row r="526" ht="19.899999999999999" customHeight="1"/>
-    <row r="527" ht="19.899999999999999" customHeight="1"/>
-    <row r="528" ht="19.899999999999999" customHeight="1"/>
-    <row r="529" ht="19.899999999999999" customHeight="1"/>
-    <row r="530" ht="19.899999999999999" customHeight="1"/>
-    <row r="531" ht="19.899999999999999" customHeight="1"/>
-    <row r="532" ht="19.899999999999999" customHeight="1"/>
-    <row r="533" ht="19.899999999999999" customHeight="1"/>
-    <row r="534" ht="19.899999999999999" customHeight="1"/>
-    <row r="535" ht="19.899999999999999" customHeight="1"/>
-    <row r="536" ht="19.899999999999999" customHeight="1"/>
-    <row r="537" ht="19.899999999999999" customHeight="1"/>
-    <row r="538" ht="19.899999999999999" customHeight="1"/>
-    <row r="539" ht="19.899999999999999" customHeight="1"/>
-    <row r="540" ht="19.899999999999999" customHeight="1"/>
-    <row r="541" ht="19.899999999999999" customHeight="1"/>
-    <row r="542" ht="19.899999999999999" customHeight="1"/>
-    <row r="543" ht="19.899999999999999" customHeight="1"/>
-    <row r="544" ht="19.899999999999999" customHeight="1"/>
-    <row r="545" ht="19.899999999999999" customHeight="1"/>
-    <row r="546" ht="19.899999999999999" customHeight="1"/>
-    <row r="547" ht="19.899999999999999" customHeight="1"/>
-    <row r="548" ht="19.899999999999999" customHeight="1"/>
-    <row r="549" ht="19.899999999999999" customHeight="1"/>
-    <row r="550" ht="19.899999999999999" customHeight="1"/>
-    <row r="551" ht="19.899999999999999" customHeight="1"/>
-    <row r="552" ht="19.899999999999999" customHeight="1"/>
-    <row r="553" ht="19.899999999999999" customHeight="1"/>
-    <row r="554" ht="19.899999999999999" customHeight="1"/>
-    <row r="555" ht="19.899999999999999" customHeight="1"/>
-    <row r="556" ht="19.899999999999999" customHeight="1"/>
-    <row r="557" ht="19.899999999999999" customHeight="1"/>
-    <row r="558" ht="19.899999999999999" customHeight="1"/>
-    <row r="559" ht="19.899999999999999" customHeight="1"/>
-    <row r="560" ht="19.899999999999999" customHeight="1"/>
-    <row r="561" ht="19.899999999999999" customHeight="1"/>
-    <row r="562" ht="19.899999999999999" customHeight="1"/>
-    <row r="563" ht="19.899999999999999" customHeight="1"/>
-    <row r="564" ht="19.899999999999999" customHeight="1"/>
-    <row r="565" ht="19.899999999999999" customHeight="1"/>
-    <row r="566" ht="19.899999999999999" customHeight="1"/>
-    <row r="567" ht="19.899999999999999" customHeight="1"/>
-    <row r="568" ht="19.899999999999999" customHeight="1"/>
-    <row r="569" ht="19.899999999999999" customHeight="1"/>
-    <row r="570" ht="19.899999999999999" customHeight="1"/>
-    <row r="571" ht="19.899999999999999" customHeight="1"/>
-    <row r="572" ht="19.899999999999999" customHeight="1"/>
-    <row r="573" ht="19.899999999999999" customHeight="1"/>
-    <row r="574" ht="19.899999999999999" customHeight="1"/>
-    <row r="575" ht="19.899999999999999" customHeight="1"/>
-    <row r="576" ht="19.899999999999999" customHeight="1"/>
-    <row r="577" ht="19.899999999999999" customHeight="1"/>
-    <row r="578" ht="19.899999999999999" customHeight="1"/>
-    <row r="579" ht="19.899999999999999" customHeight="1"/>
-    <row r="580" ht="19.899999999999999" customHeight="1"/>
-    <row r="581" ht="19.899999999999999" customHeight="1"/>
-    <row r="582" ht="19.899999999999999" customHeight="1"/>
-    <row r="583" ht="19.899999999999999" customHeight="1"/>
-    <row r="584" ht="19.899999999999999" customHeight="1"/>
-    <row r="585" ht="19.899999999999999" customHeight="1"/>
-    <row r="586" ht="19.899999999999999" customHeight="1"/>
-    <row r="587" ht="19.899999999999999" customHeight="1"/>
-    <row r="588" ht="19.899999999999999" customHeight="1"/>
-    <row r="589" ht="19.899999999999999" customHeight="1"/>
-    <row r="590" ht="19.899999999999999" customHeight="1"/>
-    <row r="591" ht="19.899999999999999" customHeight="1"/>
-    <row r="592" ht="19.899999999999999" customHeight="1"/>
-    <row r="593" ht="19.899999999999999" customHeight="1"/>
-    <row r="594" ht="19.899999999999999" customHeight="1"/>
-    <row r="595" ht="19.899999999999999" customHeight="1"/>
-    <row r="596" ht="19.899999999999999" customHeight="1"/>
-    <row r="597" ht="19.899999999999999" customHeight="1"/>
-    <row r="598" ht="19.899999999999999" customHeight="1"/>
-    <row r="599" ht="19.899999999999999" customHeight="1"/>
-    <row r="600" ht="19.899999999999999" customHeight="1"/>
-    <row r="601" ht="19.899999999999999" customHeight="1"/>
-    <row r="602" ht="19.899999999999999" customHeight="1"/>
-    <row r="603" ht="19.899999999999999" customHeight="1"/>
-    <row r="604" ht="19.899999999999999" customHeight="1"/>
-    <row r="605" ht="19.899999999999999" customHeight="1"/>
-    <row r="606" ht="19.899999999999999" customHeight="1"/>
-    <row r="607" ht="19.899999999999999" customHeight="1"/>
-    <row r="608" ht="19.899999999999999" customHeight="1"/>
-    <row r="609" ht="19.899999999999999" customHeight="1"/>
-    <row r="610" ht="19.899999999999999" customHeight="1"/>
-    <row r="611" ht="19.899999999999999" customHeight="1"/>
-    <row r="612" ht="19.899999999999999" customHeight="1"/>
-    <row r="613" ht="19.899999999999999" customHeight="1"/>
-    <row r="614" ht="19.899999999999999" customHeight="1"/>
-    <row r="615" ht="19.899999999999999" customHeight="1"/>
-    <row r="616" ht="19.899999999999999" customHeight="1"/>
-    <row r="617" ht="19.899999999999999" customHeight="1"/>
-    <row r="618" ht="19.899999999999999" customHeight="1"/>
-    <row r="619" ht="19.899999999999999" customHeight="1"/>
-    <row r="620" ht="19.899999999999999" customHeight="1"/>
-    <row r="621" ht="19.899999999999999" customHeight="1"/>
-    <row r="622" ht="19.899999999999999" customHeight="1"/>
-    <row r="623" ht="19.899999999999999" customHeight="1"/>
-    <row r="624" ht="19.899999999999999" customHeight="1"/>
-    <row r="625" ht="19.899999999999999" customHeight="1"/>
-    <row r="626" ht="19.899999999999999" customHeight="1"/>
-    <row r="627" ht="19.899999999999999" customHeight="1"/>
-    <row r="628" ht="19.899999999999999" customHeight="1"/>
-    <row r="629" ht="19.899999999999999" customHeight="1"/>
-    <row r="630" ht="19.899999999999999" customHeight="1"/>
-    <row r="631" ht="19.899999999999999" customHeight="1"/>
-    <row r="632" ht="19.899999999999999" customHeight="1"/>
-    <row r="633" ht="19.899999999999999" customHeight="1"/>
-    <row r="634" ht="19.899999999999999" customHeight="1"/>
-    <row r="635" ht="19.899999999999999" customHeight="1"/>
-    <row r="636" ht="19.899999999999999" customHeight="1"/>
-    <row r="637" ht="19.899999999999999" customHeight="1"/>
-    <row r="638" ht="19.899999999999999" customHeight="1"/>
-    <row r="639" ht="19.899999999999999" customHeight="1"/>
-    <row r="640" ht="19.899999999999999" customHeight="1"/>
-    <row r="641" ht="19.899999999999999" customHeight="1"/>
-    <row r="642" ht="19.899999999999999" customHeight="1"/>
-    <row r="643" ht="19.899999999999999" customHeight="1"/>
-    <row r="644" ht="19.899999999999999" customHeight="1"/>
-    <row r="645" ht="19.899999999999999" customHeight="1"/>
-    <row r="646" ht="19.899999999999999" customHeight="1"/>
-    <row r="647" ht="19.899999999999999" customHeight="1"/>
-    <row r="648" ht="19.899999999999999" customHeight="1"/>
-    <row r="649" ht="19.899999999999999" customHeight="1"/>
-    <row r="650" ht="19.899999999999999" customHeight="1"/>
-    <row r="651" ht="19.899999999999999" customHeight="1"/>
-    <row r="652" ht="19.899999999999999" customHeight="1"/>
-    <row r="653" ht="19.899999999999999" customHeight="1"/>
-    <row r="654" ht="19.899999999999999" customHeight="1"/>
+    <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1836">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6673,11 +6673,6 @@
   </si>
   <si>
     <t>waWrHF</t>
-  </si>
-  <si>
-    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
-遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>6Z3QVNZNC9</t>
@@ -6772,12 +6767,231 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
+遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是一款承襲經典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>線上遊戲精髓的全新手機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MMORPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。它將熟悉的角色、華麗的裝備與技能完美移植到行動平台，讓玩家能隨時隨地回味奇蹟世界的感動。
+遊戲主打暢快的戰鬥節奏與豐富的副本挑戰，無論是單人闖關或組隊刷寶，都能體驗到爆棚的打擊感與策略樂趣。自動掛機系統讓玩家輕鬆升級，省下練功時間。此外，特色玩法如自由市場交易、翅膀養成、以及多樣化的競技模式，都將帶給玩家不同以往的奇蹟新體驗。立即下載《奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼》，重溫熱血傳說，再創輝煌！</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進遊戲按切換到設置選單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設置後右邊書籤按兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到郵件收禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝福寶石*30+黃金寶箱+1*5+瑪雅之石*30+綁定金幣*8000+靈魂寶石*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KG666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KIMI666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDLS666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLO666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZY666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*10+祝福寶石*50+火之螢石碎片*50+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+套裝強化石*15+火之螢石碎片+35+冰之螢石碎片+35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+祝福寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*10+祝福寶石*10+水之螢石碎片*50+靈魂寶石*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+綁定金幣*8000+靈魂寶石*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+火之螢石碎片*20+綁定金幣*8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6820,6 +7034,19 @@
       <charset val="136"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -6834,6 +7061,17 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6912,9 +7150,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6939,13 +7177,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6958,6 +7197,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7426,7 +7668,7 @@
         <v>51</v>
       </c>
       <c r="AX1" s="2" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -14726,7 +14968,7 @@
         <v>giftcodesbanner/電鋸果汁大亂鬥-bar.jpg</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>20</v>
@@ -16098,7 +16340,7 @@
         <v>1243</v>
       </c>
       <c r="AX131" s="2" t="str">
-        <f t="shared" ref="AX131:AX172" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
+        <f t="shared" ref="AX131:AX173" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=緋石之心</v>
       </c>
     </row>
@@ -16327,7 +16569,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C172" si="6">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C173" si="6">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -16343,7 +16585,7 @@
         <v>21</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1458</v>
@@ -16810,7 +17052,7 @@
       </c>
     </row>
     <row r="143" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="12" t="s">
         <v>1540</v>
       </c>
       <c r="C143" s="2" t="str">
@@ -16859,7 +17101,7 @@
       </c>
     </row>
     <row r="144" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="14" t="s">
         <v>1550</v>
       </c>
       <c r="C144" s="2" t="str">
@@ -16902,25 +17144,25 @@
       <c r="Q144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="R144" s="13" t="s">
+      <c r="R144" s="14" t="s">
         <v>1560</v>
       </c>
       <c r="S144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="T144" s="13" t="s">
+      <c r="T144" s="14" t="s">
         <v>1561</v>
       </c>
       <c r="U144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="V144" s="13" t="s">
+      <c r="V144" s="14" t="s">
         <v>1562</v>
       </c>
       <c r="W144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="X144" s="13" t="s">
+      <c r="X144" s="14" t="s">
         <v>1563</v>
       </c>
       <c r="Y144" s="2" t="s">
@@ -16932,7 +17174,7 @@
       </c>
     </row>
     <row r="145" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="15" t="s">
         <v>1551</v>
       </c>
       <c r="C145" s="2" t="str">
@@ -16963,7 +17205,7 @@
       </c>
     </row>
     <row r="146" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="14" t="s">
+      <c r="A146" s="15" t="s">
         <v>1552</v>
       </c>
       <c r="C146" s="2" t="str">
@@ -17000,8 +17242,8 @@
       </c>
     </row>
     <row r="147" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="13" t="s">
-        <v>1809</v>
+      <c r="A147" s="14" t="s">
+        <v>1808</v>
       </c>
       <c r="C147" s="2" t="str">
         <f t="shared" si="6"/>
@@ -17037,7 +17279,7 @@
       </c>
     </row>
     <row r="148" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="14" t="s">
+      <c r="A148" s="15" t="s">
         <v>1566</v>
       </c>
       <c r="C148" s="2" t="str">
@@ -17128,7 +17370,7 @@
       </c>
     </row>
     <row r="149" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="14" t="s">
+      <c r="A149" s="15" t="s">
         <v>1567</v>
       </c>
       <c r="C149" s="2" t="str">
@@ -17183,7 +17425,7 @@
       </c>
     </row>
     <row r="150" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="14" t="s">
+      <c r="A150" s="15" t="s">
         <v>1586</v>
       </c>
       <c r="C150" s="2" t="str">
@@ -17220,7 +17462,7 @@
       </c>
     </row>
     <row r="151" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="14" t="s">
+      <c r="A151" s="15" t="s">
         <v>1587</v>
       </c>
       <c r="C151" s="2" t="str">
@@ -17245,35 +17487,35 @@
       <c r="I151" s="2" t="s">
         <v>1597</v>
       </c>
-      <c r="J151" s="15" t="s">
+      <c r="J151" s="16" t="s">
         <v>1591</v>
       </c>
-      <c r="K151" s="15" t="s">
+      <c r="K151" s="16" t="s">
         <v>1592</v>
       </c>
-      <c r="L151" s="15"/>
-      <c r="M151" s="15"/>
-      <c r="N151" s="15"/>
-      <c r="O151" s="15"/>
-      <c r="P151" s="15"/>
-      <c r="Q151" s="15"/>
-      <c r="R151" s="15"/>
-      <c r="S151" s="15"/>
-      <c r="T151" s="15"/>
-      <c r="U151" s="15"/>
-      <c r="V151" s="15"/>
-      <c r="W151" s="15"/>
-      <c r="X151" s="15"/>
-      <c r="Y151" s="15"/>
-      <c r="Z151" s="15"/>
-      <c r="AA151" s="15"/>
+      <c r="L151" s="16"/>
+      <c r="M151" s="16"/>
+      <c r="N151" s="16"/>
+      <c r="O151" s="16"/>
+      <c r="P151" s="16"/>
+      <c r="Q151" s="16"/>
+      <c r="R151" s="16"/>
+      <c r="S151" s="16"/>
+      <c r="T151" s="16"/>
+      <c r="U151" s="16"/>
+      <c r="V151" s="16"/>
+      <c r="W151" s="16"/>
+      <c r="X151" s="16"/>
+      <c r="Y151" s="16"/>
+      <c r="Z151" s="16"/>
+      <c r="AA151" s="16"/>
       <c r="AX151" s="2" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Blue eyes：公會大師</v>
       </c>
     </row>
     <row r="152" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="14" t="s">
         <v>1598</v>
       </c>
       <c r="C152" s="2" t="str">
@@ -17435,7 +17677,7 @@
       <c r="J154" s="2" t="s">
         <v>1641</v>
       </c>
-      <c r="K154" s="13" t="s">
+      <c r="K154" s="14" t="s">
         <v>1642</v>
       </c>
       <c r="L154" s="2" t="s">
@@ -17450,7 +17692,7 @@
       <c r="O154" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="P154" s="13" t="s">
+      <c r="P154" s="14" t="s">
         <v>1646</v>
       </c>
       <c r="Q154" s="2" t="s">
@@ -17468,7 +17710,7 @@
       </c>
     </row>
     <row r="155" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="14" t="s">
+      <c r="A155" s="15" t="s">
         <v>1652</v>
       </c>
       <c r="C155" s="2" t="str">
@@ -17487,28 +17729,28 @@
       <c r="G155" s="2" t="s">
         <v>1662</v>
       </c>
-      <c r="J155" s="16" t="s">
+      <c r="J155" s="17" t="s">
         <v>1655</v>
       </c>
-      <c r="K155" s="17" t="s">
+      <c r="K155" s="18" t="s">
         <v>1656</v>
       </c>
-      <c r="L155" s="16" t="s">
+      <c r="L155" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="M155" s="17" t="s">
+      <c r="M155" s="18" t="s">
         <v>1657</v>
       </c>
-      <c r="N155" s="16" t="s">
+      <c r="N155" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="O155" s="17" t="s">
+      <c r="O155" s="18" t="s">
         <v>1658</v>
       </c>
-      <c r="P155" s="16" t="s">
+      <c r="P155" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Q155" s="17" t="s">
+      <c r="Q155" s="18" t="s">
         <v>1659</v>
       </c>
       <c r="AX155" s="2" t="str">
@@ -17517,7 +17759,7 @@
       </c>
     </row>
     <row r="156" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="14" t="s">
+      <c r="A156" s="15" t="s">
         <v>1651</v>
       </c>
       <c r="C156" s="2" t="str">
@@ -17548,20 +17790,20 @@
       </c>
     </row>
     <row r="157" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="14" t="s">
+      <c r="A157" s="15" t="s">
         <v>1667</v>
       </c>
       <c r="C157" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="D157" s="11" t="s">
         <v>1671</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="F157" s="12" t="s">
+      <c r="F157" s="13" t="s">
         <v>1684</v>
       </c>
       <c r="J157" s="2" t="s">
@@ -17588,14 +17830,14 @@
       </c>
     </row>
     <row r="158" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="14" t="s">
+      <c r="A158" s="15" t="s">
         <v>1668</v>
       </c>
       <c r="C158" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="D158" s="11" t="s">
         <v>1672</v>
       </c>
       <c r="E158" s="2" t="s">
@@ -17625,14 +17867,14 @@
       </c>
     </row>
     <row r="159" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="14" t="s">
+      <c r="A159" s="15" t="s">
         <v>1669</v>
       </c>
       <c r="C159" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D159" s="11" t="s">
         <v>1673</v>
       </c>
       <c r="E159" s="2" t="s">
@@ -17665,14 +17907,14 @@
       </c>
     </row>
     <row r="160" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="14" t="s">
+      <c r="A160" s="15" t="s">
         <v>1695</v>
       </c>
       <c r="C160" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
       </c>
-      <c r="D160" s="10" t="s">
+      <c r="D160" s="11" t="s">
         <v>1674</v>
       </c>
       <c r="E160" s="2" t="s">
@@ -17702,14 +17944,14 @@
       </c>
     </row>
     <row r="161" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="14" t="s">
+      <c r="A161" s="15" t="s">
         <v>1670</v>
       </c>
       <c r="C161" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
       </c>
-      <c r="D161" s="10" t="s">
+      <c r="D161" s="11" t="s">
         <v>1675</v>
       </c>
       <c r="E161" s="2" t="s">
@@ -17739,15 +17981,15 @@
       </c>
     </row>
     <row r="162" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="15" t="s">
         <v>1693</v>
       </c>
       <c r="C162" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
       </c>
-      <c r="D162" s="10" t="s">
-        <v>1810</v>
+      <c r="D162" s="11" t="s">
+        <v>1809</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>1478</v>
@@ -17779,15 +18021,15 @@
       </c>
     </row>
     <row r="163" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="14" t="s">
+      <c r="A163" s="15" t="s">
         <v>1694</v>
       </c>
       <c r="C163" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
       </c>
-      <c r="D163" s="10" t="s">
-        <v>1811</v>
+      <c r="D163" s="11" t="s">
+        <v>1810</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>1478</v>
@@ -17819,7 +18061,7 @@
       </c>
     </row>
     <row r="164" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="14" t="s">
+      <c r="A164" s="15" t="s">
         <v>1696</v>
       </c>
       <c r="C164" s="2" t="str">
@@ -17838,7 +18080,7 @@
       <c r="G164" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="J164" s="13" t="s">
+      <c r="J164" s="14" t="s">
         <v>1700</v>
       </c>
       <c r="K164" s="2" t="s">
@@ -17868,7 +18110,7 @@
       </c>
     </row>
     <row r="165" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="14" t="s">
+      <c r="A165" s="15" t="s">
         <v>1697</v>
       </c>
       <c r="C165" s="2" t="str">
@@ -17908,7 +18150,7 @@
       </c>
     </row>
     <row r="166" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="14" t="s">
+      <c r="A166" s="15" t="s">
         <v>1720</v>
       </c>
       <c r="C166" s="2" t="str">
@@ -17948,7 +18190,7 @@
       </c>
     </row>
     <row r="167" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="14" t="s">
+      <c r="A167" s="15" t="s">
         <v>1711</v>
       </c>
       <c r="C167" s="2" t="str">
@@ -17997,7 +18239,7 @@
       </c>
     </row>
     <row r="168" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="13" t="s">
+      <c r="A168" s="14" t="s">
         <v>1722</v>
       </c>
       <c r="C168" s="2" t="str">
@@ -18034,7 +18276,7 @@
       </c>
     </row>
     <row r="169" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="14" t="s">
+      <c r="A169" s="15" t="s">
         <v>1734</v>
       </c>
       <c r="C169" s="2" t="str">
@@ -18143,7 +18385,7 @@
       </c>
     </row>
     <row r="170" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="14" t="s">
+      <c r="A170" s="15" t="s">
         <v>1735</v>
       </c>
       <c r="C170" s="2" t="str">
@@ -18204,7 +18446,7 @@
       </c>
     </row>
     <row r="171" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="14" t="s">
+      <c r="A171" s="15" t="s">
         <v>1750</v>
       </c>
       <c r="C171" s="2" t="str">
@@ -18241,7 +18483,7 @@
       </c>
     </row>
     <row r="172" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="14" t="s">
+      <c r="A172" s="15" t="s">
         <v>1785</v>
       </c>
       <c r="C172" s="2" t="str">
@@ -18249,7 +18491,7 @@
         <v>giftcodesbanner/大武道-禮包碼.jpg</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>1798</v>
+        <v>1812</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>1786</v>
@@ -18260,78 +18502,159 @@
       <c r="G172" s="2" t="s">
         <v>1788</v>
       </c>
-      <c r="J172" s="16" t="s">
+      <c r="J172" s="17" t="s">
         <v>1789</v>
       </c>
-      <c r="K172" s="17" t="s">
+      <c r="K172" s="18" t="s">
         <v>1790</v>
       </c>
-      <c r="L172" s="16" t="s">
+      <c r="L172" s="17" t="s">
         <v>1791</v>
       </c>
-      <c r="M172" s="17" t="s">
+      <c r="M172" s="18" t="s">
         <v>1792</v>
       </c>
-      <c r="N172" s="16" t="s">
+      <c r="N172" s="17" t="s">
         <v>1793</v>
       </c>
-      <c r="O172" s="17" t="s">
+      <c r="O172" s="18" t="s">
         <v>1790</v>
       </c>
-      <c r="P172" s="16" t="s">
+      <c r="P172" s="17" t="s">
         <v>1794</v>
       </c>
-      <c r="Q172" s="17" t="s">
+      <c r="Q172" s="18" t="s">
         <v>1792</v>
       </c>
-      <c r="R172" s="16" t="s">
+      <c r="R172" s="17" t="s">
         <v>1795</v>
       </c>
-      <c r="S172" s="17" t="s">
+      <c r="S172" s="18" t="s">
         <v>1790</v>
       </c>
-      <c r="T172" s="16" t="s">
+      <c r="T172" s="17" t="s">
         <v>1796</v>
       </c>
-      <c r="U172" s="17" t="s">
+      <c r="U172" s="18" t="s">
         <v>1792</v>
       </c>
-      <c r="V172" s="16" t="s">
+      <c r="V172" s="17" t="s">
         <v>1797</v>
       </c>
-      <c r="W172" s="17" t="s">
+      <c r="W172" s="18" t="s">
         <v>1790</v>
       </c>
       <c r="X172" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="Y172" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="Z172" s="2" t="s">
         <v>1799</v>
       </c>
-      <c r="Y172" s="2" t="s">
+      <c r="AA172" s="2" t="s">
         <v>1803</v>
       </c>
-      <c r="Z172" s="2" t="s">
+      <c r="AB172" s="2" t="s">
         <v>1800</v>
       </c>
-      <c r="AA172" s="2" t="s">
+      <c r="AC172" s="2" t="s">
         <v>1804</v>
       </c>
-      <c r="AB172" s="2" t="s">
+      <c r="AD172" s="2" t="s">
         <v>1801</v>
       </c>
-      <c r="AC172" s="2" t="s">
+      <c r="AE172" s="2" t="s">
         <v>1805</v>
-      </c>
-      <c r="AD172" s="2" t="s">
-        <v>1802</v>
-      </c>
-      <c r="AE172" s="2" t="s">
-        <v>1806</v>
       </c>
       <c r="AX172" s="2" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=大武道</v>
       </c>
     </row>
-    <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="10" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C173" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/奇蹟MU：爆走之翼-禮包碼.jpg</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>1813</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="N173" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="O173" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="P173" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="Q173" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="R173" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="S173" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="T173" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="U173" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="V173" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="W173" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="X173" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="Y173" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="Z173" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AA173" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AX173" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=奇蹟MU：爆走之翼</v>
+      </c>
+    </row>
     <row r="174" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="175" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -6770,6 +6770,122 @@
   <si>
     <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
 遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進遊戲按切換到設置選單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設置後右邊書籤按兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到郵件收禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝福寶石*30+黃金寶箱+1*5+瑪雅之石*30+綁定金幣*8000+靈魂寶石*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KG666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KIMI666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDLS666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLO666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZY666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*10+祝福寶石*50+火之螢石碎片*50+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+套裝強化石*15+火之螢石碎片+35+冰之螢石碎片+35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+祝福寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*10+祝福寶石*10+水之螢石碎片*50+靈魂寶石*50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+綁定金幣*8000+靈魂寶石*30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+火之螢石碎片*20+綁定金幣*8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：暴走之翼</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6797,7 +6913,7 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>：爆走之翼</t>
+      <t>：暴走之翼</t>
     </r>
     <r>
       <rPr>
@@ -6866,124 +6982,8 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>：爆走之翼》，重溫熱血傳說，再創輝煌！</t>
+      <t>：暴走之翼》，重溫熱血傳說，再創輝煌！</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>奇蹟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：爆走之翼</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進遊戲按切換到設置選單</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入設置後右邊書籤按兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到郵件收禮包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>祝福寶石*30+黃金寶箱+1*5+瑪雅之石*30+綁定金幣*8000+靈魂寶石*30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KG666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KIMI666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HDLS666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CG666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MLO666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZY666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>套裝強化石*10+祝福寶石*50+火之螢石碎片*50+靈魂寶石*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之螢石碎片*35+套裝強化石*15+火之螢石碎片+35+冰之螢石碎片+35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+祝福寶石*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>套裝強化石*10+祝福寶石*10+水之螢石碎片*50+靈魂寶石*50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水之螢石碎片*35+火之螢石碎片+35+冰之螢石碎片+35+靈魂寶石*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+綁定金幣*8000+靈魂寶石*30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>套裝強化石*30+祝福寶石*30+黃金寶箱+1*5+火之螢石碎片*20+綁定金幣*8000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18575,84 +18575,84 @@
     </row>
     <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
-        <v>1814</v>
+        <v>1834</v>
       </c>
       <c r="C173" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>giftcodesbanner/奇蹟MU：爆走之翼-禮包碼.jpg</v>
+        <v>giftcodesbanner/奇蹟MU：暴走之翼-禮包碼.jpg</v>
       </c>
       <c r="D173" s="19" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>1813</v>
       </c>
-      <c r="E173" s="2" t="s">
-        <v>1815</v>
-      </c>
       <c r="F173" s="2" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>1738</v>
       </c>
       <c r="H173" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="K173" s="2" t="s">
         <v>1817</v>
       </c>
-      <c r="J173" s="2" t="s">
+      <c r="L173" s="2" t="s">
         <v>1818</v>
       </c>
-      <c r="K173" s="2" t="s">
+      <c r="M173" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="N173" s="2" t="s">
         <v>1819</v>
       </c>
-      <c r="L173" s="2" t="s">
+      <c r="O173" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="P173" s="2" t="s">
         <v>1820</v>
       </c>
-      <c r="M173" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="N173" s="2" t="s">
+      <c r="Q173" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="R173" s="2" t="s">
         <v>1821</v>
       </c>
-      <c r="O173" s="2" t="s">
-        <v>1835</v>
-      </c>
-      <c r="P173" s="2" t="s">
+      <c r="S173" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="T173" s="2" t="s">
         <v>1822</v>
       </c>
-      <c r="Q173" s="2" t="s">
-        <v>1833</v>
-      </c>
-      <c r="R173" s="2" t="s">
+      <c r="U173" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="V173" s="2" t="s">
         <v>1823</v>
       </c>
-      <c r="S173" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="T173" s="2" t="s">
+      <c r="W173" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="X173" s="2" t="s">
         <v>1824</v>
       </c>
-      <c r="U173" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="V173" s="2" t="s">
+      <c r="Y173" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="Z173" s="2" t="s">
         <v>1825</v>
       </c>
-      <c r="W173" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="X173" s="2" t="s">
+      <c r="AA173" s="2" t="s">
         <v>1826</v>
-      </c>
-      <c r="Y173" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="Z173" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="AA173" s="2" t="s">
-        <v>1828</v>
       </c>
       <c r="AX173" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>https://www.ssbuy.tw/gift-codes.html?game=奇蹟MU：爆走之翼</v>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=奇蹟MU：暴走之翼</v>
       </c>
     </row>
     <row r="174" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="1861">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -6986,6 +6986,106 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>劍太傳說：新的開始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三國。群英燎原</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《劍太傳說：新的開始》是一款東方武俠風格的MMORPG手遊，以精緻的畫面和廣闊的開放世界，邀請玩家踏入一個充滿傳奇的江湖。在遊戲中，你將扮演一位身懷絕技的武林人士，透過修煉各式武學、參與豐富的劇情任務，逐步揭開這片土地的秘密。遊戲提供多樣化的副本挑戰、緊張刺激的熱血幫戰以及考驗實力的跨服競技。為了您的遊戲體驗，我們也提供快速儲值服務，確保您能即時獲得所需資源，享受流暢的遊戲過程。立即加入《劍太傳說》，開啟你的專屬武俠傳奇，譜寫一個全新的江湖篇章！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三國。群英燎原》是一款以經典三國歷史為背景的策略戰爭手遊。在這款遊戲中，玩家將穿越時空，化身一方霸主，親身體驗亂世之中爾虞我詐的權謀鬥爭。你的任務是招募並培養眾多耳熟能詳的三國傳奇武將，發展壯大自己的城池與勢力，並巧妙地調兵遣將，與其他玩家展開激烈的攻城掠地。遊戲的核心玩法著重於策略性的佈陣與即時戰鬥，搭配豐富的武將養成系統。我們提供安全儲值與正規儲值管道，讓您在擴張霸業的同時，能安心無虞地補充戰力。唯有深謀遠慮、知人善任，才能在這群雄割據的亂世中點燃燎原戰火，最終一統三國！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kenta666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kenta777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kenta888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>銀幣*5萬、元寶*50、召喚券*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>銀幣*5萬、元寶*50、召喚券*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲主畫面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選左上角頭像。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇「兌換碼兌換」。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入禮包碼並確認領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到「禮包碼」或「禮包碼兌換」選項。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入禮包碼並點擊「立即兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊右下角的十字進入「選單」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇「系統設定」。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WYM666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WYM888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*50+輜重箱*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*50+高級募兵令*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄技能包*10+生鐵*20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄技能包*10+木材*20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -7074,12 +7174,18 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -7152,7 +7258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7178,6 +7284,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -16340,7 +16449,7 @@
         <v>1243</v>
       </c>
       <c r="AX131" s="2" t="str">
-        <f t="shared" ref="AX131:AX173" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
+        <f t="shared" ref="AX131:AX180" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=緋石之心</v>
       </c>
     </row>
@@ -16569,7 +16678,7 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C173" si="6">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C175" si="6">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -17052,7 +17161,7 @@
       </c>
     </row>
     <row r="143" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="12" t="s">
+      <c r="A143" s="13" t="s">
         <v>1540</v>
       </c>
       <c r="C143" s="2" t="str">
@@ -17101,7 +17210,7 @@
       </c>
     </row>
     <row r="144" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="15" t="s">
         <v>1550</v>
       </c>
       <c r="C144" s="2" t="str">
@@ -17144,25 +17253,25 @@
       <c r="Q144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="R144" s="14" t="s">
+      <c r="R144" s="15" t="s">
         <v>1560</v>
       </c>
       <c r="S144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="T144" s="14" t="s">
+      <c r="T144" s="15" t="s">
         <v>1561</v>
       </c>
       <c r="U144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="V144" s="14" t="s">
+      <c r="V144" s="15" t="s">
         <v>1562</v>
       </c>
       <c r="W144" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="X144" s="14" t="s">
+      <c r="X144" s="15" t="s">
         <v>1563</v>
       </c>
       <c r="Y144" s="2" t="s">
@@ -17174,7 +17283,7 @@
       </c>
     </row>
     <row r="145" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="15" t="s">
+      <c r="A145" s="16" t="s">
         <v>1551</v>
       </c>
       <c r="C145" s="2" t="str">
@@ -17205,7 +17314,7 @@
       </c>
     </row>
     <row r="146" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="15" t="s">
+      <c r="A146" s="16" t="s">
         <v>1552</v>
       </c>
       <c r="C146" s="2" t="str">
@@ -17242,7 +17351,7 @@
       </c>
     </row>
     <row r="147" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="14" t="s">
+      <c r="A147" s="15" t="s">
         <v>1808</v>
       </c>
       <c r="C147" s="2" t="str">
@@ -17279,7 +17388,7 @@
       </c>
     </row>
     <row r="148" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="15" t="s">
+      <c r="A148" s="16" t="s">
         <v>1566</v>
       </c>
       <c r="C148" s="2" t="str">
@@ -17370,7 +17479,7 @@
       </c>
     </row>
     <row r="149" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="15" t="s">
+      <c r="A149" s="16" t="s">
         <v>1567</v>
       </c>
       <c r="C149" s="2" t="str">
@@ -17425,7 +17534,7 @@
       </c>
     </row>
     <row r="150" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="15" t="s">
+      <c r="A150" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="C150" s="2" t="str">
@@ -17462,7 +17571,7 @@
       </c>
     </row>
     <row r="151" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="15" t="s">
+      <c r="A151" s="16" t="s">
         <v>1587</v>
       </c>
       <c r="C151" s="2" t="str">
@@ -17487,35 +17596,35 @@
       <c r="I151" s="2" t="s">
         <v>1597</v>
       </c>
-      <c r="J151" s="16" t="s">
+      <c r="J151" s="17" t="s">
         <v>1591</v>
       </c>
-      <c r="K151" s="16" t="s">
+      <c r="K151" s="17" t="s">
         <v>1592</v>
       </c>
-      <c r="L151" s="16"/>
-      <c r="M151" s="16"/>
-      <c r="N151" s="16"/>
-      <c r="O151" s="16"/>
-      <c r="P151" s="16"/>
-      <c r="Q151" s="16"/>
-      <c r="R151" s="16"/>
-      <c r="S151" s="16"/>
-      <c r="T151" s="16"/>
-      <c r="U151" s="16"/>
-      <c r="V151" s="16"/>
-      <c r="W151" s="16"/>
-      <c r="X151" s="16"/>
-      <c r="Y151" s="16"/>
-      <c r="Z151" s="16"/>
-      <c r="AA151" s="16"/>
+      <c r="L151" s="17"/>
+      <c r="M151" s="17"/>
+      <c r="N151" s="17"/>
+      <c r="O151" s="17"/>
+      <c r="P151" s="17"/>
+      <c r="Q151" s="17"/>
+      <c r="R151" s="17"/>
+      <c r="S151" s="17"/>
+      <c r="T151" s="17"/>
+      <c r="U151" s="17"/>
+      <c r="V151" s="17"/>
+      <c r="W151" s="17"/>
+      <c r="X151" s="17"/>
+      <c r="Y151" s="17"/>
+      <c r="Z151" s="17"/>
+      <c r="AA151" s="17"/>
       <c r="AX151" s="2" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Blue eyes：公會大師</v>
       </c>
     </row>
     <row r="152" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="15" t="s">
         <v>1598</v>
       </c>
       <c r="C152" s="2" t="str">
@@ -17677,7 +17786,7 @@
       <c r="J154" s="2" t="s">
         <v>1641</v>
       </c>
-      <c r="K154" s="14" t="s">
+      <c r="K154" s="15" t="s">
         <v>1642</v>
       </c>
       <c r="L154" s="2" t="s">
@@ -17692,7 +17801,7 @@
       <c r="O154" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="P154" s="14" t="s">
+      <c r="P154" s="15" t="s">
         <v>1646</v>
       </c>
       <c r="Q154" s="2" t="s">
@@ -17710,7 +17819,7 @@
       </c>
     </row>
     <row r="155" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="15" t="s">
+      <c r="A155" s="16" t="s">
         <v>1652</v>
       </c>
       <c r="C155" s="2" t="str">
@@ -17729,28 +17838,28 @@
       <c r="G155" s="2" t="s">
         <v>1662</v>
       </c>
-      <c r="J155" s="17" t="s">
+      <c r="J155" s="18" t="s">
         <v>1655</v>
       </c>
-      <c r="K155" s="18" t="s">
+      <c r="K155" s="19" t="s">
         <v>1656</v>
       </c>
-      <c r="L155" s="17" t="s">
+      <c r="L155" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="M155" s="18" t="s">
+      <c r="M155" s="19" t="s">
         <v>1657</v>
       </c>
-      <c r="N155" s="17" t="s">
+      <c r="N155" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="O155" s="18" t="s">
+      <c r="O155" s="19" t="s">
         <v>1658</v>
       </c>
-      <c r="P155" s="17" t="s">
+      <c r="P155" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q155" s="18" t="s">
+      <c r="Q155" s="19" t="s">
         <v>1659</v>
       </c>
       <c r="AX155" s="2" t="str">
@@ -17759,7 +17868,7 @@
       </c>
     </row>
     <row r="156" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="15" t="s">
+      <c r="A156" s="16" t="s">
         <v>1651</v>
       </c>
       <c r="C156" s="2" t="str">
@@ -17790,20 +17899,20 @@
       </c>
     </row>
     <row r="157" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="15" t="s">
+      <c r="A157" s="16" t="s">
         <v>1667</v>
       </c>
       <c r="C157" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
       </c>
-      <c r="D157" s="11" t="s">
+      <c r="D157" s="12" t="s">
         <v>1671</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="F157" s="13" t="s">
+      <c r="F157" s="14" t="s">
         <v>1684</v>
       </c>
       <c r="J157" s="2" t="s">
@@ -17830,14 +17939,14 @@
       </c>
     </row>
     <row r="158" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="15" t="s">
+      <c r="A158" s="16" t="s">
         <v>1668</v>
       </c>
       <c r="C158" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
       </c>
-      <c r="D158" s="11" t="s">
+      <c r="D158" s="12" t="s">
         <v>1672</v>
       </c>
       <c r="E158" s="2" t="s">
@@ -17867,14 +17976,14 @@
       </c>
     </row>
     <row r="159" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="15" t="s">
+      <c r="A159" s="16" t="s">
         <v>1669</v>
       </c>
       <c r="C159" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
       </c>
-      <c r="D159" s="11" t="s">
+      <c r="D159" s="12" t="s">
         <v>1673</v>
       </c>
       <c r="E159" s="2" t="s">
@@ -17907,14 +18016,14 @@
       </c>
     </row>
     <row r="160" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="16" t="s">
         <v>1695</v>
       </c>
       <c r="C160" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
       </c>
-      <c r="D160" s="11" t="s">
+      <c r="D160" s="12" t="s">
         <v>1674</v>
       </c>
       <c r="E160" s="2" t="s">
@@ -17944,14 +18053,14 @@
       </c>
     </row>
     <row r="161" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="15" t="s">
+      <c r="A161" s="16" t="s">
         <v>1670</v>
       </c>
       <c r="C161" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
       </c>
-      <c r="D161" s="11" t="s">
+      <c r="D161" s="12" t="s">
         <v>1675</v>
       </c>
       <c r="E161" s="2" t="s">
@@ -17981,14 +18090,14 @@
       </c>
     </row>
     <row r="162" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="15" t="s">
+      <c r="A162" s="16" t="s">
         <v>1693</v>
       </c>
       <c r="C162" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
       </c>
-      <c r="D162" s="11" t="s">
+      <c r="D162" s="12" t="s">
         <v>1809</v>
       </c>
       <c r="E162" s="2" t="s">
@@ -18021,14 +18130,14 @@
       </c>
     </row>
     <row r="163" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="15" t="s">
+      <c r="A163" s="16" t="s">
         <v>1694</v>
       </c>
       <c r="C163" s="2" t="str">
         <f t="shared" si="6"/>
         <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
       </c>
-      <c r="D163" s="11" t="s">
+      <c r="D163" s="12" t="s">
         <v>1810</v>
       </c>
       <c r="E163" s="2" t="s">
@@ -18061,7 +18170,7 @@
       </c>
     </row>
     <row r="164" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="15" t="s">
+      <c r="A164" s="16" t="s">
         <v>1696</v>
       </c>
       <c r="C164" s="2" t="str">
@@ -18080,7 +18189,7 @@
       <c r="G164" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="J164" s="14" t="s">
+      <c r="J164" s="15" t="s">
         <v>1700</v>
       </c>
       <c r="K164" s="2" t="s">
@@ -18110,7 +18219,7 @@
       </c>
     </row>
     <row r="165" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="15" t="s">
+      <c r="A165" s="16" t="s">
         <v>1697</v>
       </c>
       <c r="C165" s="2" t="str">
@@ -18150,7 +18259,7 @@
       </c>
     </row>
     <row r="166" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="15" t="s">
+      <c r="A166" s="16" t="s">
         <v>1720</v>
       </c>
       <c r="C166" s="2" t="str">
@@ -18190,7 +18299,7 @@
       </c>
     </row>
     <row r="167" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="15" t="s">
+      <c r="A167" s="16" t="s">
         <v>1711</v>
       </c>
       <c r="C167" s="2" t="str">
@@ -18239,7 +18348,7 @@
       </c>
     </row>
     <row r="168" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="14" t="s">
+      <c r="A168" s="15" t="s">
         <v>1722</v>
       </c>
       <c r="C168" s="2" t="str">
@@ -18276,7 +18385,7 @@
       </c>
     </row>
     <row r="169" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="15" t="s">
+      <c r="A169" s="16" t="s">
         <v>1734</v>
       </c>
       <c r="C169" s="2" t="str">
@@ -18385,7 +18494,7 @@
       </c>
     </row>
     <row r="170" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="15" t="s">
+      <c r="A170" s="16" t="s">
         <v>1735</v>
       </c>
       <c r="C170" s="2" t="str">
@@ -18446,7 +18555,7 @@
       </c>
     </row>
     <row r="171" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="15" t="s">
+      <c r="A171" s="16" t="s">
         <v>1750</v>
       </c>
       <c r="C171" s="2" t="str">
@@ -18483,7 +18592,7 @@
       </c>
     </row>
     <row r="172" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="15" t="s">
+      <c r="A172" s="16" t="s">
         <v>1785</v>
       </c>
       <c r="C172" s="2" t="str">
@@ -18502,46 +18611,46 @@
       <c r="G172" s="2" t="s">
         <v>1788</v>
       </c>
-      <c r="J172" s="17" t="s">
+      <c r="J172" s="18" t="s">
         <v>1789</v>
       </c>
-      <c r="K172" s="18" t="s">
+      <c r="K172" s="19" t="s">
         <v>1790</v>
       </c>
-      <c r="L172" s="17" t="s">
+      <c r="L172" s="18" t="s">
         <v>1791</v>
       </c>
-      <c r="M172" s="18" t="s">
+      <c r="M172" s="19" t="s">
         <v>1792</v>
       </c>
-      <c r="N172" s="17" t="s">
+      <c r="N172" s="18" t="s">
         <v>1793</v>
       </c>
-      <c r="O172" s="18" t="s">
+      <c r="O172" s="19" t="s">
         <v>1790</v>
       </c>
-      <c r="P172" s="17" t="s">
+      <c r="P172" s="18" t="s">
         <v>1794</v>
       </c>
-      <c r="Q172" s="18" t="s">
+      <c r="Q172" s="19" t="s">
         <v>1792</v>
       </c>
-      <c r="R172" s="17" t="s">
+      <c r="R172" s="18" t="s">
         <v>1795</v>
       </c>
-      <c r="S172" s="18" t="s">
+      <c r="S172" s="19" t="s">
         <v>1790</v>
       </c>
-      <c r="T172" s="17" t="s">
+      <c r="T172" s="18" t="s">
         <v>1796</v>
       </c>
-      <c r="U172" s="18" t="s">
+      <c r="U172" s="19" t="s">
         <v>1792</v>
       </c>
-      <c r="V172" s="17" t="s">
+      <c r="V172" s="18" t="s">
         <v>1797</v>
       </c>
-      <c r="W172" s="18" t="s">
+      <c r="W172" s="19" t="s">
         <v>1790</v>
       </c>
       <c r="X172" s="2" t="s">
@@ -18573,7 +18682,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=大武道</v>
       </c>
     </row>
-    <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>1834</v>
       </c>
@@ -18581,7 +18690,7 @@
         <f t="shared" si="6"/>
         <v>giftcodesbanner/奇蹟MU：暴走之翼-禮包碼.jpg</v>
       </c>
-      <c r="D173" s="19" t="s">
+      <c r="D173" s="20" t="s">
         <v>1835</v>
       </c>
       <c r="E173" s="2" t="s">
@@ -18655,8 +18764,104 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=奇蹟MU：暴走之翼</v>
       </c>
     </row>
-    <row r="174" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="11" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C174" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/劍太傳說：新的開始-禮包碼.jpg</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="N174" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="O174" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AX174" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=劍太傳說：新的開始</v>
+      </c>
+    </row>
+    <row r="175" spans="1:50" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="11" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C175" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>giftcodesbanner/三國。群英燎原-禮包碼.jpg</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N175" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="O175" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="P175" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="Q175" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AX175" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=三國。群英燎原</v>
+      </c>
+    </row>
     <row r="176" spans="1:50" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="177" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="178" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="1863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="1872">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7051,47 +7051,82 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>WYM666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WYM888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*50+輜重箱*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*50+高級募兵令*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄技能包*10+生鐵*20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄技能包*10+木材*20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fbkenta0801</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶×50、英雄召喚券×1、銀幣×5W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final War：寒霜前線</t>
+  </si>
+  <si>
+    <t>《Final War：寒霜前線》是一款引人入勝的末日冰雪主題策略生存手遊。在這個被冰雪覆蓋的嚴酷世界中，你將扮演指揮官，肩負著重建人類文明的重任。遊戲核心玩法融合了資源管理、基地建設與英雄養成，你需要抵抗酷寒、抵禦來襲的猛獸與敵對勢力。獨特的熔爐系統是維持溫暖與希望的關鍵。招募各具特色的英雄，搭配不同兵種，制定你的生存策略，並與全球玩家結盟或對抗。準備好在這場終極寒霜戰爭中，點燃文明的最後火種，帶領你的人民走向新生嗎？立即下載，體驗極致的生存挑戰與策略博弈！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進遊戲主畫面後按左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>選擇「系統設定」。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WYM666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WYM888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元寶*50+輜重箱*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元寶*50+高級募兵令*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CSC666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄技能包*10+生鐵*20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CSC888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄技能包*10+木材*20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fbkenta0801</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元寶×50、英雄召喚券×1、銀幣×5W</t>
+    <t>畫面右方按「設定」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>往左滑找到獎勵兌換</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入禮包碼並點擊「獎勵兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑夜獵人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《黑夜獵人：專治吸血鬼、殭屍與各種不服》是一款主打休閒塔防與策略對抗的哥德風手遊。你將化身為一名強大的吸血鬼獵人，在暗夜中佈下天羅地網，抵禦一波波來襲的殭屍、狼人與吸血鬼大軍。遊戲核心玩法是策略性地放置和升級你的防禦單位，結合英雄技能，消滅所有敵人。告別複雜操作，享受單手即可暢玩的割草快感與塔防樂趣。準備好運用你的智慧，建造最強防線，成為讓所有黑暗生物聞風喪膽的終極獵人了嗎？立即下載，體驗這場刺激又爽快的暗夜狩獵！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7266,7 +7301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7317,6 +7352,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7795,7 +7833,7 @@
         <v>giftcodesbanner/巔峰極速-bar.jpg</v>
       </c>
       <c r="D2" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A2</f>
+        <f t="shared" ref="D2:D33" si="0">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A2</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=巔峰極速</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -7930,11 +7968,11 @@
         <v>108</v>
       </c>
       <c r="B3" s="2" t="str">
-        <f t="shared" ref="B3:B66" si="0">"giftcodesbanner/" &amp; A3 &amp; "-bar.jpg"</f>
+        <f t="shared" ref="B3:B66" si="1">"giftcodesbanner/" &amp; A3 &amp; "-bar.jpg"</f>
         <v>giftcodesbanner/原神-bar.jpg</v>
       </c>
       <c r="D3" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A3</f>
+        <f t="shared" si="0"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=原神</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -7979,11 +8017,11 @@
         <v>109</v>
       </c>
       <c r="B4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/極速快感-bar.jpg</v>
+      </c>
+      <c r="D4" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/極速快感-bar.jpg</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A4</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=極速快感</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -8025,11 +8063,11 @@
         <v>110</v>
       </c>
       <c r="B5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/俠客傳說：小小英雄-bar.jpg</v>
+      </c>
+      <c r="D5" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/俠客傳說：小小英雄-bar.jpg</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A5</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=俠客傳說：小小英雄</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -8128,11 +8166,11 @@
         <v>111</v>
       </c>
       <c r="B6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/逆水寒-bar.jpg</v>
+      </c>
+      <c r="D6" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/逆水寒-bar.jpg</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A6</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=逆水寒</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -8159,11 +8197,11 @@
         <v>112</v>
       </c>
       <c r="B7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/RO仙境傳說：一定要可愛-bar.jpg</v>
+      </c>
+      <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/RO仙境傳說：一定要可愛-bar.jpg</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A7</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：一定要可愛</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -8226,11 +8264,11 @@
         <v>113</v>
       </c>
       <c r="B8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/RO新世代-bar.jpg</v>
+      </c>
+      <c r="D8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/RO新世代-bar.jpg</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A8</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO新世代</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -8287,11 +8325,11 @@
         <v>114</v>
       </c>
       <c r="B9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/上古：龍神覺醒-bar.jpg</v>
+      </c>
+      <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/上古：龍神覺醒-bar.jpg</v>
-      </c>
-      <c r="D9" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A9</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=上古：龍神覺醒</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -8384,11 +8422,11 @@
         <v>115</v>
       </c>
       <c r="B10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/小艦艦超勇-bar.jpg</v>
+      </c>
+      <c r="D10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/小艦艦超勇-bar.jpg</v>
-      </c>
-      <c r="D10" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A10</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小艦艦超勇</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -8457,11 +8495,11 @@
         <v>116</v>
       </c>
       <c r="B11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/天使軍團-bar.jpg</v>
+      </c>
+      <c r="D11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/天使軍團-bar.jpg</v>
-      </c>
-      <c r="D11" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A11</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=天使軍團</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -8500,11 +8538,11 @@
         <v>117</v>
       </c>
       <c r="B12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/天堂W-bar.jpg</v>
+      </c>
+      <c r="D12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/天堂W-bar.jpg</v>
-      </c>
-      <c r="D12" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A12</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=天堂W</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8537,11 +8575,11 @@
         <v>118</v>
       </c>
       <c r="B13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/少女前線2：追放-bar.jpg</v>
+      </c>
+      <c r="D13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/少女前線2：追放-bar.jpg</v>
-      </c>
-      <c r="D13" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A13</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=少女前線2：追放</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -8610,11 +8648,11 @@
         <v>119</v>
       </c>
       <c r="B14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/幻獸傳說Ｍ-bar.jpg</v>
+      </c>
+      <c r="D14" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/幻獸傳說Ｍ-bar.jpg</v>
-      </c>
-      <c r="D14" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A14</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=幻獸傳說Ｍ</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -8707,11 +8745,11 @@
         <v>120</v>
       </c>
       <c r="B15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/未定事件簿-bar.jpg</v>
+      </c>
+      <c r="D15" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/未定事件簿-bar.jpg</v>
-      </c>
-      <c r="D15" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A15</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=未定事件簿</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -8762,11 +8800,11 @@
         <v>121</v>
       </c>
       <c r="B16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/永恆靈魂-bar.jpg</v>
+      </c>
+      <c r="D16" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/永恆靈魂-bar.jpg</v>
-      </c>
-      <c r="D16" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A16</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=永恆靈魂</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -8793,11 +8831,11 @@
         <v>122</v>
       </c>
       <c r="B17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/守住呀主公-bar.jpg</v>
+      </c>
+      <c r="D17" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/守住呀主公-bar.jpg</v>
-      </c>
-      <c r="D17" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A17</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=守住呀主公</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -8860,11 +8898,11 @@
         <v>123</v>
       </c>
       <c r="B18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/吟遊戰記-bar.jpg</v>
+      </c>
+      <c r="D18" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/吟遊戰記-bar.jpg</v>
-      </c>
-      <c r="D18" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A18</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=吟遊戰記</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -8909,11 +8947,11 @@
         <v>124</v>
       </c>
       <c r="B19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/我獨自升級：ARISE-bar.jpg</v>
+      </c>
+      <c r="D19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/我獨自升級：ARISE-bar.jpg</v>
-      </c>
-      <c r="D19" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A19</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=我獨自升級：ARISE</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -8982,11 +9020,11 @@
         <v>125</v>
       </c>
       <c r="B20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/命運聖契：少女的羈絆-bar.jpg</v>
+      </c>
+      <c r="D20" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/命運聖契：少女的羈絆-bar.jpg</v>
-      </c>
-      <c r="D20" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A20</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=命運聖契：少女的羈絆</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -9073,11 +9111,11 @@
         <v>126</v>
       </c>
       <c r="B21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/放置軍團-bar.jpg</v>
+      </c>
+      <c r="D21" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/放置軍團-bar.jpg</v>
-      </c>
-      <c r="D21" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A21</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=放置軍團</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -9128,11 +9166,11 @@
         <v>127</v>
       </c>
       <c r="B22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/明日方舟-bar.jpg</v>
+      </c>
+      <c r="D22" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/明日方舟-bar.jpg</v>
-      </c>
-      <c r="D22" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A22</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=明日方舟</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -9159,11 +9197,11 @@
         <v>128</v>
       </c>
       <c r="B23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/屍鬼三國-bar.jpg</v>
+      </c>
+      <c r="D23" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/屍鬼三國-bar.jpg</v>
-      </c>
-      <c r="D23" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A23</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=屍鬼三國</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -9244,11 +9282,11 @@
         <v>129</v>
       </c>
       <c r="B24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/星鏈計畫：未來少女-bar.jpg</v>
+      </c>
+      <c r="D24" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/星鏈計畫：未來少女-bar.jpg</v>
-      </c>
-      <c r="D24" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A24</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星鏈計畫：未來少女</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -9305,11 +9343,11 @@
         <v>130</v>
       </c>
       <c r="B25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/英雄之王-bar.jpg</v>
+      </c>
+      <c r="D25" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/英雄之王-bar.jpg</v>
-      </c>
-      <c r="D25" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A25</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=英雄之王</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -9384,11 +9422,11 @@
         <v>131</v>
       </c>
       <c r="B26" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/英雄聯盟-bar.jpg</v>
+      </c>
+      <c r="D26" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/英雄聯盟-bar.jpg</v>
-      </c>
-      <c r="D26" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A26</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=英雄聯盟</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -9418,11 +9456,11 @@
         <v>132</v>
       </c>
       <c r="B27" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/恐龍突變-bar.jpg</v>
+      </c>
+      <c r="D27" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/恐龍突變-bar.jpg</v>
-      </c>
-      <c r="D27" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A27</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=恐龍突變</v>
       </c>
       <c r="E27" s="8" t="s">
@@ -9443,11 +9481,11 @@
         <v>133</v>
       </c>
       <c r="B28" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/神域-bar.jpg</v>
+      </c>
+      <c r="D28" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/神域-bar.jpg</v>
-      </c>
-      <c r="D28" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A28</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=神域</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -9480,11 +9518,11 @@
         <v>134</v>
       </c>
       <c r="B29" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/崩壞：星穹鐵道-bar.jpg</v>
+      </c>
+      <c r="D29" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/崩壞：星穹鐵道-bar.jpg</v>
-      </c>
-      <c r="D29" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A29</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=崩壞：星穹鐵道</v>
       </c>
       <c r="E29" s="8" t="s">
@@ -9511,11 +9549,11 @@
         <v>135</v>
       </c>
       <c r="B30" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/救世者之樹：新世界-bar.jpg</v>
+      </c>
+      <c r="D30" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/救世者之樹：新世界-bar.jpg</v>
-      </c>
-      <c r="D30" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A30</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=救世者之樹：新世界</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -9584,11 +9622,11 @@
         <v>136</v>
       </c>
       <c r="B31" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/球球英雄-bar.jpg</v>
+      </c>
+      <c r="D31" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/球球英雄-bar.jpg</v>
-      </c>
-      <c r="D31" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A31</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=球球英雄</v>
       </c>
       <c r="E31" s="8" t="s">
@@ -9627,11 +9665,11 @@
         <v>137</v>
       </c>
       <c r="B32" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/第七史詩-bar.jpg</v>
+      </c>
+      <c r="D32" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/第七史詩-bar.jpg</v>
-      </c>
-      <c r="D32" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A32</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=第七史詩</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -9658,11 +9696,11 @@
         <v>138</v>
       </c>
       <c r="B33" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>giftcodesbanner/創世紀戰M：阿修羅計畫-bar.jpg</v>
+      </c>
+      <c r="D33" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>giftcodesbanner/創世紀戰M：阿修羅計畫-bar.jpg</v>
-      </c>
-      <c r="D33" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A33</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=創世紀戰M：阿修羅計畫</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -9749,11 +9787,11 @@
         <v>139</v>
       </c>
       <c r="B34" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/最強宗師-bar.jpg</v>
       </c>
       <c r="D34" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A34</f>
+        <f t="shared" ref="D34:D65" si="2">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A34</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=最強宗師</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -9846,11 +9884,11 @@
         <v>140</v>
       </c>
       <c r="B35" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/無期迷途-bar.jpg</v>
       </c>
       <c r="D35" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A35</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=無期迷途</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -9895,11 +9933,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/絕區零-bar.jpg</v>
       </c>
       <c r="D36" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A36</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=絕區零</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -9962,11 +10000,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/傳說對決-bar.jpg</v>
       </c>
       <c r="D37" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A37</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=傳說對決</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -9999,11 +10037,11 @@
         <v>336</v>
       </c>
       <c r="B38" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/楓之谷M-bar.jpg</v>
       </c>
       <c r="D38" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A38</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=楓之谷M</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -10048,11 +10086,11 @@
         <v>143</v>
       </c>
       <c r="B39" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/鳴潮-bar.jpg</v>
       </c>
       <c r="D39" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A39</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=鳴潮</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -10097,11 +10135,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/劍與遠征：啟程-bar.jpg</v>
       </c>
       <c r="D40" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A40</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=劍與遠征：啟程</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -10152,11 +10190,11 @@
         <v>145</v>
       </c>
       <c r="B41" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/熱血大作戰-bar.jpg</v>
       </c>
       <c r="D41" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A41</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=熱血大作戰</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -10219,11 +10257,11 @@
         <v>146</v>
       </c>
       <c r="B42" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/骷髏傳說：戰神崛起-bar.jpg</v>
       </c>
       <c r="D42" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A42</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=骷髏傳說：戰神崛起</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -10322,11 +10360,11 @@
         <v>147</v>
       </c>
       <c r="B43" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/黎明：血色魔女-bar.jpg</v>
       </c>
       <c r="D43" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A43</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=黎明：血色魔女</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -10425,11 +10463,11 @@
         <v>148</v>
       </c>
       <c r="B44" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/黎明啟示錄-bar.jpg</v>
       </c>
       <c r="D44" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A44</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=黎明啟示錄</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -10504,11 +10542,11 @@
         <v>149</v>
       </c>
       <c r="B45" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/龍魂旅人-bar.jpg</v>
       </c>
       <c r="D45" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A45</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=龍魂旅人</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -10607,11 +10645,11 @@
         <v>150</v>
       </c>
       <c r="B46" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/戀與深空-bar.jpg</v>
       </c>
       <c r="D46" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A46</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=戀與深空</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -10728,11 +10766,11 @@
         <v>151</v>
       </c>
       <c r="B47" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/靈魂衝擊：無限放置-bar.jpg</v>
       </c>
       <c r="D47" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A47</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=靈魂衝擊：無限放置</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -10783,11 +10821,11 @@
         <v>152</v>
       </c>
       <c r="B48" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/楓葉島-bar.jpg</v>
       </c>
       <c r="D48" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A48</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=楓葉島</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -10868,11 +10906,11 @@
         <v>153</v>
       </c>
       <c r="B49" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/無名江湖-bar.jpg</v>
       </c>
       <c r="D49" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A49</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=無名江湖</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -10917,11 +10955,11 @@
         <v>154</v>
       </c>
       <c r="B50" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/萬妖領域-bar.jpg</v>
       </c>
       <c r="D50" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A50</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=萬妖領域</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -10990,11 +11028,11 @@
         <v>155</v>
       </c>
       <c r="B51" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/一姬當千TD-bar.jpg</v>
       </c>
       <c r="D51" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A51</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=一姬當千TD</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -11039,11 +11077,11 @@
         <v>156</v>
       </c>
       <c r="B52" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/劍客行-bar.jpg</v>
       </c>
       <c r="D52" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A52</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=劍客行</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -11076,11 +11114,11 @@
         <v>157</v>
       </c>
       <c r="B53" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/時之樹少女-bar.jpg</v>
       </c>
       <c r="D53" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A53</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=時之樹少女</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -11125,11 +11163,11 @@
         <v>158</v>
       </c>
       <c r="B54" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/錨點降臨Re：Code-bar.jpg</v>
       </c>
       <c r="D54" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A54</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=錨點降臨Re：Code</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -11258,11 +11296,11 @@
         <v>159</v>
       </c>
       <c r="B55" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/神契氣靈師-bar.jpg</v>
       </c>
       <c r="D55" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A55</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=神契氣靈師</v>
       </c>
       <c r="E55" s="2" t="s">
@@ -11379,11 +11417,11 @@
         <v>160</v>
       </c>
       <c r="B56" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/不休旅途：繪卷世界-bar.jpg</v>
       </c>
       <c r="D56" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A56</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=不休旅途：繪卷世界</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -11460,11 +11498,11 @@
         <v>161</v>
       </c>
       <c r="B57" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/別破防鴨-bar.jpg</v>
       </c>
       <c r="D57" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A57</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=別破防鴨</v>
       </c>
       <c r="E57" s="8" t="s">
@@ -11557,11 +11595,11 @@
         <v>162</v>
       </c>
       <c r="B58" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/超派救星幫幫忙-bar.jpg</v>
       </c>
       <c r="D58" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A58</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=超派救星幫幫忙</v>
       </c>
       <c r="E58" s="2" t="s">
@@ -11600,11 +11638,11 @@
         <v>163</v>
       </c>
       <c r="B59" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/時光大爆炸-bar.jpg</v>
       </c>
       <c r="D59" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A59</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=時光大爆炸</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -11679,11 +11717,11 @@
         <v>164</v>
       </c>
       <c r="B60" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/深淵：不滅者-bar.jpg</v>
       </c>
       <c r="D60" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A60</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=深淵：不滅者</v>
       </c>
       <c r="E60" s="2" t="s">
@@ -11782,11 +11820,11 @@
         <v>52</v>
       </c>
       <c r="B61" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/Last War-bar.jpg</v>
       </c>
       <c r="D61" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A61</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Last War</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -11813,11 +11851,11 @@
         <v>165</v>
       </c>
       <c r="B62" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/勇士不要停-bar.jpg</v>
       </c>
       <c r="D62" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A62</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=勇士不要停</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -11928,11 +11966,11 @@
         <v>166</v>
       </c>
       <c r="B63" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/元氣火柴人-bar.jpg</v>
       </c>
       <c r="D63" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A63</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=元氣火柴人</v>
       </c>
       <c r="E63" s="8" t="s">
@@ -12073,11 +12111,11 @@
         <v>167</v>
       </c>
       <c r="B64" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/深淵之影-bar.jpg</v>
       </c>
       <c r="D64" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A64</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=深淵之影</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -12110,11 +12148,11 @@
         <v>168</v>
       </c>
       <c r="B65" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/玩星派對-bar.jpg</v>
       </c>
       <c r="D65" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A65</f>
+        <f t="shared" si="2"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=玩星派對</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -12171,11 +12209,11 @@
         <v>169</v>
       </c>
       <c r="B66" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>giftcodesbanner/進化吧!我的人生-bar.jpg</v>
       </c>
       <c r="D66" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A66</f>
+        <f t="shared" ref="D66:D97" si="3">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A66</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=進化吧!我的人生</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -12232,11 +12270,11 @@
         <v>170</v>
       </c>
       <c r="B67" s="2" t="str">
-        <f t="shared" ref="B67:B125" si="1">"giftcodesbanner/" &amp; A67 &amp; "-bar.jpg"</f>
+        <f t="shared" ref="B67:B125" si="4">"giftcodesbanner/" &amp; A67 &amp; "-bar.jpg"</f>
         <v>giftcodesbanner/星之夢幻島-bar.jpg</v>
       </c>
       <c r="D67" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A67</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星之夢幻島</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -12299,11 +12337,11 @@
         <v>171</v>
       </c>
       <c r="B68" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/小冰冰傳奇：回到最初-bar.jpg</v>
       </c>
       <c r="D68" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A68</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小冰冰傳奇：回到最初</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -12378,11 +12416,11 @@
         <v>172</v>
       </c>
       <c r="B69" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/江湖風雲傳-bar.jpg</v>
       </c>
       <c r="D69" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A69</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=江湖風雲傳</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -12421,11 +12459,11 @@
         <v>173</v>
       </c>
       <c r="B70" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/星願之冠：狼少女物語-bar.jpg</v>
       </c>
       <c r="D70" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A70</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星願之冠：狼少女物語</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -12464,11 +12502,11 @@
         <v>174</v>
       </c>
       <c r="B71" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/香蕉缺個芭樂-bar.jpg</v>
       </c>
       <c r="D71" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A71</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=香蕉缺個芭樂</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -12597,11 +12635,11 @@
         <v>175</v>
       </c>
       <c r="B72" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/精靈塔塔開-bar.jpg</v>
       </c>
       <c r="D72" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A72</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=精靈塔塔開</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -12628,11 +12666,11 @@
         <v>176</v>
       </c>
       <c r="B73" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/終末之歌-bar.jpg</v>
       </c>
       <c r="D73" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A73</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=終末之歌</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -12671,11 +12709,11 @@
         <v>177</v>
       </c>
       <c r="B74" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/森靈奇境-bar.jpg</v>
       </c>
       <c r="D74" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A74</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=森靈奇境</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -12762,11 +12800,11 @@
         <v>178</v>
       </c>
       <c r="B75" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/鬥破蒼穹：蕭門篇-bar.jpg</v>
       </c>
       <c r="D75" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A75</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=鬥破蒼穹：蕭門篇</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -12853,11 +12891,11 @@
         <v>179</v>
       </c>
       <c r="B76" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/無畏的狼煙-bar.jpg</v>
       </c>
       <c r="D76" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A76</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=無畏的狼煙</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -12896,11 +12934,11 @@
         <v>180</v>
       </c>
       <c r="B77" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/代號：無頭-bar.jpg</v>
       </c>
       <c r="D77" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A77</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=代號：無頭</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -12969,11 +13007,11 @@
         <v>181</v>
       </c>
       <c r="B78" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/牛頭人GO-bar.jpg</v>
       </c>
       <c r="D78" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A78</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=牛頭人GO</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -13042,11 +13080,11 @@
         <v>182</v>
       </c>
       <c r="B79" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/派對吧三國-bar.jpg</v>
       </c>
       <c r="D79" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A79</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=派對吧三國</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -13127,11 +13165,11 @@
         <v>183</v>
       </c>
       <c r="B80" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/酒酒大俠-bar.jpg</v>
       </c>
       <c r="D80" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A80</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=酒酒大俠</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -13194,11 +13232,11 @@
         <v>184</v>
       </c>
       <c r="B81" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/鼠衛家園-bar.jpg</v>
       </c>
       <c r="D81" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A81</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=鼠衛家園</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -13249,11 +13287,11 @@
         <v>185</v>
       </c>
       <c r="B82" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/未頌者之歌：異世界冒險奇譚-bar.jpg</v>
       </c>
       <c r="D82" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A82</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=未頌者之歌：異世界冒險奇譚</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -13313,11 +13351,11 @@
         <v>186</v>
       </c>
       <c r="B83" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/熱練戰士-bar.jpg</v>
       </c>
       <c r="D83" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A83</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=熱練戰士</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -13374,11 +13412,11 @@
         <v>187</v>
       </c>
       <c r="B84" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/聯盟戰棋-bar.jpg</v>
       </c>
       <c r="D84" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A84</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=聯盟戰棋</v>
       </c>
       <c r="E84" s="2" t="s">
@@ -13420,11 +13458,11 @@
         <v>188</v>
       </c>
       <c r="B85" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/劍客物語-bar.jpg</v>
       </c>
       <c r="D85" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A85</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=劍客物語</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -13499,11 +13537,11 @@
         <v>189</v>
       </c>
       <c r="B86" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/人在塔在-bar.jpg</v>
       </c>
       <c r="D86" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A86</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=人在塔在</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -13536,11 +13574,11 @@
         <v>190</v>
       </c>
       <c r="B87" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/龍語霜城-bar.jpg</v>
       </c>
       <c r="D87" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A87</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=龍語霜城</v>
       </c>
       <c r="E87" s="2" t="s">
@@ -13639,11 +13677,11 @@
         <v>191</v>
       </c>
       <c r="B88" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/洛伊的移動要塞-bar.jpg</v>
       </c>
       <c r="D88" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A88</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=洛伊的移動要塞</v>
       </c>
       <c r="E88" s="2" t="s">
@@ -13712,11 +13750,11 @@
         <v>192</v>
       </c>
       <c r="B89" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/喵喵王國-bar.jpg</v>
       </c>
       <c r="D89" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A89</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=喵喵王國</v>
       </c>
       <c r="E89" s="2" t="s">
@@ -13743,11 +13781,11 @@
         <v>193</v>
       </c>
       <c r="B90" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/東京謎影者-bar.jpg</v>
       </c>
       <c r="D90" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A90</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=東京謎影者</v>
       </c>
       <c r="E90" s="2" t="s">
@@ -13789,11 +13827,11 @@
         <v>194</v>
       </c>
       <c r="B91" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/戰極死遊-bar.jpg</v>
       </c>
       <c r="D91" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A91</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=戰極死遊</v>
       </c>
       <c r="E91" s="2" t="s">
@@ -13832,11 +13870,11 @@
         <v>195</v>
       </c>
       <c r="B92" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/進擊的蝸牛-bar.jpg</v>
       </c>
       <c r="D92" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A92</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=進擊的蝸牛</v>
       </c>
       <c r="E92" s="2" t="s">
@@ -13953,11 +13991,11 @@
         <v>196</v>
       </c>
       <c r="B93" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/純白大作戰-bar.jpg</v>
       </c>
       <c r="D93" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A93</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=純白大作戰</v>
       </c>
       <c r="E93" s="2" t="s">
@@ -14017,11 +14055,11 @@
         <v>197</v>
       </c>
       <c r="B94" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/黑星勇者-bar.jpg</v>
       </c>
       <c r="D94" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A94</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=黑星勇者</v>
       </c>
       <c r="E94" s="2" t="s">
@@ -14054,11 +14092,11 @@
         <v>198</v>
       </c>
       <c r="B95" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/龍之谷：經典再現-bar.jpg</v>
       </c>
       <c r="D95" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A95</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=龍之谷：經典再現</v>
       </c>
       <c r="E95" s="2" t="s">
@@ -14115,11 +14153,11 @@
         <v>199</v>
       </c>
       <c r="B96" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/楓之谷Artale-bar.jpg</v>
       </c>
       <c r="D96" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A96</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=楓之谷Artale</v>
       </c>
       <c r="E96" s="2" t="s">
@@ -14161,11 +14199,11 @@
         <v>200</v>
       </c>
       <c r="B97" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/出發吧麥芬-bar.jpg</v>
       </c>
       <c r="D97" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A97</f>
+        <f t="shared" si="3"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=出發吧麥芬</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -14192,11 +14230,11 @@
         <v>201</v>
       </c>
       <c r="B98" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/RO仙境傳說：守護永恆的愛 Classic-bar.jpg</v>
       </c>
       <c r="D98" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A98</f>
+        <f t="shared" ref="D98:D129" si="5">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A98</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：守護永恆的愛 Classic</v>
       </c>
       <c r="E98" s="2" t="s">
@@ -14331,11 +14369,11 @@
         <v>202</v>
       </c>
       <c r="B99" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/魔力寶貝：復興-bar.jpg</v>
       </c>
       <c r="D99" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A99</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魔力寶貝：復興</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -14404,11 +14442,11 @@
         <v>203</v>
       </c>
       <c r="B100" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/東京喰種Awakening-bar.jpg</v>
       </c>
       <c r="D100" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A100</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=東京喰種Awakening</v>
       </c>
       <c r="E100" s="2" t="s">
@@ -14507,11 +14545,11 @@
         <v>204</v>
       </c>
       <c r="B101" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/晶核-bar.jpg</v>
       </c>
       <c r="D101" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A101</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=晶核</v>
       </c>
       <c r="E101" s="2" t="s">
@@ -14598,11 +14636,11 @@
         <v>205</v>
       </c>
       <c r="B102" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/無盡夢迴-bar.jpg</v>
       </c>
       <c r="D102" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A102</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=無盡夢迴</v>
       </c>
       <c r="E102" s="2" t="s">
@@ -14659,11 +14697,11 @@
         <v>206</v>
       </c>
       <c r="B103" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/RO仙境傳說：放推冒險團-bar.jpg</v>
       </c>
       <c r="D103" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A103</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：放推冒險團</v>
       </c>
       <c r="E103" s="2" t="s">
@@ -14732,11 +14770,11 @@
         <v>207</v>
       </c>
       <c r="B104" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/英雄刷刷刷-bar.jpg</v>
       </c>
       <c r="D104" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A104</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=英雄刷刷刷</v>
       </c>
       <c r="E104" s="2" t="s">
@@ -14838,11 +14876,11 @@
         <v>208</v>
       </c>
       <c r="B105" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/萬靈物語-bar.jpg</v>
       </c>
       <c r="D105" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A105</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=萬靈物語</v>
       </c>
       <c r="E105" s="2" t="s">
@@ -14944,11 +14982,11 @@
         <v>209</v>
       </c>
       <c r="B106" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/斗羅大陸：逆轉時空-bar.jpg</v>
       </c>
       <c r="D106" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A106</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=斗羅大陸：逆轉時空</v>
       </c>
       <c r="E106" s="2" t="s">
@@ -15023,11 +15061,11 @@
         <v>210</v>
       </c>
       <c r="B107" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/魔靈召喚：保衛戰-bar.jpg</v>
       </c>
       <c r="D107" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A107</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魔靈召喚：保衛戰</v>
       </c>
       <c r="E107" s="2" t="s">
@@ -15048,11 +15086,11 @@
         <v>211</v>
       </c>
       <c r="B108" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/潘多蘭島-bar.jpg</v>
       </c>
       <c r="D108" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A108</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=潘多蘭島</v>
       </c>
       <c r="E108" s="2" t="s">
@@ -15079,11 +15117,11 @@
         <v>212</v>
       </c>
       <c r="B109" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/電鋸果汁大亂鬥-bar.jpg</v>
       </c>
       <c r="D109" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A109</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=電鋸果汁大亂鬥</v>
       </c>
       <c r="E109" s="2" t="s">
@@ -15110,11 +15148,11 @@
         <v>213</v>
       </c>
       <c r="B110" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/風色幻想NeXus-bar.jpg</v>
       </c>
       <c r="D110" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A110</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=風色幻想NeXus</v>
       </c>
       <c r="E110" s="2" t="s">
@@ -15153,11 +15191,11 @@
         <v>214</v>
       </c>
       <c r="B111" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/星河訣愛-bar.jpg</v>
       </c>
       <c r="D111" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A111</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星河訣愛</v>
       </c>
       <c r="E111" s="2" t="s">
@@ -15226,11 +15264,11 @@
         <v>1221</v>
       </c>
       <c r="B112" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/kingshot-bar.jpg</v>
       </c>
       <c r="D112" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A112</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=kingshot</v>
       </c>
       <c r="E112" s="2" t="s">
@@ -15281,11 +15319,11 @@
         <v>1222</v>
       </c>
       <c r="B113" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/胡鬧地牢-bar.jpg</v>
       </c>
       <c r="D113" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A113</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=胡鬧地牢</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -15378,11 +15416,11 @@
         <v>1223</v>
       </c>
       <c r="B114" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/小小軍團-重生-bar.jpg</v>
       </c>
       <c r="D114" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A114</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小小軍團-重生</v>
       </c>
       <c r="E114" s="2" t="s">
@@ -15481,11 +15519,11 @@
         <v>1267</v>
       </c>
       <c r="B115" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/爪爪遠征-bar.jpg</v>
       </c>
       <c r="D115" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A115</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=爪爪遠征</v>
       </c>
       <c r="E115" s="2" t="s">
@@ -15512,11 +15550,11 @@
         <v>1268</v>
       </c>
       <c r="B116" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/勇士團團轉-bar.jpg</v>
       </c>
       <c r="D116" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A116</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=勇士團團轉</v>
       </c>
       <c r="E116" s="2" t="s">
@@ -15543,11 +15581,11 @@
         <v>1269</v>
       </c>
       <c r="B117" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/魁 三國志大戰-bar.jpg</v>
       </c>
       <c r="D117" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A117</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魁 三國志大戰</v>
       </c>
       <c r="E117" s="2" t="s">
@@ -15580,11 +15618,11 @@
         <v>1270</v>
       </c>
       <c r="B118" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/tokyo beast-bar.jpg</v>
       </c>
       <c r="D118" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A118</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=tokyo beast</v>
       </c>
       <c r="E118" s="2" t="s">
@@ -15611,11 +15649,11 @@
         <v>1271</v>
       </c>
       <c r="B119" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/切換英雄：放置型RPG-bar.jpg</v>
       </c>
       <c r="D119" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A119</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=切換英雄：放置型RPG</v>
       </c>
       <c r="E119" s="8" t="s">
@@ -15678,11 +15716,11 @@
         <v>1294</v>
       </c>
       <c r="B120" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/小死神傳奇-bar.jpg</v>
       </c>
       <c r="D120" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A120</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小死神傳奇</v>
       </c>
       <c r="E120" s="2" t="s">
@@ -15709,11 +15747,11 @@
         <v>1295</v>
       </c>
       <c r="B121" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/闇影詩章：凌越世界-bar.jpg</v>
       </c>
       <c r="D121" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A121</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=闇影詩章：凌越世界</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -15740,11 +15778,11 @@
         <v>1298</v>
       </c>
       <c r="B122" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/雪月風花-bar.jpg</v>
       </c>
       <c r="D122" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A122</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=雪月風花</v>
       </c>
       <c r="E122" s="2" t="s">
@@ -15855,11 +15893,11 @@
         <v>1299</v>
       </c>
       <c r="B123" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/文明帝國：同盟時代-bar.jpg</v>
       </c>
       <c r="D123" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A123</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=文明帝國：同盟時代</v>
       </c>
       <c r="E123" s="2" t="s">
@@ -15892,11 +15930,11 @@
         <v>1300</v>
       </c>
       <c r="B124" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/魔法商店大亨-bar.jpg</v>
       </c>
       <c r="D124" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A124</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魔法商店大亨</v>
       </c>
       <c r="E124" s="2" t="s">
@@ -15959,11 +15997,11 @@
         <v>1301</v>
       </c>
       <c r="B125" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>giftcodesbanner/新仙劍奇俠傳lite-bar.jpg</v>
       </c>
       <c r="D125" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A125</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=新仙劍奇俠傳lite</v>
       </c>
       <c r="E125" s="2" t="s">
@@ -16108,7 +16146,7 @@
         <v>giftcodesbanner/神州M-bar.jpg</v>
       </c>
       <c r="D126" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A126</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=神州M</v>
       </c>
       <c r="E126" s="2" t="s">
@@ -16145,7 +16183,7 @@
         <v>giftcodesbanner/英雄傳說：卡卡布三部曲-bar.jpg</v>
       </c>
       <c r="D127" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A127</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=英雄傳說：卡卡布三部曲</v>
       </c>
       <c r="E127" s="2" t="s">
@@ -16244,11 +16282,11 @@
         <v>1382</v>
       </c>
       <c r="B128" s="2" t="str">
-        <f t="shared" ref="B128:B134" si="2">"giftcodesbanner/" &amp; A128 &amp; "-bar.jpg"</f>
+        <f t="shared" ref="B128:B134" si="6">"giftcodesbanner/" &amp; A128 &amp; "-bar.jpg"</f>
         <v>giftcodesbanner/胡來英雄-bar.jpg</v>
       </c>
       <c r="D128" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A128</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=胡來英雄</v>
       </c>
       <c r="E128" s="8" t="s">
@@ -16305,11 +16343,11 @@
         <v>1383</v>
       </c>
       <c r="B129" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/一天又一天的RPG-bar.jpg</v>
       </c>
       <c r="D129" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A129</f>
+        <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=一天又一天的RPG</v>
       </c>
       <c r="E129" s="2" t="s">
@@ -16366,11 +16404,11 @@
         <v>1384</v>
       </c>
       <c r="B130" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/銀與血-bar.jpg</v>
       </c>
       <c r="D130" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A130</f>
+        <f t="shared" ref="D130:D161" si="7">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A130</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=銀與血</v>
       </c>
       <c r="E130" s="2" t="s">
@@ -16427,11 +16465,11 @@
         <v>1385</v>
       </c>
       <c r="B131" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/緋石之心-bar.jpg</v>
       </c>
       <c r="D131" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A131</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=緋石之心</v>
       </c>
       <c r="E131" s="2" t="s">
@@ -16464,11 +16502,11 @@
         <v>1416</v>
       </c>
       <c r="B132" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/滔湧少女-bar.jpg</v>
       </c>
       <c r="D132" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A132</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=滔湧少女</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -16513,11 +16551,11 @@
         <v>1417</v>
       </c>
       <c r="B133" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/漫威祕法狂潮-bar.jpg</v>
       </c>
       <c r="D133" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A133</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=漫威祕法狂潮</v>
       </c>
       <c r="E133" s="2" t="s">
@@ -16544,11 +16582,11 @@
         <v>1418</v>
       </c>
       <c r="B134" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>giftcodesbanner/魔教回歸：2D MMORPG-bar.jpg</v>
       </c>
       <c r="D134" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A134</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魔教回歸：2D MMORPG</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -16591,7 +16629,7 @@
         <v>giftcodesbanner/屍戰王朝-禮包碼.jpg</v>
       </c>
       <c r="D135" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A135</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=屍戰王朝</v>
       </c>
       <c r="E135" s="5" t="s">
@@ -16684,11 +16722,11 @@
         <v>1439</v>
       </c>
       <c r="C136" s="2" t="str">
-        <f t="shared" ref="C136:C175" si="3">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C136:C175" si="8">"giftcodesbanner/" &amp; A136 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/機甲變變變-禮包碼.jpg</v>
       </c>
       <c r="D136" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A136</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=機甲變變變</v>
       </c>
       <c r="E136" s="5" t="s">
@@ -16733,11 +16771,11 @@
         <v>1438</v>
       </c>
       <c r="C137" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/狼少女蘭吉-禮包碼.jpg</v>
       </c>
       <c r="D137" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A137</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=狼少女蘭吉</v>
       </c>
       <c r="E137" s="5" t="s">
@@ -16770,11 +16808,11 @@
         <v>1539</v>
       </c>
       <c r="C138" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/RO仙境傳說：曙光-禮包碼.jpg</v>
       </c>
       <c r="D138" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A138</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO仙境傳說：曙光</v>
       </c>
       <c r="E138" s="5" t="s">
@@ -16873,11 +16911,11 @@
         <v>1437</v>
       </c>
       <c r="C139" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/星曲Ultra-禮包碼.jpg</v>
       </c>
       <c r="D139" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A139</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星曲Ultra</v>
       </c>
       <c r="E139" s="5" t="s">
@@ -16910,11 +16948,11 @@
         <v>1479</v>
       </c>
       <c r="C140" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/第七天災-禮包碼.jpg</v>
       </c>
       <c r="D140" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A140</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=第七天災</v>
       </c>
       <c r="E140" s="5" t="s">
@@ -17055,11 +17093,11 @@
         <v>1480</v>
       </c>
       <c r="C141" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/百萬神界-禮包碼.jpg</v>
       </c>
       <c r="D141" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A141</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=百萬神界</v>
       </c>
       <c r="E141" s="5" t="s">
@@ -17134,11 +17172,11 @@
         <v>1481</v>
       </c>
       <c r="C142" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/Dark war-禮包碼.jpg</v>
       </c>
       <c r="D142" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A142</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Dark war</v>
       </c>
       <c r="E142" s="5" t="s">
@@ -17171,11 +17209,11 @@
         <v>1540</v>
       </c>
       <c r="C143" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/美男惡徒-禮包碼.jpg</v>
       </c>
       <c r="D143" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A143</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=美男惡徒</v>
       </c>
       <c r="E143" s="8" t="s">
@@ -17220,11 +17258,11 @@
         <v>1550</v>
       </c>
       <c r="C144" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/三國冰河時代-禮包碼.jpg</v>
       </c>
       <c r="D144" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A144</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=三國冰河時代</v>
       </c>
       <c r="E144" s="2" t="s">
@@ -17293,11 +17331,11 @@
         <v>1551</v>
       </c>
       <c r="C145" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/暗黑崛起-禮包碼.jpg</v>
       </c>
       <c r="D145" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A145</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=暗黑崛起</v>
       </c>
       <c r="E145" s="8" t="s">
@@ -17324,11 +17362,11 @@
         <v>1552</v>
       </c>
       <c r="C146" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/轉生魔劍士養成：策略放置RPG-禮包碼.jpg</v>
       </c>
       <c r="D146" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A146</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=轉生魔劍士養成：策略放置RPG</v>
       </c>
       <c r="E146" s="8" t="s">
@@ -17361,11 +17399,11 @@
         <v>1808</v>
       </c>
       <c r="C147" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/極速漂移：3V3-禮包碼.jpg</v>
       </c>
       <c r="D147" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A147</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=極速漂移：3V3</v>
       </c>
       <c r="E147" s="2" t="s">
@@ -17398,11 +17436,11 @@
         <v>1566</v>
       </c>
       <c r="C148" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/斗羅大陸：獵魂世界-禮包碼.jpg</v>
       </c>
       <c r="D148" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A148</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=斗羅大陸：獵魂世界</v>
       </c>
       <c r="E148" s="8" t="s">
@@ -17489,11 +17527,11 @@
         <v>1567</v>
       </c>
       <c r="C149" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/指點兵兵-禮包碼.jpg</v>
       </c>
       <c r="D149" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A149</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=指點兵兵</v>
       </c>
       <c r="E149" s="8" t="s">
@@ -17544,11 +17582,11 @@
         <v>1586</v>
       </c>
       <c r="C150" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/變身傳奇-禮包碼.jpg</v>
       </c>
       <c r="D150" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A150</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=變身傳奇</v>
       </c>
       <c r="E150" s="2" t="s">
@@ -17581,11 +17619,11 @@
         <v>1587</v>
       </c>
       <c r="C151" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/Blue eyes：公會大師-禮包碼.jpg</v>
       </c>
       <c r="D151" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A151</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Blue eyes：公會大師</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -17634,11 +17672,11 @@
         <v>1598</v>
       </c>
       <c r="C152" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/杖劍傳說：坎斯汀之約-禮包碼.jpg</v>
       </c>
       <c r="D152" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A152</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=杖劍傳說：坎斯汀之約</v>
       </c>
       <c r="E152" s="8" t="s">
@@ -17722,11 +17760,11 @@
         <v>1623</v>
       </c>
       <c r="C153" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/超級海戰：紀元崛起-禮包碼.jpg</v>
       </c>
       <c r="D153" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A153</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=超級海戰：紀元崛起</v>
       </c>
       <c r="E153" s="8" t="s">
@@ -17771,11 +17809,11 @@
         <v>1635</v>
       </c>
       <c r="C154" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/進擊的惡魔團-禮包碼.jpg</v>
       </c>
       <c r="D154" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A154</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=進擊的惡魔團</v>
       </c>
       <c r="E154" s="8" t="s">
@@ -17829,11 +17867,11 @@
         <v>1652</v>
       </c>
       <c r="C155" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/蝕影：緋之契-禮包碼.jpg</v>
       </c>
       <c r="D155" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A155</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=蝕影：緋之契</v>
       </c>
       <c r="E155" s="2" t="s">
@@ -17878,11 +17916,11 @@
         <v>1651</v>
       </c>
       <c r="C156" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/RO：Crush-禮包碼.jpg</v>
       </c>
       <c r="D156" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A156</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=RO：Crush</v>
       </c>
       <c r="E156" s="2" t="s">
@@ -17909,11 +17947,11 @@
         <v>1667</v>
       </c>
       <c r="C157" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/溯回青空-禮包碼.jpg</v>
       </c>
       <c r="D157" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A157</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=溯回青空</v>
       </c>
       <c r="E157" s="12" t="s">
@@ -17949,11 +17987,11 @@
         <v>1668</v>
       </c>
       <c r="C158" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/蒼之啟示錄-禮包碼.jpg</v>
       </c>
       <c r="D158" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A158</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=蒼之啟示錄</v>
       </c>
       <c r="E158" s="12" t="s">
@@ -17986,11 +18024,11 @@
         <v>1669</v>
       </c>
       <c r="C159" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/第六絕區-禮包碼.jpg</v>
       </c>
       <c r="D159" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A159</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=第六絕區</v>
       </c>
       <c r="E159" s="12" t="s">
@@ -18026,11 +18064,11 @@
         <v>1695</v>
       </c>
       <c r="C160" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/MO.CO-禮包碼.jpg</v>
       </c>
       <c r="D160" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A160</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=MO.CO</v>
       </c>
       <c r="E160" s="12" t="s">
@@ -18063,11 +18101,11 @@
         <v>1670</v>
       </c>
       <c r="C161" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/幻世三國：一騎當千-禮包碼.jpg</v>
       </c>
       <c r="D161" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A161</f>
+        <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=幻世三國：一騎當千</v>
       </c>
       <c r="E161" s="12" t="s">
@@ -18100,11 +18138,11 @@
         <v>1693</v>
       </c>
       <c r="C162" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/小兵立大功-禮包碼.jpg</v>
       </c>
       <c r="D162" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A162</f>
+        <f t="shared" ref="D162:D175" si="9">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A162</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="E162" s="12" t="s">
@@ -18140,11 +18178,11 @@
         <v>1694</v>
       </c>
       <c r="C163" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/像素全明星-禮包碼.jpg</v>
       </c>
       <c r="D163" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A163</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=像素全明星</v>
       </c>
       <c r="E163" s="12" t="s">
@@ -18180,11 +18218,11 @@
         <v>1696</v>
       </c>
       <c r="C164" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/浣熊傳說-禮包碼.jpg</v>
       </c>
       <c r="D164" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A164</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=浣熊傳說</v>
       </c>
       <c r="E164" s="8" t="s">
@@ -18229,11 +18267,11 @@
         <v>1697</v>
       </c>
       <c r="C165" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/勇者格鬥城-禮包碼.jpg</v>
       </c>
       <c r="D165" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A165</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=勇者格鬥城</v>
       </c>
       <c r="E165" s="8" t="s">
@@ -18269,11 +18307,11 @@
         <v>1720</v>
       </c>
       <c r="C166" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/龐寶：背包英雄們-禮包碼.jpg</v>
       </c>
       <c r="D166" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A166</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=龐寶：背包英雄們</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -18309,11 +18347,11 @@
         <v>1711</v>
       </c>
       <c r="C167" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/星耀球會-禮包碼.jpg</v>
       </c>
       <c r="D167" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A167</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星耀球會</v>
       </c>
       <c r="E167" s="8" t="s">
@@ -18358,11 +18396,11 @@
         <v>1722</v>
       </c>
       <c r="C168" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/東方幻想ECLIPSE-禮包碼.jpg</v>
       </c>
       <c r="D168" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A168</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=東方幻想ECLIPSE</v>
       </c>
       <c r="E168" s="2" t="s">
@@ -18395,11 +18433,11 @@
         <v>1734</v>
       </c>
       <c r="C169" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/世紀帝國M-禮包碼.jpg</v>
       </c>
       <c r="D169" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A169</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=世紀帝國M</v>
       </c>
       <c r="E169" s="2" t="s">
@@ -18504,11 +18542,11 @@
         <v>1735</v>
       </c>
       <c r="C170" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/歐啦!守得豬-禮包碼.jpg</v>
       </c>
       <c r="D170" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A170</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=歐啦!守得豬</v>
       </c>
       <c r="E170" s="2" t="s">
@@ -18565,11 +18603,11 @@
         <v>1750</v>
       </c>
       <c r="C171" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/18櫻花幕府-禮包碼.jpg</v>
       </c>
       <c r="D171" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A171</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=18櫻花幕府</v>
       </c>
       <c r="E171" s="8" t="s">
@@ -18602,11 +18640,11 @@
         <v>1785</v>
       </c>
       <c r="C172" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/大武道-禮包碼.jpg</v>
       </c>
       <c r="D172" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A172</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=大武道</v>
       </c>
       <c r="E172" s="8" t="s">
@@ -18693,11 +18731,11 @@
         <v>1834</v>
       </c>
       <c r="C173" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/奇蹟MU：暴走之翼-禮包碼.jpg</v>
       </c>
       <c r="D173" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A173</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=奇蹟MU：暴走之翼</v>
       </c>
       <c r="E173" s="20" t="s">
@@ -18775,11 +18813,11 @@
         <v>1836</v>
       </c>
       <c r="C174" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/劍太傳說：新的開始-禮包碼.jpg</v>
       </c>
       <c r="D174" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A174</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=劍太傳說：新的開始</v>
       </c>
       <c r="E174" s="2" t="s">
@@ -18816,10 +18854,10 @@
         <v>1844</v>
       </c>
       <c r="Q174" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="R174" s="2" t="s">
         <v>1861</v>
-      </c>
-      <c r="R174" s="2" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="175" spans="1:38" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18827,11 +18865,11 @@
         <v>1837</v>
       </c>
       <c r="C175" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>giftcodesbanner/三國。群英燎原-禮包碼.jpg</v>
       </c>
       <c r="D175" s="2" t="str">
-        <f>"https://www.ssbuy.tw/gift-codes.html?game="&amp;A175</f>
+        <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=三國。群英燎原</v>
       </c>
       <c r="E175" s="2" t="s">
@@ -18841,7 +18879,7 @@
         <v>1851</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>1852</v>
+        <v>1865</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>1849</v>
@@ -18850,47 +18888,125 @@
         <v>1850</v>
       </c>
       <c r="K175" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M175" s="2" t="s">
         <v>1853</v>
       </c>
-      <c r="L175" s="2" t="s">
+      <c r="N175" s="2" t="s">
         <v>1855</v>
       </c>
-      <c r="M175" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="N175" s="2" t="s">
+      <c r="O175" s="2" t="s">
         <v>1856</v>
       </c>
-      <c r="O175" s="2" t="s">
+      <c r="P175" s="2" t="s">
         <v>1857</v>
       </c>
-      <c r="P175" s="2" t="s">
+      <c r="Q175" s="2" t="s">
         <v>1858</v>
       </c>
-      <c r="Q175" s="2" t="s">
+      <c r="R175" s="2" t="s">
         <v>1859</v>
       </c>
-      <c r="R175" s="2" t="s">
-        <v>1860</v>
-      </c>
     </row>
-    <row r="176" spans="1:38" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:38" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="21" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C176" s="2" t="str">
+        <f t="shared" ref="C176:C177" si="10">"giftcodesbanner/" &amp; A176 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/Final War：寒霜前線-禮包碼.jpg</v>
+      </c>
+      <c r="D176" s="2" t="str">
+        <f t="shared" ref="D176:D177" si="11">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A176</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Final War：寒霜前線</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="N176" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="O176" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="P176" s="2" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="11" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C177" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>giftcodesbanner/黑夜獵人-禮包碼.jpg</v>
+      </c>
+      <c r="D177" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=黑夜獵人</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="K177" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="M177" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="N177" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="O177" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="P177" s="2" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="193" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="194" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="195" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="1886">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7129,12 +7129,113 @@
     <t>《黑夜獵人：專治吸血鬼、殭屍與各種不服》是一款主打休閒塔防與策略對抗的哥德風手遊。你將化身為一名強大的吸血鬼獵人，在暗夜中佈下天羅地網，抵禦一波波來襲的殭屍、狼人與吸血鬼大軍。遊戲核心玩法是策略性地放置和升級你的防禦單位，結合英雄技能，消滅所有敵人。告別複雜操作，享受單手即可暢玩的割草快感與塔防樂趣。準備好運用你的智慧，建造最強防線，成為讓所有黑暗生物聞風喪膽的終極獵人了嗎？立即下載，體驗這場刺激又爽快的暗夜狩獵！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>魔法黯道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>《魔法膽道》是一款闇黑像素風格的放置RPG手遊，帶你深入無盡地城展開刷寶冒險。新手上路務必尋找最新的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換豐富資源即可快人一步，輕鬆開荒。遊戲核心玩法是高度自由的配點與技能組合，讓你打造專屬流派。除了透過掛機農資源，許多玩家為了加速角色成長，會尋找專業的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務來獲取稀有道具與特權，讓戰力突飛猛進。無論是無課休閒玩家或課長，都能在這款遊戲中享受放置養成的樂趣，體驗復古又刺激的暗黑世界。</t>
+    </r>
+  </si>
+  <si>
+    <t>MFADSQFL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MFADSQDKKJG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MFADGZLB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MFADSQDKSDG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MFADSQDL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效期限到8月12日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效期限到8月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Facebook追蹤有禮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 有效期限到8月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面上方搖桿按鈕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉到最下面按兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入兌換碼即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7215,6 +7316,21 @@
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -7301,7 +7417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7355,6 +7471,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18946,7 +19065,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="11" t="s">
         <v>1870</v>
       </c>
@@ -18992,21 +19111,75 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="22" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C178" s="2" t="str">
+        <f t="shared" ref="C178" si="12">"giftcodesbanner/" &amp; A178 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/魔法黯道-禮包碼.jpg</v>
+      </c>
+      <c r="D178" s="2" t="str">
+        <f t="shared" ref="D178" si="13">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A178</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=魔法黯道</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="N178" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="O178" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="P178" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="Q178" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="R178" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="S178" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="T178" s="2" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="193" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="194" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="195" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3204" uniqueCount="1888">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7228,6 +7228,14 @@
   </si>
   <si>
     <t>輸入兌換碼即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神代紀事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《神代紀事》是一款像素風Roguelite冒險RPG，採單手直立式操控，讓您隨時沉浸在神話世界。探索隨機地圖，組合百種技能與多樣武器，挑戰生存極限。官方時常發布禮包碼，讓玩家能免費兌換豐富資源，享受開局優勢。遊戲主要考驗技術與策略，但透過適度的儲值則可加速角色成長或解鎖限定道具，讓您的冒險旅程更加個人化。立即化身啟源者，善用免費禮包碼福利與儲值助力，與朋友連線，共同寫下不朽的戰鬥史詩！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19116,11 +19124,11 @@
         <v>1872</v>
       </c>
       <c r="C178" s="2" t="str">
-        <f t="shared" ref="C178" si="12">"giftcodesbanner/" &amp; A178 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C178:C179" si="12">"giftcodesbanner/" &amp; A178 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/魔法黯道-禮包碼.jpg</v>
       </c>
       <c r="D178" s="2" t="str">
-        <f t="shared" ref="D178" si="13">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A178</f>
+        <f t="shared" ref="D178:D179" si="13">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A178</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=魔法黯道</v>
       </c>
       <c r="E178" t="s">
@@ -19166,7 +19174,46 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C179" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>giftcodesbanner/神代紀事-禮包碼.jpg</v>
+      </c>
+      <c r="D179" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=神代紀事</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="N179" s="2" t="s">
+        <v>1869</v>
+      </c>
+    </row>
     <row r="180" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3204" uniqueCount="1888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3212" uniqueCount="1896">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7236,6 +7236,37 @@
   </si>
   <si>
     <t>《神代紀事》是一款像素風Roguelite冒險RPG，採單手直立式操控，讓您隨時沉浸在神話世界。探索隨機地圖，組合百種技能與多樣武器，挑戰生存極限。官方時常發布禮包碼，讓玩家能免費兌換豐富資源，享受開局優勢。遊戲主要考驗技術與策略，但透過適度的儲值則可加速角色成長或解鎖限定道具，讓您的冒險旅程更加個人化。立即化身啟源者，善用免費禮包碼福利與儲值助力，與朋友連線，共同寫下不朽的戰鬥史詩！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天命國度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲主畫面點左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JOINNOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右邊齒輪設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上剛剛複製的禮包碼</t>
+  </si>
+  <si>
+    <t>《天命國度 》是 IGG 匠心打造的史詩級策略手遊。在這個奇幻大陸上，您將化身領主，從零開始建造宏偉王國，集結傳說英雄，與全球菁英玩家展開即時策略對決。遊戲不僅考驗您的戰術佈局，更重視資源的累積與運用。想在開戰時取得優勢，記得隨時關注官方釋出的最新禮包碼，並可尋找可靠的代儲值管道來極大化您的資源效益，讓您的王國以前所未有的速度崛起，稱霸全服！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通星耀石*10+1000寶石*5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19214,7 +19245,40 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="22" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C180" s="2" t="str">
+        <f t="shared" ref="C180" si="14">"giftcodesbanner/" &amp; A180 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/天命國度-禮包碼.jpg</v>
+      </c>
+      <c r="D180" s="2" t="str">
+        <f t="shared" ref="D180" si="15">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A180</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=天命國度</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>1895</v>
+      </c>
+    </row>
     <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="183" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3212" uniqueCount="1896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="1914">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7267,6 +7267,123 @@
   </si>
   <si>
     <t>普通星耀石*10+1000寶石*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰國武士道</t>
+  </si>
+  <si>
+    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，織田信長、豐臣秀吉、德川家康等傳奇武將悉數登場，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>《超蝦大作戰》是一款充滿趣味與創意的休閒放置養成遊戲。玩家將進入一個奇妙的異世界，從一顆蝦蛋開始，透過不斷吞噬與進化，培養出千奇百怪、戰力爆表的究極神蝦。遊戲畫風搞怪可愛，玩法輕鬆上手，您將見證小蝦米如何一步步變異，解鎖各種腦洞大開的基因形態，最終成為稱霸水域的蝦界王者。為了幫助您的神蝦快速成長，記得要隨時關注並領取官方發布的最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換免費的鑽石和加速道具。遊戲內也提供便捷的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。快來加入這場超展開的蝦世界冒險，看看你的蝦能進化到多狂！</t>
+    </r>
+  </si>
+  <si>
+    <t>超蝦大作戰</t>
+  </si>
+  <si>
+    <t>lemon666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瀨戶環奈&amp;檸檬福利蝦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KW5RER2ES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RW5RH58HU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳奇金卡檸檬妹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定頭像框</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DW5R6LSJG
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UW5RJ9B83
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定稱號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初來蝦到禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面點頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設定後點兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方釋出中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7456,7 +7573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7512,6 +7629,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19279,8 +19399,89 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C181" s="2" t="str">
+        <f t="shared" ref="C181" si="16">"giftcodesbanner/" &amp; A181 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/戰國武士道-禮包碼.jpg</v>
+      </c>
+      <c r="D181" s="2" t="str">
+        <f t="shared" ref="D181" si="17">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A181</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=戰國武士道</v>
+      </c>
+      <c r="E181" s="23" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="L181" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="10" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C182" s="2" t="str">
+        <f t="shared" ref="C182" si="18">"giftcodesbanner/" &amp; A182 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/超蝦大作戰-禮包碼.jpg</v>
+      </c>
+      <c r="D182" s="2" t="str">
+        <f t="shared" ref="D182" si="19">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A182</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=超蝦大作戰</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="N182" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="O182" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="P182" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="Q182" s="8" t="s">
+        <v>1906</v>
+      </c>
+      <c r="R182" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="S182" s="8" t="s">
+        <v>1907</v>
+      </c>
+      <c r="T182" s="2" t="s">
+        <v>1908</v>
+      </c>
+    </row>
     <row r="183" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="184" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="185" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -7273,7 +7273,68 @@
     <t>戰國武士道</t>
   </si>
   <si>
-    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，織田信長、豐臣秀吉、德川家康等傳奇武將悉數登場，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
+    <t>超蝦大作戰</t>
+  </si>
+  <si>
+    <t>lemon666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瀨戶環奈&amp;檸檬福利蝦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KW5RER2ES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RW5RH58HU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳奇金卡檸檬妹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定頭像框</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DW5R6LSJG
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UW5RJ9B83
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定稱號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初來蝦到禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面點頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入設定後點兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方釋出中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -7283,7 +7344,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="1"/>
@@ -7305,7 +7366,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="1"/>
@@ -7322,68 +7383,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。快來加入這場超展開的蝦世界冒險，看看你的蝦能進化到多狂！</t>
+      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。</t>
     </r>
-  </si>
-  <si>
-    <t>超蝦大作戰</t>
-  </si>
-  <si>
-    <t>lemon666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瀨戶環奈&amp;檸檬福利蝦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KW5RER2ES</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RW5RH58HU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傳奇金卡檸檬妹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>限定頭像框</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">DW5R6LSJG
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">UW5RJ9B83
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>限定稱號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初來蝦到禮包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲主畫面點頭像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進入設定後點兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>官方釋出中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7391,7 +7392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7482,6 +7483,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="1"/>
@@ -19412,7 +19422,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=戰國武士道</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>1897</v>
+        <v>1912</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>1478</v>
@@ -19421,15 +19431,15 @@
         <v>1478</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="C182" s="2" t="str">
         <f t="shared" ref="C182" si="18">"giftcodesbanner/" &amp; A182 &amp; "-禮包碼.jpg"</f>
@@ -19440,46 +19450,46 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=超蝦大作戰</v>
       </c>
       <c r="E182" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K182" s="2" t="s">
         <v>1898</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>1911</v>
-      </c>
-      <c r="H182" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="K182" s="2" t="s">
+      <c r="L182" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="M182" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="L182" s="2" t="s">
+      <c r="N182" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="O182" s="2" t="s">
         <v>1901</v>
       </c>
-      <c r="M182" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="N182" s="2" t="s">
+      <c r="P182" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="Q182" s="8" t="s">
         <v>1904</v>
       </c>
-      <c r="O182" s="2" t="s">
-        <v>1903</v>
-      </c>
-      <c r="P182" s="2" t="s">
+      <c r="R182" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="S182" s="8" t="s">
         <v>1905</v>
       </c>
-      <c r="Q182" s="8" t="s">
+      <c r="T182" s="2" t="s">
         <v>1906</v>
-      </c>
-      <c r="R182" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="S182" s="8" t="s">
-        <v>1907</v>
-      </c>
-      <c r="T182" s="2" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="183" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="1914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="1935">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7326,10 +7326,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>官方釋出中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7385,6 +7381,93 @@
       </rPr>
       <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真妖獸!廢柴要修仙</t>
+  </si>
+  <si>
+    <t>在遊戲主畫面點左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中間下方找到「虛寶碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在Ssbuy複製好的禮包兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回到主畫面點左下角「洞府」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到信件裡即可領取優惠禮包內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+加速券*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+精金*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+法寶精華*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+法寶精華*5+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+乾坤石·橙*1+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+槌子*50+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+加速券*5+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備好踏上顛覆傳統的修仙之旅嗎？《真妖獸!廢柴要修仙》是一款讓你從廢柴逆襲成仙的放置RPG。遊戲以「渡劫飛升」與「降妖伏魔」為核心玩法，帶來最刺激的修仙體驗。你將在仙俠世界收服奇珍異獸，不斷修煉突破。為了助你快速提升實力，官方時常提供豐富的禮包碼，輕鬆獲取大量資源。遊戲的煉丹、煉器與洞府等養成系統極具深度。若想在仙途上領先，安全的代儲值服務能讓你迅速累積優勢，解鎖強力法寶與稀有妖獸，打造你的修仙傳奇，成為三界主宰！立即下載，開啟你的逆天修行路。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19234,7 +19317,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="11" t="s">
         <v>1870</v>
       </c>
@@ -19280,7 +19363,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="22" t="s">
         <v>1872</v>
       </c>
@@ -19335,7 +19418,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>1886</v>
       </c>
@@ -19375,7 +19458,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="22" t="s">
         <v>1888</v>
       </c>
@@ -19409,7 +19492,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
         <v>1896</v>
       </c>
@@ -19422,7 +19505,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=戰國武士道</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>1478</v>
@@ -19431,13 +19514,13 @@
         <v>1478</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
         <v>1897</v>
       </c>
@@ -19450,7 +19533,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=超蝦大作戰</v>
       </c>
       <c r="E182" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>1908</v>
@@ -19459,7 +19542,7 @@
         <v>1909</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>1910</v>
+        <v>1917</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>1898</v>
@@ -19492,16 +19575,88 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="10" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C183" s="2" t="str">
+        <f t="shared" ref="C183" si="20">"giftcodesbanner/" &amp; A183 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/真妖獸!廢柴要修仙-禮包碼.jpg</v>
+      </c>
+      <c r="D183" s="2" t="str">
+        <f t="shared" ref="D183" si="21">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A183</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=真妖獸!廢柴要修仙</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="L183" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="M183" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="N183" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="O183" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="P183" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="Q183" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="R183" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="S183" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="T183" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="U183" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="V183" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="W183" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="X183" s="2" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="193" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="194" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="195" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="1935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="1942">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7391,83 +7391,157 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回到主畫面點左下角「洞府」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到信件裡即可領取優惠禮包內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+加速券*10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+精金*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙玉*50+異獸蛋*50+法寶精華*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+法寶精華*5+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+乾坤石·橙*1+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+槌子*50+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>異獸蛋*100+加速券*5+靈石*5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備好踏上顛覆傳統的修仙之旅嗎？《真妖獸!廢柴要修仙》是一款讓你從廢柴逆襲成仙的放置RPG。遊戲以「渡劫飛升」與「降妖伏魔」為核心玩法，帶來最刺激的修仙體驗。你將在仙俠世界收服奇珍異獸，不斷修煉突破。為了助你快速提升實力，官方時常提供豐富的禮包碼，輕鬆獲取大量資源。遊戲的煉丹、煉器與洞府等養成系統極具深度。若想在仙途上領先，安全的代儲值服務能讓你迅速累積優勢，解鎖強力法寶與稀有妖獸，打造你的修仙傳奇，成為三界主宰！立即下載，開啟你的逆天修行路。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4gpa91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>《三國志Thrones》是一款讓您身歷其境的策略手遊，完美還原三國時代的壯闊史詩。遊戲中，您將扮演一方之主，從零開始建立您的城池，招募關羽、張飛、趙雲等傳奇武將，並透過合縱連橫的外交手段，與其他玩家結盟或對抗，最終目標是稱霸天下。遊戲畫面精緻，戰鬥場景氣勢磅礡，讓您體驗最真實的三國戰爭。想要快速提升實力，除了透過</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>獲得更多資源，也別忘了尋找最新的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換豐富的虛寶獎勵，讓您的統一天下之路更加順遂！立即下載《三國志Thrones》，開啟您的三國霸業！</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*168+資源補給箱*10+豪華大餐*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>畫面中間下方找到「虛寶碼」</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>貼上在Ssbuy複製好的禮包兌換碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上禮包碼並點擊「立即兌換」即可領取獎勵。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回到主畫面點左下角「洞府」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進到信件裡即可領取優惠禮包內容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仙玉*50+異獸蛋*50+加速券*10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仙玉*50+異獸蛋*50+精金*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIP888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仙玉*50+異獸蛋*50+法寶精華*5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>異獸蛋*100+法寶精華*5+靈石*5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>異獸蛋*100+乾坤石·橙*1+靈石*5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>異獸蛋*100+槌子*50+靈石*5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVIP999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>異獸蛋*100+加速券*5+靈石*5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>準備好踏上顛覆傳統的修仙之旅嗎？《真妖獸!廢柴要修仙》是一款讓你從廢柴逆襲成仙的放置RPG。遊戲以「渡劫飛升」與「降妖伏魔」為核心玩法，帶來最刺激的修仙體驗。你將在仙俠世界收服奇珍異獸，不斷修煉突破。為了助你快速提升實力，官方時常提供豐富的禮包碼，輕鬆獲取大量資源。遊戲的煉丹、煉器與洞府等養成系統極具深度。若想在仙途上領先，安全的代儲值服務能讓你迅速累積優勢，解鎖強力法寶與稀有妖獸，打造你的修仙傳奇，成為三界主宰！立即下載，開啟你的逆天修行路。</t>
+    <t>畫面下方「禮包兌換」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點券定即可領取兌換碼禮包內容物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三國志Thrones</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19542,7 +19616,7 @@
         <v>1909</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>1898</v>
@@ -19580,75 +19654,108 @@
         <v>1913</v>
       </c>
       <c r="C183" s="2" t="str">
-        <f t="shared" ref="C183" si="20">"giftcodesbanner/" &amp; A183 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C183:C184" si="20">"giftcodesbanner/" &amp; A183 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/真妖獸!廢柴要修仙-禮包碼.jpg</v>
       </c>
       <c r="D183" s="2" t="str">
-        <f t="shared" ref="D183" si="21">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A183</f>
+        <f t="shared" ref="D183:D184" si="21">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A183</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=真妖獸!廢柴要修仙</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>1914</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>1915</v>
+        <v>1936</v>
       </c>
       <c r="H183" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I183" s="2" t="s">
         <v>1916</v>
       </c>
-      <c r="I183" s="2" t="s">
+      <c r="J183" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="K183" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J183" s="2" t="s">
+      <c r="L183" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="M183" s="2" t="s">
         <v>1919</v>
       </c>
-      <c r="K183" s="2" t="s">
-        <v>1920</v>
-      </c>
-      <c r="L183" s="2" t="s">
+      <c r="N183" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="O183" s="2" t="s">
         <v>1922</v>
       </c>
-      <c r="M183" s="2" t="s">
-        <v>1921</v>
-      </c>
-      <c r="N183" s="2" t="s">
+      <c r="P183" s="2" t="s">
         <v>1923</v>
       </c>
-      <c r="O183" s="2" t="s">
+      <c r="Q183" s="2" t="s">
         <v>1924</v>
       </c>
-      <c r="P183" s="2" t="s">
+      <c r="R183" s="2" t="s">
         <v>1925</v>
       </c>
-      <c r="Q183" s="2" t="s">
+      <c r="S183" s="2" t="s">
         <v>1926</v>
       </c>
-      <c r="R183" s="2" t="s">
+      <c r="T183" s="2" t="s">
         <v>1927</v>
       </c>
-      <c r="S183" s="2" t="s">
+      <c r="U183" s="2" t="s">
         <v>1928</v>
       </c>
-      <c r="T183" s="2" t="s">
+      <c r="V183" s="2" t="s">
         <v>1929</v>
       </c>
-      <c r="U183" s="2" t="s">
+      <c r="W183" s="2" t="s">
         <v>1930</v>
       </c>
-      <c r="V183" s="2" t="s">
+      <c r="X183" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="W183" s="2" t="s">
-        <v>1932</v>
-      </c>
-      <c r="X183" s="2" t="s">
+    </row>
+    <row r="184" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C184" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>giftcodesbanner/三國志Thrones-禮包碼.jpg</v>
+      </c>
+      <c r="D184" s="2" t="str">
+        <f t="shared" si="21"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=三國志Thrones</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="K184" s="2" t="s">
         <v>1933</v>
       </c>
+      <c r="L184" s="2" t="s">
+        <v>1935</v>
+      </c>
     </row>
-    <row r="184" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="1942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="1951">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7542,6 +7542,42 @@
   </si>
   <si>
     <t>三國志Thrones</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄之地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLMobile777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruroro666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附靈召喚券*5+金幣*16888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附靈召喚券*3+金幣*8888+隨機強化沙禮包*20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面右上角四葉草點開</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點右下角齒輪設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤滑到底「兌換碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到信箱領取免費兌換碼禮包</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19654,11 +19690,11 @@
         <v>1913</v>
       </c>
       <c r="C183" s="2" t="str">
-        <f t="shared" ref="C183:C184" si="20">"giftcodesbanner/" &amp; A183 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C183:C185" si="20">"giftcodesbanner/" &amp; A183 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/真妖獸!廢柴要修仙-禮包碼.jpg</v>
       </c>
       <c r="D183" s="2" t="str">
-        <f t="shared" ref="D183:D184" si="21">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A183</f>
+        <f t="shared" ref="D183:D185" si="21">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A183</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=真妖獸!廢柴要修仙</v>
       </c>
       <c r="E183" s="2" t="s">
@@ -19756,7 +19792,46 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C185" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>giftcodesbanner/英雄之地-禮包碼.jpg</v>
+      </c>
+      <c r="D185" s="2" t="str">
+        <f t="shared" si="21"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄之地</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="N185" s="2" t="s">
+        <v>1946</v>
+      </c>
+    </row>
     <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="188" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="1951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="1952">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7578,6 +7578,11 @@
   </si>
   <si>
     <t>到信箱領取免費兌換碼禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《英勇之地》是一款奇幻風格的輕度 Roguelike RPG 動作冒險手遊。玩家將扮演一位英勇的騎士，在充滿挑戰的奇幻世界中，探索地圖、收集裝備與技能，並與各種怪物戰鬥。遊戲主打流暢的戰鬥體驗與多樣化的職業和技能組合，讓每場冒險都充滿未知與驚喜。透過不斷挑戰關卡，提升角色等級，並利用強大的裝備與技能來擊敗最終頭目。遊戲內提供多種禮包碼供玩家兌換豐富獎勵，同時也支援多樣化的代儲值管道，讓玩家能輕鬆獲得更多資源，快速增強戰力，享受更加暢快的遊戲樂趣。
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19804,6 +19809,9 @@
         <f t="shared" si="21"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=英雄之地</v>
       </c>
+      <c r="E185" s="8" t="s">
+        <v>1951</v>
+      </c>
       <c r="F185" s="2" t="s">
         <v>1947</v>
       </c>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -7545,10 +7545,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>英雄之地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HLMobile777</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7583,6 +7579,10 @@
   <si>
     <t xml:space="preserve">《英勇之地》是一款奇幻風格的輕度 Roguelike RPG 動作冒險手遊。玩家將扮演一位英勇的騎士，在充滿挑戰的奇幻世界中，探索地圖、收集裝備與技能，並與各種怪物戰鬥。遊戲主打流暢的戰鬥體驗與多樣化的職業和技能組合，讓每場冒險都充滿未知與驚喜。透過不斷挑戰關卡，提升角色等級，並利用強大的裝備與技能來擊敗最終頭目。遊戲內提供多種禮包碼供玩家兌換豐富獎勵，同時也支援多樣化的代儲值管道，讓玩家能輕鬆獲得更多資源，快速增強戰力，享受更加暢快的遊戲樂趣。
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英勇之地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19799,45 +19799,45 @@
     </row>
     <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>1942</v>
+        <v>1951</v>
       </c>
       <c r="C185" s="2" t="str">
         <f t="shared" si="20"/>
-        <v>giftcodesbanner/英雄之地-禮包碼.jpg</v>
+        <v>giftcodesbanner/英勇之地-禮包碼.jpg</v>
       </c>
       <c r="D185" s="2" t="str">
         <f t="shared" si="21"/>
-        <v>https://www.ssbuy.tw/gift-codes.html?game=英雄之地</v>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=英勇之地</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="F185" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G185" s="2" t="s">
         <v>1947</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="H185" s="2" t="s">
         <v>1948</v>
-      </c>
-      <c r="H185" s="2" t="s">
-        <v>1949</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>1939</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="K185" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="M185" s="2" t="s">
         <v>1943</v>
       </c>
-      <c r="L185" s="2" t="s">
+      <c r="N185" s="2" t="s">
         <v>1945</v>
-      </c>
-      <c r="M185" s="2" t="s">
-        <v>1944</v>
-      </c>
-      <c r="N185" s="2" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="1952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="1977">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7585,12 +7585,135 @@
     <t>英勇之地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>未鑑定勇者團</t>
+  </si>
+  <si>
+    <t>戰靈異聞社</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《未鑑定勇者團》是一款像素風格的放置型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RPG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手遊，帶您進入一個充滿懷舊與冒險的奇幻世界。遊戲核心特色在於其獨特的「未鑑定」系統，玩家將招募各種職業的勇者，他們的能力與潛力都是未知的，需要透過您的細心培養和鑑定，才能發掘出最強大的隱藏英雄。遊戲玩法輕鬆，即使離線也能持續獲得收益，讓您輕鬆養成您的勇者隊伍。為了讓您的冒險之路更加順暢，別忘了隨時查找最新的禮包碼，兌換豐富的虛寶獎勵，快速提升戰力。若想在遊戲中取得更多優勢，也可以考慮使用安全的代儲值服務，輕鬆獲取鑽石與各種稀有道具，打造無堅不摧的傳奇勇者團。立即加入，揭開所有未鑑定勇者的神秘面紗，展開一場獨一無二的冒險旅程！</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《戰靈異聞社》是一款都市怪談風格的卡牌放置手遊。遊戲將您帶入一個現代與靈異交織的世界，您將扮演「異聞社」的社長，專門解決各種超自然事件。遊戲美術風格獨特，融合了潮流與傳統元素，打造出百位以上各具特色的「戰靈」。玩家需要策略性地組合隊伍，利用戰靈之間的羈絆與技能，挑戰各種詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌之餘也能享受卡牌養成的樂趣。官方經常發放福利，記得要關注社群平台領取最新的禮包碼，強化您的戰靈隊伍。對於追求極致遊戲體驗的玩家，尋找可靠的代儲值管道能幫助您更快地收集心儀角色，解鎖更強大的力量，帶領您的異聞社，揭開所有神秘事件背後的真相。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面右上角「設置」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點開後按右下角「兌換碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼之後按是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25VACAYHOT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>礦山.D 通行證 x3 / 訓練.D 通行證 x3 / 礦石.D 通行證 x3 / 工藝.D 通行證 x3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08WAVEAUG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寶石 x30000 / 盟友召喚券 x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>領取免費兌換碼禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點擊主介面左上方「福利」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊進入「虛寶碼」介面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入虛寶碼點擊「提交」後便可前往信件領取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHIAO777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級固防寶石*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+橙品附魂之靈*1+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHIAO666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級強攻寶石*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+中品冰靈圖騰*2+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+中品雷靈圖騰*2+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7696,6 +7819,11 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7781,7 +7909,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7840,6 +7968,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19797,7 +19928,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>1951</v>
       </c>
@@ -19840,8 +19971,101 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="21" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C186" s="2" t="str">
+        <f t="shared" ref="C186:C187" si="22">"giftcodesbanner/" &amp; A186 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/未鑑定勇者團-禮包碼.jpg</v>
+      </c>
+      <c r="D186" s="2" t="str">
+        <f t="shared" ref="D186:D187" si="23">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A186</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=未鑑定勇者團</v>
+      </c>
+      <c r="E186" s="24" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="N186" s="2" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="21" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C187" s="2" t="str">
+        <f t="shared" si="22"/>
+        <v>giftcodesbanner/戰靈異聞社-禮包碼.jpg</v>
+      </c>
+      <c r="D187" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=戰靈異聞社</v>
+      </c>
+      <c r="E187" s="23" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="N187" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="O187" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="P187" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="Q187" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="R187" s="8" t="s">
+        <v>1976</v>
+      </c>
+      <c r="S187" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="T187" s="8" t="s">
+        <v>1975</v>
+      </c>
+    </row>
     <row r="188" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="189" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="190" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="1977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="1980">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7592,128 +7592,250 @@
     <t>戰靈異聞社</t>
   </si>
   <si>
+    <t>遊戲主畫面右上角「設置」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點開後按右下角「兌換碼」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼之後按是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25VACAYHOT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>礦山.D 通行證 x3 / 訓練.D 通行證 x3 / 礦石.D 通行證 x3 / 工藝.D 通行證 x3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08WAVEAUG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寶石 x30000 / 盟友召喚券 x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>領取免費兌換碼禮包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點擊主介面左上方「福利」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊進入「虛寶碼」介面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入虛寶碼點擊「提交」後便可前往信件領取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHIAO777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級固防寶石*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+橙品附魂之靈*1+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHIAO666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級強攻寶石*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COUNT2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+中品冰靈圖騰*2+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+喚靈神符*2+中品雷靈圖騰*2+靈器魂玉*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>見習骷髏王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待更新中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>《未鑑定勇者團》是一款像素風格的放置型</t>
+      <t>《見習骷髏王》是一款別出心裁的放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演從墳墓甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。為加速霸業，別忘了尋找社群發布的最新</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> RPG </t>
+      <t>禮包碼</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換關鍵資源讓軍團更壯大。若想在初期取得壓倒性優勢，可考慮使用便利的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
         <charset val="136"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>手遊，帶您進入一個充滿懷舊與冒險的奇幻世界。遊戲核心特色在於其獨特的「未鑑定」系統，玩家將招募各種職業的勇者，他們的能力與潛力都是未知的，需要透過您的細心培養和鑑定，才能發掘出最強大的隱藏英雄。遊戲玩法輕鬆，即使離線也能持續獲得收益，讓您輕鬆養成您的勇者隊伍。為了讓您的冒險之路更加順暢，別忘了隨時查找最新的禮包碼，兌換豐富的虛寶獎勵，快速提升戰力。若想在遊戲中取得更多優勢，也可以考慮使用安全的代儲值服務，輕鬆獲取鑽石與各種稀有道具，打造無堅不摧的傳奇勇者團。立即加入，揭開所有未鑑定勇者的神秘面紗，展開一場獨一無二的冒險旅程！</t>
+      <t>代儲值</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《戰靈異聞社》是一款都市怪談風格的卡牌放置手遊。遊戲將您帶入一個現代與靈異交織的世界，您將扮演「異聞社」的社長，專門解決各種超自然事件。遊戲美術風格獨特，融合了潮流與傳統元素，打造出百位以上各具特色的「戰靈」。玩家需要策略性地組合隊伍，利用戰靈之間的羈絆與技能，挑戰各種詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌之餘也能享受卡牌養成的樂趣。官方經常發放福利，記得要關注社群平台領取最新的禮包碼，強化您的戰靈隊伍。對於追求極致遊戲體驗的玩家，尋找可靠的代儲值管道能幫助您更快地收集心儀角色，解鎖更強大的力量，帶領您的異聞社，揭開所有神秘事件背後的真相。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲主畫面右上角「設置」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點開後按右下角「兌換碼」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>貼上在SSbuy複製好的禮包兌換碼之後按是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25VACAYHOT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>礦山.D 通行證 x3 / 訓練.D 通行證 x3 / 礦石.D 通行證 x3 / 工藝.D 通行證 x3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>08WAVEAUG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寶石 x30000 / 盟友召喚券 x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>領取免費兌換碼禮包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲內點擊主介面左上方「福利」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊進入「虛寶碼」介面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入虛寶碼點擊「提交」後便可前往信件領取</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHIAO777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級固防寶石*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COUNT1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+喚靈神符*2+橙品附魂之靈*1+靈器魂玉*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHIAO666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+喚靈神符*2+裝備尋寶券*2+7級強攻寶石*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COUNT3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COUNT2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+喚靈神符*2+中品冰靈圖騰*2+靈器魂玉*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+喚靈神符*2+中品雷靈圖騰*2+靈器魂玉*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，確保您能輕鬆碾壓前來挑戰的勇者。立即加入，帶領您的骷髏大軍，征服整個世界！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>《戰靈異聞社》是款都市怪談風卡牌放置手遊，帶您進入現代與靈異交織的世界。您將扮演「異聞社」社長，解決各種超自然事件。遊戲美術風格獨特，融合潮流與傳統，打造出百位各具特色的「戰靈」。玩家需策略性組合隊伍，利用戰靈羈絆與技能，挑戰詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌中也能享受卡牌養成樂趣。官方常發放福利，記得關注社群領取最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，強化您的隊伍。為追求極致體驗，尋找可靠的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管道能助您更快收集角色、解鎖強大力量，帶領異聞社揭開所有事件的真相。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>《未鑑定勇者團》是一款像素風放置型 RPG，帶您進入懷舊與冒險的奇幻世界。其核心特色在於獨特的「未鑑定」系統，玩家將招募職業、潛力皆未知的勇者，透過細心培養和鑑定，發掘最強大的隱藏英雄。遊戲玩法輕鬆，離線也能持續獲得收益，讓您無痛養成勇者隊伍。為了讓冒險之路更順暢，別忘了查找最新的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換豐富獎勵以快速提升戰力。若想取得更多優勢，也可考慮安全的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，輕鬆獲取稀有道具，打造無堅不摧的勇者團。立即加入，揭開所有勇者的神秘面紗，展開獨一無二的冒險！</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7819,11 +7941,6 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7909,7 +8026,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7968,9 +8085,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19983,32 +20097,32 @@
         <f t="shared" ref="D186:D187" si="23">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A186</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=未鑑定勇者團</v>
       </c>
-      <c r="E186" s="24" t="s">
+      <c r="E186" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>1954</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="G186" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="H186" s="2" t="s">
         <v>1956</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="I186" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="K186" s="2" t="s">
         <v>1957</v>
       </c>
-      <c r="H186" s="2" t="s">
+      <c r="L186" s="2" t="s">
         <v>1958</v>
       </c>
-      <c r="I186" s="2" t="s">
-        <v>1963</v>
-      </c>
-      <c r="K186" s="2" t="s">
+      <c r="M186" s="2" t="s">
         <v>1959</v>
       </c>
-      <c r="L186" s="2" t="s">
+      <c r="N186" s="2" t="s">
         <v>1960</v>
-      </c>
-      <c r="M186" s="2" t="s">
-        <v>1961</v>
-      </c>
-      <c r="N186" s="2" t="s">
-        <v>1962</v>
       </c>
     </row>
     <row r="187" spans="1:24" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20023,50 +20137,89 @@
         <f t="shared" si="23"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=戰靈異聞社</v>
       </c>
-      <c r="E187" s="23" t="s">
-        <v>1955</v>
+      <c r="E187" t="s">
+        <v>1978</v>
       </c>
       <c r="F187" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H187" s="2" t="s">
         <v>1964</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="K187" s="2" t="s">
         <v>1965</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="L187" s="2" t="s">
         <v>1966</v>
       </c>
-      <c r="K187" s="2" t="s">
+      <c r="M187" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="N187" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="O187" s="2" t="s">
         <v>1967</v>
       </c>
-      <c r="L187" s="2" t="s">
+      <c r="P187" s="2" t="s">
         <v>1968</v>
       </c>
-      <c r="M187" s="2" t="s">
+      <c r="Q187" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="R187" s="8" t="s">
+        <v>1974</v>
+      </c>
+      <c r="S187" s="2" t="s">
         <v>1971</v>
       </c>
-      <c r="N187" s="2" t="s">
-        <v>1972</v>
-      </c>
-      <c r="O187" s="2" t="s">
-        <v>1969</v>
-      </c>
-      <c r="P187" s="2" t="s">
-        <v>1970</v>
-      </c>
-      <c r="Q187" s="2" t="s">
-        <v>1974</v>
-      </c>
-      <c r="R187" s="8" t="s">
+      <c r="T187" s="8" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C188" s="2" t="str">
+        <f t="shared" ref="C188" si="24">"giftcodesbanner/" &amp; A188 &amp; "-禮包碼.jpg"</f>
+        <v>giftcodesbanner/見習骷髏王-禮包碼.jpg</v>
+      </c>
+      <c r="D188" s="2" t="str">
+        <f t="shared" ref="D188" si="25">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A188</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=見習骷髏王</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>1976</v>
       </c>
-      <c r="S187" s="2" t="s">
-        <v>1973</v>
-      </c>
-      <c r="T187" s="8" t="s">
-        <v>1975</v>
+      <c r="G188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="O188" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="P188" s="2" t="s">
+        <v>1976</v>
       </c>
     </row>
-    <row r="188" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="189" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="190" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="191" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -7685,55 +7685,6 @@
   </si>
   <si>
     <r>
-      <t>《見習骷髏王》是一款別出心裁的放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演從墳墓甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。為加速霸業，別忘了尋找社群發布的最新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>禮包碼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，兌換關鍵資源讓軍團更壯大。若想在初期取得壓倒性優勢，可考慮使用便利的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>代儲值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>服務，確保您能輕鬆碾壓前來挑戰的勇者。立即加入，帶領您的骷髏大軍，征服整個世界！</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>《戰靈異聞社》是款都市怪談風卡牌放置手遊，帶您進入現代與靈異交織的世界。您將扮演「異聞社」社長，解決各種超自然事件。遊戲美術風格獨特，融合潮流與傳統，打造出百位各具特色的「戰靈」。玩家需策略性組合隊伍，利用戰靈羈絆與技能，挑戰詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌中也能享受卡牌養成樂趣。官方常發放福利，記得關注社群領取最新</t>
     </r>
     <r>
@@ -7829,6 +7780,10 @@
       </rPr>
       <t>服務，輕鬆獲取稀有道具，打造無堅不摧的勇者團。立即加入，揭開所有勇者的神秘面紗，展開獨一無二的冒險！</t>
     </r>
+  </si>
+  <si>
+    <t>《見習骷髏王》是一款放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。別忘了尋找社群發布的最新禮包碼，兌換關鍵資源讓軍團更壯大。若想在初期取得壓倒性優勢，可考慮使用便利的代儲值服務，確保您能輕鬆碾壓前來挑戰的勇者。帶領您的骷髏大軍，征服整個世界！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -20098,7 +20053,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=未鑑定勇者團</v>
       </c>
       <c r="E186" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>1954</v>
@@ -20138,7 +20093,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=戰靈異聞社</v>
       </c>
       <c r="E187" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>1962</v>
@@ -20193,7 +20148,7 @@
         <v>https://www.ssbuy.tw/gift-codes.html?game=見習骷髏王</v>
       </c>
       <c r="E188" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>1976</v>

--- a/giftcodes.xlsx
+++ b/giftcodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="1988">
   <si>
     <t>遊戲名稱</t>
   </si>
@@ -7783,6 +7783,38 @@
   </si>
   <si>
     <t>《見習骷髏王》是一款放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。別忘了尋找社群發布的最新禮包碼，兌換關鍵資源讓軍團更壯大。若想在初期取得壓倒性優勢，可考慮使用便利的代儲值服務，確保您能輕鬆碾壓前來挑戰的勇者。帶領您的骷髏大軍，征服整個世界！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*80萬+英雄經驗*20萬+印章碎片*100+武鬥秘典*2+高級招募券*5+鑽石*500+香吉士碎片*50+進階石*70+密文卷軸*20+競技場挑戰券*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ANIMEWARD1zON7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點遊戲主畫面點左上角頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按右下角「禮包兌換」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按兌換即可領取免費兌換禮包碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全明星無雙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《全明星無雙》是一款集結超人氣動漫角色的3D動作(盜版)手遊，打造夢幻的跨次元戰場。遊戲採用次世代技術，呈現華麗戰鬥畫面與流暢連招，帶來前所未有的打擊快感。您可以收集悟空、魯夫、炭治郎等英雄，組建最強隊伍。玩法豐富，有沉浸式主線劇情、PVP競技場與團隊Raid副本。為了幫助玩家快速成長，官方經常發放最新的禮包碼，讓您輕鬆獲得稀有道具。SSbuy也提供便利安全的代儲值服務，確保您消費物超所值，在稱霸全明星的道路上暢行無阻！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20140,11 +20172,11 @@
         <v>1975</v>
       </c>
       <c r="C188" s="2" t="str">
-        <f t="shared" ref="C188" si="24">"giftcodesbanner/" &amp; A188 &amp; "-禮包碼.jpg"</f>
+        <f t="shared" ref="C188:C189" si="24">"giftcodesbanner/" &amp; A188 &amp; "-禮包碼.jpg"</f>
         <v>giftcodesbanner/見習骷髏王-禮包碼.jpg</v>
       </c>
       <c r="D188" s="2" t="str">
-        <f t="shared" ref="D188" si="25">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A188</f>
+        <f t="shared" ref="D188:D189" si="25">"https://www.ssbuy.tw/gift-codes.html?game="&amp;A188</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=見習骷髏王</v>
       </c>
       <c r="E188" t="s">
@@ -20175,7 +20207,40 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="189" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C189" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>giftcodesbanner/全明星無雙-禮包碼.jpg</v>
+      </c>
+      <c r="D189" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=全明星無雙</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>1980</v>
+      </c>
+    </row>
     <row r="190" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="191" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="192" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
